--- a/neuroblastoma/results/RNA-seq/RNA-seq_MES_vs_ADR/tables/MES_vs_ADRN_GSEA_C6_onco.xlsx
+++ b/neuroblastoma/results/RNA-seq/RNA-seq_MES_vs_ADR/tables/MES_vs_ADRN_GSEA_C6_onco.xlsx
@@ -39,1138 +39,1138 @@
     <t xml:space="preserve">hits</t>
   </si>
   <si>
+    <t xml:space="preserve">Mel18 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABLIM3 , ADAM12 , ADAM19 , ADGRE5 , AGRN , ARL4C , ASPH , BDKRB2 , C3orf52 , CA12 , CDCP1 , CDH13 , CHST11 , CHST3 , CLDN1 , COL7A1 , CPA4 , CSF1 , CSPG4 , CTSS , DDX11 , ECM1 , EDN1 , EPHA2 , F3 , FADS3 , FAP , FJX1 , FOSL1 , FURIN , FZD6 , GAL , GREM1 , HAS2 , HBEGF , HS3ST3A1 , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB8 , ITPR3 , JAG1 , LIF , LRIG1 , MICA , MICB , NRP1 , NT5E , P2RX5 , P3H3 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PLAUR , PTHLH , RREB1 , SLC1A5 , SLC22A4 , SLC29A1 , SLC6A9 , SLC7A11 , SLC7A5 , SLCO2A1 , SLCO4A1 , STEAP3 , STX1A , TAP1 , TGFB2 , VEGFC , WNT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bmi1 Dn Mel18 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ABLIM3 , ADAM12 , ADAM19 , ADGRE5 , ADM2 , ANXA3 , APBB2 , ARL4C , ASPH , ATF3 , BST1 , CDH13 , CHST11 , CHST3 , CLDN1 , COL7A1 , CPA4 , CSF1 , CSPG4 , CXCL8 , EDN1 , EHD1 , F3 , FADS3 , FAP , FJX1 , FOSL1 , GAB2 , GADD45A , GAL , GREM1 , HAS2 , HBEGF , IL1A , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB8 , JAG1 , KCNN4 , KLF7 , LIF , MAP3K7CL , MARCHF3 , MGLL , MICA , NKAIN1 , NT5E , P2RX5 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PLAUR , PODXL , PTHLH , RREB1 , SCML2 , SLC22A4 , SLC6A9 , SLC7A11 , SLC7A5 , STX1A , TAGLN , TGFB2 , TRIB3 , VEGFC , WEE1 , WNT5B , ZEB2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Egfr Up.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCC3 , ACTG2 , ADM , AKAP12 , ANGPTL4 , AOX1 , ARAP2 , ARFGAP3 , ARID5B , ASPH , ATXN1 , BCL3 , BMP7 , CAPN2 , CARMIL1 , CASP7 , CCDC68 , CCL2 , CCN1 , CCN2 , CEBPD , CEMIP , CLDN1 , CMAHP , COL5A2 , COTL1 , CRISPLD2 , CXADR , CYP27B1 , DRAM1 , DUSP4 , DUSP5 , EDN1 , EGFR , ELK3 , ELL2 , ENPP1 , EPAS1 , ETHE1 , EXT1 , F2RL1 , FADS3 , FERMT2 , FGFR3 , FHOD1 , FNDC3B , GAL , GBP1 , GBP2 , GCLM , GCNT1 , GJA1 , GRAMD2B , HBEGF , HSPA2 , ICAM1 , IFIT3 , IL1R1 , IL4R , INHBA , IRF1 , ITGA2 , ITGA3 , ITGB6 , KLF4 , KRT7 , KRT81 , LIF , LOXL2 , LPP , MALL , MAOA , MBNL2 , MEIS3P1 , MGAT4A , MGLL , MIR22HG , MMP1 , MMP10 , NFKB2 , PAPSS2 , PCDH9 , PDE4B , PDLIM7 , PGM3 , PHLDA1 , PIGA , PLAGL1 , PSMB10 , PSMB9 , RAB27A , RCAN1 , RGS16 , RHOQ , RPS6KA3 , SAT1 , SDCBP , SEC23A , SEL1L3 , SGMS1 , SLC7A11 , SLCO2A1 , SPAG1 , SQOR , SUSD6 , TAP1 , TCIM , TFPI , TGFB2 , TNFAIP8 , TNNT1 , TNS3 , WIPI1 , WNT5A</t>
+    <t xml:space="preserve">ABCC3 , ANGPTL4 , AOX1 , ARFGAP3 , ARID5B , ASPH , ATF3 , ATXN1 , BCL3 , BMP7 , CAPN2 , CASP7 , CCN1 , CCN2 , CEBPD , CEMIP , CLDN1 , CMAHP , COTL1 , CXADR , DRAM1 , DUSP4 , DUSP5 , EDN1 , EGFR , ELK3 , ELL2 , EPAS1 , ETHE1 , EXT1 , F2RL1 , FADS3 , FERMT2 , FGFR3 , FHOD1 , FNDC3B , GAL , GBP1 , GBP2 , GCLM , GJA1 , HBEGF , HSPA2 , ICAM1 , IFIT3 , IL1R1 , IL4R , INHBA , IRF1 , ITGA2 , ITGA3 , KLF4 , LIF , LOXL2 , LPP , MAOA , MBNL2 , MGAT4A , MGLL , MIR22HG , MMP1 , MMP10 , NFKB2 , PAPSS2 , PCDH9 , PDE4B , PDLIM7 , PHLDA1 , PSMB10 , PSMB9 , RAB27A , RCAN1 , RGS16 , RPS6KA3 , SAMD4A , SAT1 , SDCBP , SEC23A , SEL1L3 , SGMS1 , SLC7A11 , SLCO2A1 , SPAG1 , SQOR , TAP1 , TGFB2 , TNFAIP8 , WIPI1 , WNT5A</t>
   </si>
   <si>
     <t xml:space="preserve">Bmi1 Dn.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCA1 , ACKR3 , ACTA2 , ADAM12 , ADGRE5 , ADRB2 , AGRN , ANXA3 , ASPH , B4GALNT1 , BDKRB2 , BST1 , C3AR1 , CCN3 , CD82 , CDCP1 , CHST3 , CLDN1 , CLSPN , COL13A1 , COL7A1 , CPA4 , CRISPLD2 , CSF1 , CSPG4 , CSPG5 , CTSS , DHRS3 , DKK1 , EDN1 , EPHA2 , F3 , FADS3 , FAP , FGFR1 , FJX1 , FLNB , FURIN , GAL , GPRC5A , HAS2 , HBEGF , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB6 , ITGB8 , JAG1 , KCNC4 , LAMB3 , LCP1 , LIF , LRIG1 , LRRC15 , MARCHF3 , MFAP5 , MFGE8 , MICA , MICB , MMP3 , NT5E , P3H3 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PODXL , PSG5 , PTHLH , SIRPA , SLC1A5 , SLC29A1 , SLC29A2 , SLC7A5 , SLCO2A1 , SLCO4A1 , SRPX2 , STX1A , TAGLN , TAP1 , TCIM , TGFB2 , TIE1 , TMEM51 , TNFRSF9 , TRIO , VANGL1 , VEGFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bmi1 Dn Mel18 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ABLIM3 , ADAM12 , ADAM19 , ADGRE5 , ADM , ADM2 , ADRB2 , ANXA3 , APBB2 , ARL4C , ASPH , BIRC3 , BST1 , C3AR1 , CDC42EP2 , CDH13 , CHST3 , CLDN1 , COL13A1 , COL7A1 , CPA4 , CRISPLD2 , CSF1 , CSPG4 , CXCL8 , EDN1 , EHD1 , F3 , FADS3 , FAP , FJX1 , FOSL1 , GAB2 , GADD45A , GAL , HAS2 , HBEGF , HTR1D , IL1A , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB6 , ITGB8 , JAG1 , KCNN4 , KLF7 , LAMB3 , LCP1 , LIF , LRRC15 , MAP3K7CL , MARCHF3 , MGLL , MICA , NKAIN1 , NPPB , NT5E , P2RX5 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PLAUR , PODXL , PTHLH , RREB1 , SCML2 , SIK1 , SLC22A4 , SLC6A9 , SLC7A11 , SLC7A5 , STX1A , TAGLN , TCIM , TGFB2 , TMEM51 , TNFRSF9 , TRIB3 , TRIO , TUFT1 , VEGFC , WNT5B , ZC3H12A , ZEB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mel18 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABLIM3 , ADAM12 , ADAM19 , ADGRE5 , ADM , AGRN , ARL4C , ASPH , BDKRB2 , C3AR1 , C3orf52 , CA12 , CACNG4 , CDCP1 , CDH13 , CHST2 , CHST3 , CLDN1 , CLSPN , COL13A1 , COL7A1 , CPA4 , CRISPLD2 , CSF1 , CSPG4 , CTSS , DDX11 , ECM1 , EDN1 , EPHA2 , F3 , FADS3 , FAP , FJX1 , FOSL1 , FURIN , FZD6 , GAL , HAS2 , HBEGF , HS3ST3A1 , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB8 , JAG1 , LAMB3 , LCP1 , LIF , LRIG1 , MICA , MICB , NRP1 , NT5E , P2RX5 , P3H3 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PLAUR , PTHLH , RREB1 , SIK1 , SLC1A5 , SLC22A4 , SLC29A1 , SLC6A9 , SLC7A11 , SLC7A5 , SLCO2A1 , SLCO4A1 , SPP1 , SRPX2 , STEAP3 , STX1A , TAP1 , TGFB2 , TGFBR3 , TIE1 , TMEM51 , TNFRSF9 , VEGFC , WNT5B , ZC3H12A</t>
+    <t xml:space="preserve">ABCA1 , ACKR3 , ACTA2 , ADAM12 , ADGRE5 , AGRN , ANPEP , ANXA3 , ASPH , BDKRB2 , BST1 , CCN3 , CD82 , CDCP1 , CHST11 , CHST3 , CLDN1 , COL7A1 , CPA4 , CSF1 , CSPG4 , CTNS , CTSS , DKK1 , EDN1 , EPHA2 , F3 , FADS3 , FAP , FJX1 , FLNB , FURIN , GAL , GPRC5A , GREM1 , HAS2 , HBEGF , IL7R , INHBA , ITGA3 , ITGA4 , ITGA5 , ITGB8 , JAG1 , LIF , LRIG1 , MARCHF3 , MFGE8 , MICA , MICB , MMP3 , NT5E , P3H3 , PAPPA , PDCD1LG2 , PIEZO1 , PLAT , PLXNA2 , PODXL , PSG5 , PTHLH , SIRPA , SLC1A5 , SLC29A1 , SLC29A2 , SLC7A5 , SLCO2A1 , SLCO4A1 , STX1A , TAGLN , TAP1 , TGFB2 , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mek Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC3 , ABCG1 , AGAP1 , AKR1C3 , ALDH1A3 , ANGPTL4 , AQP3 , ARHGDIB , ARL4C , ARRB1 , ASPH , ATXN1 , BCAM , BCL3 , BMP7 , CAPN2 , CAPN5 , CEMIP , CHST11 , CLMN , COTL1 , CRAT , CRLF1 , CUEDC1 , CXADR , CXCR4 , DBNDD1 , DUSP4 , EDN1 , EFHD2 , EHBP1L1 , ELL2 , ENO2 , EPAS1 , EPHA2 , EPHX1 , F2RL1 , FERMT2 , FGFR3 , FLVCR2 , FOSL1 , GAL , GALNT12 , GDF15 , IL4R , ITGB4 , KCNN4 , KLF4 , L1CAM , LAMC1 , LHFPL6 , LIMCH1 , LOXL1 , MAOA , MAP3K9 , MICAL2 , MXRA7 , MYO1D , NEDD9 , NPC2 , OTULINL , PACS1 , PCDH1 , PCDH9 , PDLIM7 , PEG10 , PLAU , PLPP1 , PPARG , RAI14 , RAI2 , S100A6 , SAMD4A , SDCBP , SLC2A10 , SLC7A11 , SORL1 , SPAG1 , SPTBN2 , TGFB1I1 , TGFBI , THEM6 , TIMP2 , TNFAIP8 , VASP , VWA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc V6.5 Up Early.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEBP1 , AHNAK , ALX3 , ANXA1 , ANXA2 , ANXA3 , ANXA5 , AQP3 , AXL , B2M , BCL3 , BGN , BHLHE40 , C16orf74 , CALD1 , CALML4 , CAPN2 , CAVIN1 , CAVIN2 , CCDC80 , CCN1 , CCN2 , CD44 , CDC42EP1 , COL11A1 , COL1A1 , COL3A1 , COL4A1 , COL4A2 , CSRP1 , F2RL1 , FAP , FBLN2 , FGF2 , FHL2 , GAP43 , GASK1B , GBP2 , GSN , HBEGF , HTRA1 , IGFBP3 , IGFBP7 , INHBA , KIF18A , KLF4 , LOX , LOXL1 , MGP , NID1 , NUPR1 , PARVA , PLAU , S100A4 , S100A6 , SCARA3 , SERPINE1 , SLC39A1 , SLC8A3 , SOCS3 , SULT1E1 , TAGLN , TGFB1I1 , TIMP2 , TM4SF1 , TNC , TNFRSF12A , TSHZ2 , TUBB6 , ZFP36L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordenonsi Yap Conserved Signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGFG2 , AMOTL2 , AXL , CAVIN2 , CCN1 , CCN2 , CENPF , CRIM1 , DAB2 , DDAH1 , DLC1 , DUSP1 , FGF2 , FLNA , FSTL1 , GADD45B , GAS6 , GLS , HEXB , ITGB5 , LHFPL6 , PDLIM2 , SCHIP1 , SERPINE1 , SGK1 , SLIT2 , STMN1 , TGFB2 , TGM2 , THBS1 , TNS1 , TOP2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erbb2 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC3 , ABCG1 , ACHE , ANGPTL4 , ANXA6 , APLP1 , AQP3 , ASPH , ATXN1 , BCAM , BCL3 , BCL6 , BMPR1B , CAPN2 , CAPN5 , CAST , CEMIP , CHST11 , CLMN , CREB3L2 , CRLF1 , CXADR , CXCL8 , CXCR4 , DAB2 , DOCK10 , DRAM1 , DUSP4 , EDN1 , ENO2 , EPAS1 , EPHX1 , GALNT12 , GDF15 , GDPD3 , GNAI2 , HSPA2 , IL1R1 , ITGB4 , KCNMA1 , KCNN4 , KIAA0513 , LAMB2 , LIMCH1 , LMO3 , LOXL1 , MAOA , METRN , MGAT4A , MUC1 , MXRA7 , MYO1D , NIBAN1 , NOTCH3 , NPC2 , P4HA2 , PACS1 , PAPSS2 , PCDH1 , PDE4B , PGPEP1 , PLPP1 , PLPP2 , PPP1R3C , PRPS1 , S100A6 , SAT1 , SDCBP , SLC2A10 , SOX9 , SPTBN2 , ST8SIA4 , TENT5C , THEM6 , VASP , VWA1 , WIPI1 , ZNF365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raf Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC3 , ACSL4 , ANGPTL4 , ARHGAP26 , ASPH , CAPN2 , CAST , CD44 , CEBPD , CLDN1 , CLMN , COTL1 , CREB3L2 , CRIM1 , DHTKD1 , DUSP4 , EGFR , EPAS1 , ERAP1 , FAM13A , FERMT2 , FGF1 , GALNT12 , GATA2 , GCLM , GM2A , GPR37 , GRB10 , HACD1 , HBEGF , HEG1 , HSPA2 , IMPA2 , ITGA6 , KCNN4 , KLF6 , L1CAM , LAMC1 , MALT1 , MICAL2 , MORC4 , MTMR11 , NDC80 , NEDD4 , NFE2L3 , NMI , NMU , NPC2 , NUAK1 , OPTN , PARVA , PEG10 , PHYH , PKD2 , PLS3 , PPARG , PRPS1 , PSMB10 , PSMB9 , PXDC1 , PYGL , RCAN1 , RNF144A , RRAS2 , SAT1 , SCARA3 , SCG2 , SDCBP , SEPTIN6 , SLC31A2 , SMAGP , SYNE2 , TBC1D2 , TNFAIP8 , UPP1 , VTN , XYLT1 , ZNF331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Nomo Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ACVR1 , ARID5B , ARL4C , ASPH , ATG101 , BBS12 , BCL3 , BCL6 , CADM1 , CAMK2D , CC2D1B , CCDC71L , CFL2 , CLVS1 , COL6A3 , COQ10B , CSRNP1 , DAB2 , DOCK4 , DUSP1 , DUSP5 , EPAS1 , FAM114A1 , FAM13A , FBXL13 , FBXO32 , GASK1B , GBP3 , GCNT2 , GDF15 , GJA1 , GLIPR1 , GPNMB , GPR137B , H2BC4 , HECW2 , HMOX1 , HNMT , ICAM1 , IER3 , IFI16 , IL10RA , IL1A , IL1R1 , IL6ST , IL7R , IRS1 , JAKMIP2 , JUN , KCNJ2 , KDELR3 , KIFC3 , KLF6 , LACC1 , LIMK1 , MAFF , MAP3K8 , MGAT4B , MIR22HG , MMP1 , MMP10 , MTSS1 , NAMPT , NCEH1 , NRP1 , NUAK1 , OSTM1 , OTUD1 , PGBD5 , PHLDA1 , PID1 , PINLYP , PLAU , PPCS , PPP1R15A , PTBP2 , PTPN3 , PTPRO , PTX3 , RAB12 , RASGRP3 , RHOB , RIN2 , RIT1 , SAMD9L , SCG2 , SDC4 , SEMA4D , SETBP1 , SGK1 , SQSTM1 , STAM2 , STC1 , STK17B , TGIF1 , TLR6 , TM6SF1 , TWF1 , UBE3C , UEVLD , UPP1 , USP53 , VWA5A , WNT5A , ZEB2 , ZFP36 , ZFP36L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tbk1.Df Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACVR1 , ADGRE5 , AKR1C3 , ANPEP , ANXA6 , ATF3 , C1GALT1C1 , C3orf52 , CASP7 , CHGB , CHIC2 , CIB1 , CKB , CRABP2 , CRIP2 , CSGALNACT2 , CXCL8 , CYBRD1 , DAB2 , DCUN1D2 , DLG3 , DNMT3B , DPY19L1 , DUSP14 , DUSP3 , DUSP5 , ENDOD1 , ENDOG , ENO2 , EOGT , EPB41L4B , FERMT2 , FZD6 , GALNT10 , GALNT12 , GCH1 , GPHN , GRINA , GTF2H1 , HBEGF , HMOX1 , HSPA2 , IGSF3 , IL1A , IL1R1 , ISL1 , ITGAV , LAPTM4A , LIPG , MGLL , MICA , MTCL1 , NF2 , NFKB1 , NRBF2 , OSTM1 , P2RX5 , PASK , PCLO , PEG10 , PID1 , PIK3CD , PIP4K2C , PLAU , PLAUR , PLEKHF2 , PLPP2 , PPP2R3A , PROS1 , PTHLH , PXDC1 , PXDN , RAB29 , RIN2 , RIT1 , RPL23AP7 , RRAS , RUNX1 , SCHIP1 , SERTAD2 , SIRPA , SLC2A10 , SLC2A3 , SLC30A1 , SLC35A2 , SLC37A1 , SNAP23 , SNCA , SPOCK1 , SRPX , STEAP1B , STX3 , TFE3 , TMED5 , TMEM104 , TMEM184B , TMEM50A , TNFAIP1 , TNFAIP3 , TNFAIP8 , TP53I3 , TRAK2 , TRAM2 , TRIM36 , VAMP3 , VCAN , WWTR1</t>
   </si>
   <si>
     <t xml:space="preserve">Kras.kidney Up.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ADCY1 , AK5 , ANK2 , ANK3 , ATP1A2 , CALB1 , CDK5R1 , CFAP69 , CHGA , CHGB , CPEB3 , CRYAB , CRYM , DNM3 , DYNC1I1 , EMP1 , ESRRG , FZD3 , GABRA5 , GAD1 , GAP43 , GATM , GLDC , GPNMB , GPR19 , GPR37 , GPRC5B , GRIA2 , HPCAL4 , ITGBL1 , KCNJ8 , KIF5C , LIMCH1 , LMO3 , MAP7 , NAP1L2 , NEBL , NEFL , NME5 , NMNAT2 , NOL4 , NRCAM , NRXN1 , NSG1 , NSG2 , NUDT11 , PCDH9 , PEG3 , PELI2 , PLCL1 , PLP1 , PLSCR4 , PNMA2 , RAPGEF4 , RIT2 , RTN1 , SATB1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SNAP25 , SNAP91 , SOBP , SORBS1 , ST3GAL6 , TCEAL2 , TMEM100 , TMOD1 , TRIB2 , TRIL , TRIM9 , TSPAN7 , TUBB4A , WSCD1 , ZNF536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mek Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCC3 , ABCG1 , ACSL1 , ADM , AGAP1 , AKR1C2 , AKR1C3 , ANGPTL4 , ANOS1 , AQP3 , ARHGDIB , ARL4C , ARRB1 , ASPH , ATXN1 , BCAM , BCL3 , BMP7 , C1orf115 , CAPN2 , CAPN5 , CEMIP , CLDN4 , COL5A2 , CORO1A , COTL1 , CRAT , CRLF1 , CUEDC1 , CXADR , CXCR4 , DBNDD1 , DUSP4 , EDN1 , EFHD2 , EHBP1L1 , ELL2 , ENO2 , EPAS1 , EPHA2 , EPHX1 , F2RL1 , FERMT2 , FGFR3 , FLVCR2 , FOSL1 , GAL , GALNT12 , GCNT1 , GDF15 , GRAMD2B , IL4R , INAVA , ITGB4 , KCNN4 , KLF4 , KRT7 , KRT81 , L1CAM , LAMC1 , LHFPL6 , LIMCH1 , LOXL1 , MALL , MAOA , MAP3K9 , MICAL2 , MXRA7 , MYO1D , NEDD9 , NPC2 , NT5DC2 , OTULINL , PACS1 , PCDH1 , PCDH9 , PDLIM7 , PEG10 , PLAU , PLPP1 , PPARG , PTK7 , RAI14 , RAI2 , S100A6 , SDCBP , SGCE , SLC2A10 , SLC7A11 , SPAG1 , SPTBN2 , TGFB1I1 , TGFBI , THEM6 , TIMP2 , TNFAIP8 , TNS3 , VASP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tbk1.Df Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACVR1 , ADGRE5 , ADGRG1 , AKR1C3 , ANKMY2 , ANXA6 , AP5Z1 , ATP10D , ATP11B , C1GALT1C1 , C3orf52 , CASP7 , CCDC68 , CHGB , CHIC2 , CIB1 , CKB , CLCA2 , CLDN4 , CORO1A , CRABP2 , CRIP2 , CSGALNACT2 , CXCL8 , CYBRD1 , DAB2 , DLG3 , DNMT3B , DPY19L1 , DUSP14 , DUSP3 , DUSP5 , EMP3 , ENDOD1 , ENDOG , ENO2 , EOGT , EPB41L4B , FERMT2 , FZD6 , GALNT10 , GALNT12 , GCH1 , GINS1 , GNG11 , GPHN , GRINA , GTF2H1 , HBEGF , HSPA2 , IGF1R , IGSF3 , IL1A , IL1R1 , ISL1 , ITGAV , KLF11 , LAPTM4A , LIPG , MGLL , MICA , MMP9 , MREG , MTCL1 , NETO2 , NF2 , NFKB1 , NRBF2 , NUDT4 , OSTM1 , P2RX5 , PASK , PCLO , PEG10 , PID1 , PIK3CD , PIP4K2C , PLAU , PLAUR , PLEKHF2 , PLPP2 , PPP2R3A , PROS1 , PTHLH , PTK7 , PXDC1 , PXDN , RAB29 , RAB4B , RABGEF1 , RAD51AP1 , RIN2 , RIT1 , RLN2 , RPL23AP7 , RRAS , RUNX1 , SCHIP1 , SERTAD2 , SIRPA , SLC2A10 , SLC2A3 , SLC30A1 , SLC33A1 , SLC35A2 , SLC37A1 , SLC38A6 , SNAP23 , SNCA , SNX24 , SPOCK1 , SRPX , STEAP1B , STX3 , TFE3 , TMED5 , TMEM104 , TMEM184B , TNFAIP1 , TNFAIP3 , TNFAIP8 , TNFRSF10B , TNS3 , TP53I3 , TPST1 , TRAK2 , TRAM2 , TRIM36 , TUFT1 , UXS1 , VAMP3 , VCAN , WWTR1 , ZC3H12A</t>
+    <t xml:space="preserve">ADCY1 , AK5 , ANK2 , CALB1 , CDK5R1 , CHGA , CHGB , CPEB3 , DLGAP2 , DNM3 , ESRRG , FZD3 , GAP43 , GATM , GLDC , GPNMB , GPR19 , GPR37 , GRIA2 , HPCAL4 , KIF5C , LIMCH1 , LMO3 , NAP1L2 , NEBL , NMNAT2 , NOL4 , NRCAM , NRXN1 , NSG1 , NSG2 , NUDT11 , PCDH9 , PEG3 , PELI2 , PLCL1 , PNMA2 , RAPGEF4 , RTN1 , SATB1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SNAP25 , SNAP91 , SOBP , SORBS1 , SORL1 , ST3GAL6 , SYT1 , TCEAL2 , TMOD1 , TRIB2 , TRIL , TRIM9 , TSPAN7 , TUBB4A , ZNF536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2f1 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4GALT , ACKR3 , ADAMTS1 , ADARB1 , AJUBA , AMPD3 , ANGPTL4 , ANXA1 , ANXA4 , APBB2 , APC2 , AVPI1 , BAG3 , BCL6 , CALML4 , CAPN2 , CAVIN2 , CHRNA7 , COL11A1 , COL3A1 , CRIP2 , CSF1 , DAB2 , EBF1 , EFNA4 , EPS8 , F3 , FAS , FCHO1 , GADD45A , GBP2 , HES6 , HLA-B , IFIT2 , IL1R1 , IL6ST , KLF2 , LAMA4 , LIMA1 , LRIG1 , MMP24OS , MX1 , MYC , NFKB1 , NFKBIZ , NOTCH2 , NPR1 , PAK3 , PHLDA1 , PLA2G4A , PLAT , PLXND1 , RAB11FIP5 , RAB9A , RALGDS , RAP2B , RASA3 , RUNX2 , SASH1 , SEC23A , SERTAD1 , SGK1 , SIX5 , STAT6 , STX4 , TCF4 , TGFB1I1 , TGFB3 , TGM2 , TNXB , TRIB3 , UBE2H , UNC93B1 , VCAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.df.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL , ADGRE5 , AKR1C3 , AKT3 , ALDH1A3 , ANKRD46 , ANPEP , ASPH , AURKB , BCL2L1 , BCL3 , BCL6 , BMP6 , CALHM2 , CCDC85B , CDKN2B , CHRNA5 , CLPB , COL6A3 , CRYZ , CUX2 , CXCL8 , DKK1 , DLGAP5 , DPYD , DPYSL2 , E2F8 , EHBP1L1 , ELK3 , G6PD , GCH1 , GREM1 , HS3ST3A1 , HSPA2 , IFI35 , IFI44L , IFIT1 , IL13RA2 , INHBA , INPP4B , LGALS3BP , LOXL2 , MAP3K6 , MMP1 , MVP , NAT1 , NRP1 , PDLIM2 , PID1 , PITPNC1 , PLAT , PLAU , PLIN3 , PLPP2 , PROCR , PTPRG , PXDN , RAC2 , RASIP1 , RETSAT , RPS6KA5 , RRAD , SERPINE1 , SLC22A4 , SLC2A10 , SMTN , SRPX , STX4 , SUGCT , TLR2 , TM4SF1 , TMEM158 , TP53I3 , VCAN , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cahoy Astroglial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTA2 , ADGRG6 , AEBP1 , ANXA1 , ANXA4 , ATOH8 , ATP8A1 , C1QTNF1 , CALHM5 , CASP1 , CLCN4 , CNN1 , COL5A1 , CTTN , DYSF , FAS , FBLN5 , GLIPR2 , GNA14 , GPHN , GPNMB , HMOX1 , IGFBP3 , KLHL21 , LGALS3 , LOX , LOXL2 , LPIN3 , LTBP2 , MORC4 , MSN , MYOF , NUAK2 , PHACTR3 , PRSS23 , PTRH1 , RASSF4 , SEMA3B , SERPINE1 , SLC66A3 , TAGLN , TIMP1 , TNFRSF12A , TOR4A , TSPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lte2 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADD3 , AMIGO2 , ANXA3 , ASCL1 , ATF3 , BCL2 , BCL2L11 , BHLHE41 , CA12 , CAP2 , CASP8 , CHN1 , CNN2 , COL9A3 , CRABP1 , DDX60 , DLC1 , DNAJB14 , EFEMP1 , ELF4 , ELOVL2 , FHL2 , GADD45A , GAL , GEM , GRB10 , GREB1 , H2AC6 , H4C8 , ID1 , IFI35 , IFI44L , IFIT1 , IFIT3 , ISG15 , JAG1 , KLF4 , LAMA3 , LGALS1 , LGALS3BP , MGP , MICB , MTCL1 , MYO10 , NMI , NOTCH1 , NRP1 , OAS3 , PARP12 , PCSK6 , PDLIM3 , PEG10 , PPM1E , PRSS23 , PSMB9 , PTBP2 , PTPRK , RAB31 , RNF6 , RPS6KA3 , SAMD9 , SLC16A7 , SLC7A11 , SP100 , SP110 , SVIL , SYTL2 , TAP1 , TENM1 , TM4SF1 , TSPO , UGCG , USP18 , ZNF273 , ZNF84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ACVR1 , ANXA1 , ARID5B , ASPH , ATXN1 , BBS12 , BCL3 , BCL6 , CC2D1B , CCDC71L , CCN3 , CDKN1A , CFL2 , CLDN1 , CLVS1 , CMTM3 , COL6A3 , COQ10B , CPEB2 , CREB5 , CSRNP1 , CYBRD1 , DOCK4 , DUSP1 , DUSP5 , DUSP8 , FAM177A1 , GASK1B , GBP3 , GDF15 , GJA1 , GLCE , GLIPR1 , GPR137B , GPR137C , H2AC6 , H2BC21 , H2BC4 , H3C12 , HBEGF , HECW2 , HMOX1 , HNMT , ICAM1 , IFI16 , IL10RA , IL1A , IL6ST , ITGB8 , JUN , KCNJ2 , KLF6 , LIMK1 , MAFF , MIR22HG , MMP1 , MTSS1 , NAMPT , NBEAL1 , NCEH1 , NFXL1 , NRP1 , NUAK1 , OSTM1 , OTUD1 , PHLDA1 , PID1 , PLAU , PPCS , PPP1R15A , PRTFDC1 , PTPRO , RAB12 , RASGRP3 , RHOB , RHOC , RIN2 , RIT1 , RTN1 , SAMD9L , SCG2 , SETBP1 , SGK1 , SLC7A11 , SQSTM1 , STAM2 , STC1 , TGIF1 , TLR6 , TTLL7 , TWF1 , UPP1 , USP53 , VSIR , VWA5A , WNT5A , ZEB2 , ZFP36 , ZFP36L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rps14 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADD2 , AGAP1 , AGFG2 , ATAD2 , ATP1B2 , BAG2 , BAG3 , C14orf132 , CCNB2 , CENPE , CLCN4 , COBLL1 , COLEC11 , CRMP1 , CYBRD1 , DBH , DDN , DLGAP5 , DYRK3 , E2F8 , ENG , EPB41 , ESPL1 , EXO1 , FICD , GAL , ID1 , INCENP , KANK2 , KIF15 , KIF20A , KIF2C , KIF5A , MACROD1 , MAMLD1 , MCM10 , MDM4 , MKI67 , MSH2 , MYBL2 , MYLIP , NCAPH , NEFH , NID2 , NMU , PBK , PC , PCSK7 , PKLR , POLD1 , PRC1 , RAP1GAP , RASIP1 , S100A3 , SH3TC2 , SLC29A1 , SLC29A2 , SPHK1 , SPTB , STEAP3 , STMN2 , SUV39H2 , TFAP2B , TGM2 , THEM6 , TLX2 , TMSB15A , TUBB2B , ZNF74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat Gds748 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , AQP3 , ASRGL1 , BAG3 , C3orf52 , CEBPB , COTL1 , CRYBG1 , DDAH1 , FAH , FAM3C , FZD7 , GCH1 , ITGA9 , MYB , NEDD9 , NPTX1 , PHLDA2 , PLEKHB2 , RUNX1 , SLC39A14 , SLC3A2 , SRPX , TP53I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P53 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC2 , ACTA2 , ADCY1 , AJAP1 , ARMC2 , CA12 , CASP1 , CDKN1A , CFI , CHGA , CPS1 , CTSL , CYFIP2 , DOCK2 , ECM1 , ELOVL2 , FAS , FBLN5 , FDXR , FRMD4B , GLDC , GLS , GPNMB , GPR137B , GREB1 , GSDME , HMOX1 , HOXD8 , HSPA2 , IFFO1 , IFI16 , IGFBP7 , IL1R1 , ITGA4 , KBTBD11 , KCNAB2 , L1CAM , LYST , MGLL , MITF , NAMPT , NAV3 , NCALD , NEFM , NID1 , NINJ1 , NRCAM , NSG1 , PDE4B , PLA2G4A , PLCB4 , PLXNC1 , PMEL , PTPRM , SGK1 , SLC16A4 , SLC24A5 , SLC6A15 , SOCS3 , SOX4 , ST3GAL5 , ST3GAL6 , ST8SIA1 , STAT6 , TAGLN3 , TNS2 , TP53TG1 , TRIM38 , TSPAN7 , VCAN , VIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.600 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ADCYAP1R1 , ANGPTL4 , ANPEP , ARL4C , ASIC4 , ASTN1 , BEX1 , BMP7 , C1QTNF1 , CALB1 , CDHR2 , CDK5R1 , CHGA , CHGB , CHRNA3 , COL26A1 , CTNNA2 , CTNND2 , CXCR4 , DBH , DCBLD2 , DLGAP2 , DNM3 , DNMBP , DOCK4 , DUSP4 , EFCAB6 , FNDC8 , GFAP , GLDC , GPR19 , GPR37 , HAS2 , HBEGF , HS3ST3B1 , HTR7 , IL13RA2 , INHBA , ITGA2 , KCNAB3 , KCNC1 , KCNH2 , KCNK3 , KIF5A , KIF5C , LIMCH1 , LMO3 , MGAT4A , MMD , MMP1 , MMP10 , MMP11 , NAP1L2 , NAV3 , NMNAT2 , NOL4 , NRCAM , NRP1 , NTRK3 , PCDH9 , PDE2A , PEG3 , PELI2 , PLA2G4C , PLAT , PLAU , PNMA2 , PTX3 , RREB1 , RTN1 , SATB1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SLCO4A1 , SLCO5A1 , SLIT1 , SNAP25 , SNAP91 , SORL1 , SOX9 , ST3GAL6 , STC1 , STX1A , SYT1 , TAGLN3 , TERT , TGM2 , TLR4 , TMEM158 , TRIB2 , TRIM36 , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P53 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADORA2B , AHR , AMPH , ANXA1 , APBB2 , AXL , BCAR3 , BCL10 , BIRC2 , CALB1 , CCN1 , CD24 , CDH13 , CDKN2A , CEMIP , CLTCL1 , CNR1 , COL3A1 , CRIM1 , CRYBG1 , CXADR , DKK1 , EFEMP1 , EGFR , ELF4 , F3 , FBLN2 , FHL2 , FOXN3 , GP1BB , IGFBP6 , IRF1 , ITGA2 , ITGB4 , KLF5 , KRT18 , LAMB2 , LOXL1 , LRIG1 , LTBP1 , MAFF , MEST , MMP1 , MYOF , NDC80 , NEBL , NMNAT2 , NMU , NR2F2 , OIP5 , OLFML2A , PLAU , PODXL , PPARG , PRDX2 , RBP1 , RRAS2 , SCG2 , SDC4 , SLIT2 , SMAGP , SOX9 , SPINT2 , SULF1 , SYNJ2 , TGFBI , TPBG , VASP , YAP1 , ZNF185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crx Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2 , BACH2 , BCL3 , C1QTNF6 , CAMK2B , CAPN12 , CD44 , CDKN1A , CEBPA , CEBPB , CEBPD , CHRNA3 , CHRNB4 , COL4A2 , DUSP16 , FKBP5 , FMN1 , FOXD1 , FRMD6 , GDAP1L1 , GFAP , GLIPR2 , HLA-B , INSM2 , KDELR3 , MAP3K8 , MYOCD , NFKB1 , NUPR1 , OSMR , PHOX2B , PLAT , PLEC , PLOD2 , RAI14 , S100A16 , S100A6 , SEL1L3 , SEMA5B , SH3BP4 , SOCS3 , SPSB2 , TAGLN2 , TECTA , TGM2 , TIMP1 , TLE1 , TMBIM1 , TMOD1 , TNFRSF12A , TUBB6</t>
   </si>
   <si>
     <t xml:space="preserve">Rb P107 Dn.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ABAT , ACTG2 , ASF1B , BEX2 , BGN , BLVRB , CCNF , CD248 , CDC45 , CDH11 , CDH2 , CDKN1C , CENPH , CENPK , CHAF1B , COL1A1 , COL1A2 , COL5A1 , COL6A1 , COL6A2 , DHFR , DNA2 , DUSP1 , E2F1 , E2F8 , EFS , ETHE1 , FANCA , FANCL , FBLN2 , FBLN5 , FBN1 , FEN1 , FKBP10 , FSTL1 , GINS4 , GTSE1 , H1-10 , HMGN2 , INCENP , KIF4A , LGALS3BP , LIG1 , LOXL1 , LYPD1 , MAD2L1 , MCM2 , MCM5 , MCM6 , MCM7 , MFGE8 , NCAPH , PAQR4 , PCNA , POLD1 , POLE , POLE2 , PRC1 , PRIM1 , PTMA , RBPMS2 , RFC2 , RFC3 , RFC5 , RPA3 , RRM1 , S100A4 , SRPX2 , STMN1 , TAGLN , TYRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordenonsi Yap Conserved Signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMOTL2 , ASAP1 , AXL , BIRC5 , CAVIN2 , CCN1 , CCN2 , CENPF , CRIM1 , DAB2 , DDAH1 , DLC1 , DUSP1 , DUT , FGF2 , FLNA , FSTL1 , GADD45B , GAS6 , GLS , HEXB , HMMR , ITGB5 , LHFPL6 , MDFIC , PDLIM2 , PMP22 , SCHIP1 , SERPINE1 , SLIT2 , STMN1 , TGFB2 , TGM2 , THBS1 , TNNT2 , TNS1 , TOP2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc V6.5 Up Early.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM21 , AHNAK , ANXA1 , ANXA2 , ANXA3 , ANXA5 , AQP3 , AXL , B2M , BCAN , BCL3 , BGN , BHLHE40 , C16orf74 , CADPS , CALD1 , CALML4 , CAPN2 , CAV1 , CAVIN1 , CAVIN2 , CCDC34 , CCDC80 , CCN1 , CCN2 , CDC42EP1 , CFB , COL1A1 , COL1A2 , COL4A1 , COL4A2 , CSRP1 , EMP1 , F2RL1 , FAP , FBLN2 , FBXO6 , FGF2 , FHL2 , GAP43 , GASK1B , GBP2 , GBX2 , GSN , HBEGF , HES7 , HTRA1 , IGFBP3 , IGFBP7 , INHBA , KIF18A , KLF4 , LAMC2 , LOX , LOXL1 , MGP , MYO7B , NID1 , NUPR1 , PARVA , PLAU , PLCL2 , PMP22 , S100A4 , S100A6 , SCARA3 , SERPINE1 , SLC8A3 , SMARCD3 , SOCS3 , STARD8 , SULT1E1 , TAGLN , TGFB1I1 , TIMP2 , TM4SF1 , TNC , TNFRSF12A , TRIM54 , TSHZ2 , TUBB6 , ZFP36L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raf Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCC3 , ACSL1 , ACSL4 , ANGPTL4 , ANKMY2 , ASPH , C1GALT1 , CAPN2 , CAST , CEBPD , CERK , CLDN1 , CORO1A , COTL1 , CREB3L2 , CRIM1 , CRISPLD2 , DHTKD1 , DUSP4 , EGFR , EPAS1 , ERAP1 , FERMT2 , FGF1 , GALNT12 , GATA2 , GCLM , GM2A , GPR37 , GRAMD2B , GRB10 , HACD1 , HBEGF , HEG1 , HSPA2 , IMPA2 , ITGA6 , ITGB6 , KCNN4 , KLF6 , L1CAM , LAMC1 , MICAL2 , MORC4 , MSX2 , MTMR11 , MYCL , NDC80 , NEDD4 , NFE2L3 , NMI , NMT2 , NMU , NPC2 , NUAK1 , OPTN , P3H2 , PARVA , PDE4D , PEG10 , PHYH , PKD2 , PLS3 , PPARG , PRPS1 , PSMB10 , PSMB9 , PXDC1 , PYGL , RASL11B , RCAN1 , RNF144A , RRAS2 , SAT1 , SCARA3 , SCG2 , SDCBP , SEPTIN6 , SGCE , SLC31A2 , SMAGP , SYNE2 , TBC1D2 , TCIM , TFPI2 , TLE2 , TMSB15B , TNFAIP8 , TNNT1 , UGT8 , UPP1 , VTN , XYLT1 , ZNF331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lte2 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMIGO2 , ANXA3 , ASCL1 , BCL2 , BCL2L11 , BHLHE41 , BST2 , CA12 , CAP2 , CASP8 , CAV1 , CHN1 , CNN2 , COL9A3 , CRABP1 , DDX60 , DLC1 , DNAJB14 , DSCAM , EFEMP1 , ELF4 , ELOVL2 , EPB41L2 , FHL2 , GADD45A , GAL , GEM , GFRA1 , GRB10 , GREB1 , H2AC6 , H4C8 , HERC6 , HES1 , ID1 , IFI35 , IFI44 , IFI44L , IFI6 , IFIH1 , IFIT1 , IFIT3 , IGF1R , IRF9 , ISG15 , JAG1 , JAK2 , KLF4 , LAMA3 , LAMP3 , LGALS1 , LGALS3BP , MATN2 , MGP , MICB , MOCOS , MTCL1 , MYO10 , NMI , NMRK1 , NOTCH1 , NRP1 , OAS3 , PARP12 , PCSK6 , PDLIM3 , PEG10 , PPM1E , PRSS23 , PSMB9 , PTBP2 , PTPRK , RAB31 , RNF6 , RPS6KA3 , SAMD9 , SLC16A7 , SLC7A11 , SP100 , SP110 , SVIL , SYTL2 , TAP1 , TDRD7 , TENM1 , TFPI2 , TM4SF1 , TSPO , UGCG , USP18 , ZNF107 , ZNF273 , ZNF43</t>
+    <t xml:space="preserve">ABAT , BEX2 , BGN , BLVRB , CD248 , CD81 , CDKN1C , CENPH , COL1A1 , COL5A1 , COL6A1 , COL6A2 , DHFR , DNA2 , DUSP1 , E2F1 , E2F8 , ETHE1 , FANCL , FBLN2 , FBLN5 , FBN1 , FKBP10 , FSTL1 , GTSE1 , H1-10 , HMGN2 , INCENP , KIF4A , LGALS3BP , LIG1 , LOXL1 , LYPD1 , MAD2L1 , MCM2 , MCM6 , MCM7 , MFGE8 , NCAPH , PAQR4 , PCNA , POLD1 , POLE , PRC1 , PRIM1 , PTMA , RBPMS2 , S100A4 , STMN1 , TAGLN</t>
   </si>
   <si>
     <t xml:space="preserve">E2f3 Up.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ABHD15 , ANKRD18A , ATAD2 , BRI3BP , C11orf96 , CBX2 , CCP110 , CDK19 , CDK5R1 , CDKN1C , CHRDL2 , CHST2 , CHST7 , CSPG5 , DDAH1 , DHRS13 , DTL , EEF1A2 , EFS , EGR2 , EML6 , ENO2 , FAM222A , FAM43B , FANCA , FAXC , FEN1 , FGFR3 , FOXD1 , GAD1 , GCH1 , GINS1 , GKAP1 , GPR137C , HSPA2 , IL17RB , INA , JPH1 , KCNA6 , L3MBTL3 , MANEAL , MBOAT1 , MEX3B , MICB , MYB , NAT8L , NEFL , NGEF , NPAS1 , NPTX1 , NUDT22 , PCNA , PCOLCE2 , PDIA2 , PDXP , PEG10 , PGAP4 , PLSCR4 , PLXND1 , POLE , POLE2 , PTCH1 , RASGRP1 , RECQL4 , REEP1 , RTN4R , SAMD1 , SBK1 , SEPTIN3 , SIX5 , SLC27A2 , SLC6A2 , SOWAHA , SYN1 , SYNM , TAF5 , TIAM1 , TLCD1 , TLE2 , TMEM158 , TMEM97 , TP53I13 , TPPP , UBE2QL1 , UGT8 , WNT9A , ZDHHC23 , ZFP30 , ZNF367 , ZNF483 , ZNF703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erbb2 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCC3 , ABCG1 , AKR1C2 , ANGPTL4 , ANKMY2 , ANXA6 , APLP1 , AQP3 , ASPH , ATXN1 , B3GALT4 , BCAM , BCL3 , BCL6 , BMPR1B , C1orf115 , CA8 , CAPN2 , CAPN5 , CAST , CEMIP , CREB3L2 , CRLF1 , CXADR , CXCL8 , CXCR4 , DAB2 , DOCK10 , DRAM1 , DUSP4 , EDN1 , ENO2 , EPAS1 , EPHX1 , FMO5 , GALNT12 , GDF15 , GNAI2 , GRAMD2B , HSPA2 , IL1R1 , ITGB4 , ITGB6 , KCNMA1 , KCNN4 , KIAA0513 , KRT7 , KRT81 , LAMB2 , LIMCH1 , LMO3 , LOXL1 , MALL , MAOA , METRN , MGAT4A , MSX2 , MUC1 , MXRA7 , MYO1D , NIBAN1 , NOTCH3 , NPC2 , P4HA2 , PACS1 , PAPSS2 , PCDH1 , PDE4B , PDE4D , PGPEP1 , PLEKHB1 , PLPP1 , PLPP2 , PPP1R3C , PRPS1 , S100A6 , SAT1 , SDCBP , SLC2A10 , SOX9 , SPAG4 , SPTBN2 , ST8SIA4 , TENT5C , THEM6 , TNNT1 , TPK1 , TSPAN1 , VASP , WIPI1 , ZNF365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P53 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM , ADORA2B , AHR , AMPH , ANXA1 , APBB2 , AXL , BCAR3 , BCL10 , CALB1 , CCN1 , CD24 , CDH11 , CDH13 , CDKN2A , CDKN2D , CEMIP , CFB , CLTCL1 , CNR1 , COL13A1 , COL1A2 , CORO2A , CRIM1 , CRYBG1 , CST6 , CXADR , DHRS3 , DKK1 , EFEMP1 , EGFR , ELF4 , ENPP4 , F3 , FBLN2 , FHL2 , GLUL , IGFBP6 , IRF1 , ITGA2 , ITGB4 , KLF5 , KRT15 , KRT18 , LAMB2 , LAMP3 , LOXL1 , LRIG1 , LTBP1 , MAFF , MEST , MMP1 , MYCL , MYOF , NDC80 , NEBL , NMNAT2 , NMU , NR2F2 , OIP5 , OLFML2A , PLAU , PLCE1 , PODXL , PPARG , PPL , PRDX2 , PTK7 , RAMP1 , RBP1 , RNASE4 , RRAS2 , SCG2 , SDC4 , SH3GLB1 , SLIT2 , SMAGP , SOX9 , SPINT2 , SULF1 , SYNJ2 , TGFBI , TJP2 , TOX3 , TPBG , TSPAN8 , UGT8 , USP1 , VASP , YAP1 , ZNF185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cahoy Astroglial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTA2 , ADGRG6 , ANXA1 , ANXA4 , ATOH8 , ATP8A1 , BST2 , C1QTNF1 , CALHM5 , CASP1 , CD109 , CLCN4 , CNN1 , COL5A1 , COL8A1 , CTTN , DYSF , EMP3 , FAS , FBLN5 , GLIPR2 , GPHN , GPNMB , IGFBP3 , ITGBL1 , KLHL21 , LGALS3 , LOX , LOXL2 , LPIN3 , LTBP2 , MORC4 , MSN , MYOF , NUAK2 , PCDH17 , PHACTR3 , PRSS23 , PSRC1 , PTRH1 , RASSF4 , SEMA3B , SERPINE1 , SLC66A3 , TAGLN , TIMP1 , TMEM37 , TNFRSF12A , TOR4A , TRAF1 , TSPO</t>
+    <t xml:space="preserve">ABHD15 , ANKRD18A , ATAD2 , ATP6V1E1 , C11orf96 , CBX2 , CDK19 , CDK5R1 , CDKN1C , CEBPA , CHST1 , CHST7 , DDAH1 , DHRS13 , DTL , EEF1A2 , EGLN1 , EML6 , ENO2 , FAM222A , FAM43B , FAXC , FGFR3 , FOXD1 , GCH1 , GKAP1 , GPR137C , HSPA2 , INA , JPH1 , L3MBTL3 , MANEAL , MBOAT1 , MICB , MYB , NAT8L , NGEF , NPAS1 , NPTX1 , PCNA , PCOLCE2 , PDIA2 , PEG10 , PLXND1 , POLE , PTCH1 , PXMP2 , RAB26 , RECQL4 , REEP1 , RTN4R , SAMD1 , SBK1 , SEPTIN3 , SIX5 , SLC6A2 , SYN1 , TAF5 , TIAM1 , TLCD1 , TM6SF1 , TMEM158 , TMEM97 , TP53I13 , TPPP , UBE2QL1 , ZFP30 , ZNF483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lef1 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ARC , ARID3B , AXL , BMP7 , C14orf132 , CDKN2A , CHGB , CHST11 , COL6A1 , COL9A3 , CRABP2 , CXCR4 , CYBRD1 , DCLK1 , DKK1 , DLL3 , ELK3 , FJX1 , FLNC , FN1 , FNBP1 , FOSL1 , GATA3 , GNG4 , HAS2 , HSPA1A , IGFBP6 , IGFBP7 , IL11 , KCNN4 , L1CAM , LGALS1 , LOXL1 , LTBP2 , MAOA , MSN , NELL2 , NMNAT2 , NR3C1 , NRIP3 , NTSR1 , PCSK5 , PDGFA , PDZD2 , PELI2 , PHLDA3 , PLTP , PRPH , PRPS1 , PTPRN2 , RAI2 , RAMP2 , RBP1 , S100A2 , S100A3 , S100A4 , SCN5A , SERPINE1 , SLC2A3 , SLIT1 , STRA6 , TGM2 , TMEM158 , TMOD1 , TUBB2B , VIM , WNT5A , WWC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.300 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ANGPTL4 , ANPEP , ASIC4 , ASTN1 , BEX1 , CALB1 , CDK5R1 , CHGA , CHGB , COL26A1 , CTNNA2 , DBH , DCBLD2 , DNM3 , DOCK4 , EFCAB6 , FNDC8 , GLDC , GPR19 , HAS2 , HTR7 , IL13RA2 , ITGA2 , KCNH2 , KIF5A , KIF5C , LMO3 , MMP1 , MMP11 , NAP1L2 , NAV3 , NOL4 , NRCAM , PDE2A , PEG3 , PTX3 , RREB1 , RTN1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SLCO5A1 , SNAP25 , SNAP91 , SORL1 , ST3GAL6 , STC1 , SYT1 , TERT , TRIB2 , TRIM36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tgfb Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCG1 , ACSBG1 , ADAM22 , ANK1 , ATF3 , BCOR , BHLHE40 , CCN2 , CDKN2B , CHST11 , CHST3 , CLCF1 , CYP2J2 , DACT1 , DDC , DLC1 , DPY19L1 , EDN1 , ELK3 , ELL2 , F2RL1 , FERMT2 , FGF1 , FOXD1 , GADD45B , IL11 , IRS1 , ITGA5 , JUN , KCNN4 , KLF4 , KLF7 , LARP6 , LIF , LIPG , LTBP2 , LYPD1 , MMD , NGF , PAIP2B , PDGFA , PHLDB1 , PIK3CD , PPP1R13L , PVRIG , PXDC1 , RHOB , RRAD , S100A3 , SCHIP1 , SEC14L2 , SGK1 , SLCO2A1 , SMOX , SMTN , SMURF2 , SPHK1 , SPSB1 , SSBP3 , STC1 , TAGLN , TNFAIP8 , TUBB4A , UBL3 , YIPF5 , ZFP36L1</t>
   </si>
   <si>
     <t xml:space="preserve">Rps14 Dn.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ACTA2 , ADA , ADAMTS6 , ADRA2A , ANXA3 , ANXA6 , ARL4C , ATP8B1 , BCL6 , BIRC3 , BST1 , C3AR1 , CALB1 , CAPG , CASP1 , CCL2 , CCNA1 , CDCP1 , CDKN1A , COLEC12 , CPM , CRIM1 , CROT , CTSH , CTSS , CXCL8 , DCN , DNAJC22 , EMP1 , ENPP2 , EPS8L2 , EVI2A , FBN2 , FLVCR2 , FUCA1 , GDF15 , GJA1 , GNAZ , GNB5 , GPNMB , GPR137B , HLA-DMA , ICAM3 , IFI16 , IGFBP7 , IL1B , IL1RAP , JAG1 , KBTBD11 , KYNU , MAF , MDFIC , MX1 , MX2 , PADI2 , PDE4D , PDGFA , PID1 , PLAU , PLK2 , PTPRG , RAB31 , RASGRP3 , RBM47 , RGL1 , RHOB , RIN2 , SCN3A , SDC4 , SEMA3D , SH3GL3 , SIRPA , SLC31A2 , SMAD3 , SPP1 , SPTLC3 , ST3GAL6 , STX3 , TAC3 , TGFBI , TIGAR , TNFRSF9 , TRIM22 , TRIM36 , ZMAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lef1 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , AKAP12 , ANO1 , ARC , ARG2 , ARHGAP4 , ARID3B , AXL , BMP7 , C14orf132 , CARD9 , CBS , CD302 , CDKN2A , CHGB , CHST2 , COL6A1 , COL9A3 , CRABP2 , CXCR4 , CYBRD1 , DKK1 , DLL3 , DNAJC6 , EGR2 , ELK3 , EMP1 , EMP3 , FJX1 , FLNC , FN1 , FNBP1 , FOSL1 , GATA3 , GNG11 , GNG4 , HAS2 , IGFBP6 , IGFBP7 , IL11 , KCNG1 , KCNN4 , KRT81 , L1CAM , LGALS1 , LOXL1 , LTBP2 , MAOA , MSN , NELL2 , NMNAT2 , NR3C1 , NRIP3 , NTSR1 , PDGFA , PDZD2 , PELI2 , PHLDA3 , PLTP , PRPH , PRPS1 , PTPRN2 , RAI2 , RAMP2 , RBP1 , ROR2 , RPP25 , S100A2 , S100A3 , S100A4 , SCN5A , SERPINE1 , SLC2A3 , SLC35G2 , SLC43A3 , SLIT1 , STRA6 , TGM2 , TH , TMEM158 , TMEM47 , TMOD1 , TUBB2B , VIM , WNT5A , WWC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Nomo Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ACP5 , ACVR1 , ARID5B , ARL4C , ASPH , ATG101 , BBS12 , BCL3 , BCL6 , C3AR1 , C5AR1 , CAMK2D , CC2D1B , CCDC71L , CFL2 , CLVS1 , CNIH3 , COL6A3 , COQ10B , CREBRF , CSRNP1 , DAB2 , DDIT4L , DOCK4 , DUSP1 , DUSP5 , EGR2 , ELK4 , EMP1 , EPAS1 , FABP4 , FAM114A1 , FBXL13 , FBXO32 , FOS , GALNT4 , GASK1B , GBP3 , GCNT2 , GDF15 , GJA1 , GLIPR1 , GNG11 , GPNMB , GPR137B , H2BC4 , HECW2 , HNMT , ICAM1 , IER3 , IFI16 , IL1A , IL1B , IL1R1 , IL6ST , IL7R , IRS1 , JUN , KCNJ2 , KDELR3 , KIFC3 , KITLG , KLF6 , KYNU , LACC1 , LAMB3 , LIMK1 , MAFF , MAP3K8 , MEIS3P1 , MERTK , MGAT4B , MIR22HG , MMP1 , MMP10 , MTSS1 , NCEH1 , NEAT1 , NRP1 , NUAK1 , OSTM1 , OTUD1 , PGBD5 , PHLDA1 , PID1 , PINLYP , PLAU , PPCS , PPP1R15A , PTBP2 , PTGFRN , PTPN3 , PTX3 , RASGRP3 , RHOB , RIN2 , RIT1 , RNASEL , RND3 , SAMD9L , SCG2 , SDC4 , SEMA4D , SETBP1 , SQSTM1 , ST3GAL1 , STAM2 , STC1 , STK17B , TGIF1 , TLR6 , TWF1 , UEVLD , UPP1 , USP53 , VWA5A , WNT5A , ZEB2 , ZFP36 , ZFP36L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2f1 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4GALT , ACKR3 , ADARB1 , AJUBA , AMPD3 , ANGPTL4 , ANXA1 , ANXA4 , ANXA8 , APBB2 , APC2 , AVPI1 , BAG3 , BCL6 , CALML4 , CAPN2 , CAVIN2 , CCL2 , CHRNA7 , CREBRF , CRIP2 , CSF1 , DAB2 , EFNA4 , EPS8 , EVI2A , F3 , FAS , FCHO1 , GADD45A , GBP2 , GFRA1 , GHR , HES6 , HLA-B , IFIT2 , IL1R1 , IL6ST , ITPR2 , KLF2 , LIMA1 , LRIG1 , MMP24OS , MX1 , MYC , NEAT1 , NFKB1 , NFKBIZ , NOTCH2 , NPR1 , PAK3 , PHLDA1 , PLAT , PLK2 , PLXND1 , POLD4 , PTGS1 , PTGS2 , RAB11FIP5 , RAB9A , RALGDS , RAP2B , RUNX2 , SASH1 , SEC23A , SERTAD1 , SIX5 , SNAI1 , STAT3 , STAT6 , STOM , STX4 , TCF4 , TGFB1I1 , TGFB3 , TGM2 , TNXB , TRIB3 , UBE2H , UNC93B1 , VCAN , ZC3H12A , ZFR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat Gds748 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP3 , ASRGL1 , BAG3 , C3orf52 , CEBPB , COTL1 , CRYBG1 , DDAH1 , DYNC1I1 , FAH , FAM3C , FZD7 , GAD1 , GADD45G , GCH1 , GCNT1 , ITGA9 , MSX2 , MYB , NEDD9 , NPTX1 , PDE4D , PHLDA2 , PLEKHB2 , RUNX1 , SLC3A2 , SRPX , TP53I3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.600 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , ADCYAP1R1 , ADGRA2 , ANGPTL4 , ANK3 , ANO1 , ARHGAP24 , ARL4C , ASIC4 , ASTN1 , ATP1A2 , BEX1 , BMP7 , C1QTNF1 , CALB1 , CDK5R1 , CEL , CFAP69 , CHGA , CHGB , CHRNA3 , COL26A1 , CTNNA2 , CTNND2 , CXCR4 , CYP27B1 , DBH , DCBLD2 , DNM3 , DNMBP , DOCK4 , DUSP4 , DYNC1I1 , EFCAB6 , EMP1 , EVI2A , EXOC6B , GLDC , GNG11 , GPR19 , GPR37 , HAS2 , HBEGF , HS3ST3B1 , HTR7 , INHBA , ITGA2 , ITGBL1 , KCNAB3 , KCNC1 , KCNH2 , KCNJ8 , KCNK3 , KIF5A , KIF5C , LDB3 , LIMCH1 , LMO3 , MGAT4A , MMD , MMP1 , MMP10 , MMP11 , MMP9 , NAP1L2 , NAV3 , NME5 , NMNAT2 , NOL4 , NRCAM , NRP1 , NTRK3 , PCDH9 , PDE2A , PEG3 , PELI2 , PLA2G4C , PLAT , PLAU , PNMA2 , PTGS2 , PTX3 , RBP4 , RREB1 , RTN1 , RUBCNL , SATB1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SLCO4A1 , SLCO5A1 , SLIT1 , SNAP25 , SNAP91 , SOX9 , SPP1 , ST3GAL6 , STC1 , STX1A , TAGLN3 , TBX3 , TEC , TERT , TFPI , TGM2 , TLR4 , TMEM158 , TOX3 , TRIB2 , TRIM36 , UGT8 , VEGFC , ZDHHC11</t>
+    <t xml:space="preserve">ACTA2 , ADAMTS6 , ANPEP , ANXA3 , ANXA6 , ARL4C , ATP8B1 , BCL6 , BST1 , CACNB4 , CALB1 , CASP1 , CDCP1 , CDKN1A , CRIM1 , CROT , CTSS , CXCL8 , CYFIP2 , DCN , DNAJC22 , ENPP2 , FBN2 , FLVCR2 , FUCA1 , GDF15 , GJA1 , GNAZ , GNB5 , GPNMB , GPR137B , IFI16 , IGFBP7 , IL1RAP , JAG1 , KBTBD11 , MAF , MX1 , PADI2 , PDGFA , PID1 , PLAU , PROM1 , PTPRG , PTPRO , RAB31 , RASGRP3 , RBM47 , RGL1 , RHOB , RIN2 , SCN3A , SDC4 , SEMA3D , SH3GL3 , SIRPA , SLC31A2 , SORL1 , ST3GAL6 , STX3 , TAC3 , TGFBI , TIGAR , TM6SF1 , TRIM36 , ZMAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtor Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ACKR3 , C1QTNF4 , C1R , C2 , COQ8A , CSDC2 , CSGALNACT2 , CTNS , DNASE2 , DNMBP , DUSP1 , EFEMP2 , FAH , FANK1 , FBXO32 , H1-10 , HSPA1A , HTRA1 , ISL1 , KCNC1 , KCNK3 , KCNQ1 , KLF2 , LTBP1 , MED12L , METTL27 , MYC , MYCN , NCAM1 , NELL2 , NFXL1 , OLFML3 , OSGIN1 , OSMR , PALD1 , PDE4B , PDE9A , PDGFA , PDIA5 , PDLIM3 , PLTP , PPP1R3C , PRSS23 , PTGIS , RBP1 , RRM2B , S1PR3 , SASH1 , SCARA3 , SIX5 , SLC12A4 , SLC2A4 , SLC39A13 , SLC44A1 , STX1A , SULT1E1 , SYN2 , THBS3 , TNIP2 , TNS2 , TSPAN4 , XDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tgfb Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADAMTS1 , ANGPTL4 , ARID5B , AVPI1 , BCL6 , BDKRB2 , CAVIN2 , CHST7 , CITED2 , COL4A1 , CXADR , DUSP4 , ENTPD7 , FAM13A , FHL3 , FNDC3B , FRMD4B , FSTL3 , GATA3 , GCH1 , GPR39 , GPRC5C , HS3ST1 , HSF2 , HSPG2 , ID1 , IFIT1 , IFIT2 , IFIT3 , IRF1 , ISL1 , JADE2 , KIF18A , MIR22HG , MITF , MN1 , MPPED2 , MRM1 , NPAS1 , NR2F2 , NUDT18 , NUDT6 , PAQR5 , PCBP3 , PGBD5 , PIK3R3 , PLXNA2 , PTCH1 , PTX3 , RAB33A , RAB38 , RAI2 , RBM47 , RGL1 , SERTAD2 , SH3TC2 , SKP2 , SLC30A1 , SMAD7 , TMCC2 , TRPM4 , ZNF292 , ZNF395 , ZNF74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pten Dn.v2 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3 , ALDH1A3 , ANGPTL4 , ANXA3 , ARHGDIB , ARL4C , ARVCF , ATP2B2 , CASP4 , CLIP4 , CLPB , CPA4 , CSF1 , CUEDC1 , CXCL8 , GNA14 , HSPB7 , HSPB8 , IL4R , IL7R , JUN , LAMA3 , LIPG , LOXL2 , MIR22HG , NAALAD2 , NAV3 , NID2 , NNAT , NOL4 , OSGIN1 , PC , PCSK7 , PLAU , RHBDF1 , RTN1 , SAMD4A , SATB1 , SECTM1 , SLC2A4 , SLC66A3 , SPOCK1 , THBS4 , TIGAR , TMEM127 , TP53I3 , TRIB2 , UTRN , VAMP5 , ZMAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoxa9 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTA2 , ADAM9 , AGTPBP1 , ANKRD46 , ARHGAP26 , ARL4C , ATXN1 , BST1 , COL6A3 , COQ10B , CSPG4 , CTSL , CXCL8 , CYFIP2 , CYLD , DYNLT3 , FAM98A , FAS , FCGRT , FDXR , FNDC3B , FUCA1 , GADD45A , GALNT7 , GDF15 , GLIPR1 , GNS , GPR137B , H2AC6 , H2BC9 , IER5 , IFFO1 , IFI16 , IL10RA , IL13RA1 , ISG15 , KLF4 , MYOF , NAGK , OSTM1 , OTULINL , PARP12 , PIK3R3 , RBM47 , SCHIP1 , SCPEP1 , SERPINB8 , SLC22A18 , SLC22A4 , SLC30A1 , SLC35D2 , SLC46A3 , SORL1 , ST3GAL6 , TAX1BP3 , THBS4 , TIGAR , TP53I3 , TP53TG1 , TRPM4 , TSPOAP1 , TWF1 , UGGT2 , VCAN , ZMAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.50 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL4 , CALB1 , CHGB , DOCK4 , GLDC , HTR7 , IL13RA2 , ITGA2 , KIF5C , LMO3 , MMP11 , NRCAM , PEG3 , RREB1 , SCG3 , SIGLEC15 , SNAP25 , SNAP91 , ST3GAL6 , STC1 , TERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Skm Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL6 , ACTA2 , ANXA1 , ARHGAP42 , ARID5B , ASPH , BBS12 , BCL3 , CALHM2 , CCN3 , CDKN1A , CDKN1C , CFL2 , CLDN1 , CMTM3 , CPEB2 , CREB5 , CYBRD1 , DNAJB4 , DUSP1 , DUSP5 , DUSP8 , ERRFI1 , EVI5 , FAM177A1 , GBP2 , GBP3 , GDPD1 , GLIPR1 , GPR137B , GPR137C , H2AC6 , H2BC21 , H2BC4 , H3C12 , H4C8 , HBEGF , HECW2 , HMOX1 , IFI16 , IL10RA , IL15 , IL1A , IRF1 , ITGB8 , KCNJ2 , KLF6 , LGALS1 , LRRC37A2 , MAP2 , MIR22HG , MPPED2 , MYEF2 , NAMPT , NBEAL1 , NFKBIZ , NFXL1 , NMNAT1 , PALLD , PHLDA1 , PID1 , PLAU , PLXNB2 , PPCS , PRTFDC1 , PTPRM , PTPRO , RAB7B , RASGRP3 , RHOB , RHOC , RIT1 , RTN1 , SETBP1 , SGK1 , SH2B3 , SLC7A11 , SQSTM1 , STAM2 , STOX2 , TGFB1I1 , TK2 , TLR6 , TMTC3 , TTLL7 , TWF1 , UPP1 , VSIR , ZFP36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atf2 S Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA8 , ABCC3 , ADAM22 , ADARB1 , ANGPTL4 , BMP6 , BMPR1B , CEMIP , CLGN , CLMN , COBLL1 , COL11A1 , COL7A1 , CRIP2 , CRLF1 , DNAJC12 , EFEMP1 , ENO2 , EVC , FBLN2 , FGF7 , GALNT12 , GAS1 , GCH1 , GPRASP1 , GPRC5C , IL1R1 , IL1RAP , IL4R , ITPR1 , KBTBD11 , KCNAB2 , KRT8 , LAMA2 , MN1 , MYO1D , NFIB , NGF , OSMR , PADI2 , PCSK7 , PDLIM3 , PID1 , PLAAT3 , PNMA2 , POLE , PTGER2 , PTGIS , SDC3 , SERPINB7 , SGCG , SIK2 , SLC12A8 , SLC4A2 , SNCAIP , SORBS1 , SPINT2 , ST3GAL6 , STMN2 , TENM4 , THOC6 , TPD52 , VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snf5 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL4 , C1QTNF1 , CACNB4 , CARD10 , CBR3 , CD99L2 , CDH10 , CDKN2A , CELF4 , CHODL , CNTN1 , CRMP1 , CYP7B1 , DSG2 , EFEMP1 , ENO3 , FADS3 , FAH , FBLIM1 , FOXD1 , IL11 , IL13RA2 , ITGA3 , IVL , KCNAB1 , KIRREL1 , LMOD1 , LOXL4 , MALAT1 , MGST2 , MMP10 , MMP3 , MYLK , NFKBIZ , NIPAL2 , NPR1 , NPR3 , NSG1 , OTUD7A , P2RX5 , PAPPA , PCOLCE2 , PTPRK , PTPRVP , RAG2 , RFX3 , RGS16 , RRAD , SH3RF1 , SLC16A3 , SNCA , SPEG , STAR , SYTL2</t>
   </si>
   <si>
     <t xml:space="preserve">Prc2 Ezh2 Up.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">AATK , ABLIM3 , ADGRG1 , AHNAK2 , ANGPTL4 , ANKRD46 , ARL4C , ASPN , ATXN1 , B3GALT4 , B4GALNT1 , C3orf52 , CARD9 , CCDC68 , CDCP1 , CDH13 , CFAP69 , CLIP1 , CNIH3 , COL13A1 , CORO2B , CROT , CXCL8 , DCBLD2 , DNAJC12 , DUSP3 , DUSP8 , EDN1 , ERAP2 , F2RL1 , FLVCR2 , FOLR3 , FXYD6 , GPM6B , GPR37 , HBEGF , HS3ST3A1 , IFI44 , IL33 , IL6R , ITGA2 , KIAA0513 , KLF11 , KLF4 , KYNU , L1CAM , MALL , MAN2A1 , MCTP1 , MMP10 , MTHFD2L , NOVA1 , NPAS2 , NTSR1 , OSGIN1 , OSTM1 , PAMR1 , PAQR5 , PCBP3 , PCDH9 , PDGFA , PIK3CB , PPP2R1B , PRKG2 , PTBP2 , PTHLH , PTPRB , RGS16 , SETBP1 , SHISAL1 , SLC2A3 , SLC5A7 , SLC6A15 , SRPX2 , TBC1D19 , TMEM100 , TOR4A , TSPAN7 , TTLL7 , TUB , UBE2O , VSNL1 , VWA5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ACVR1 , ADM , ANXA1 , ARID5B , ASPH , ATXN1 , BBS12 , BCL3 , BCL6 , C5AR1 , CC2D1B , CCDC71L , CCN3 , CD101 , CD36 , CDKN1A , CFL2 , CLDN1 , CLVS1 , CMTM1 , CMTM3 , CNIH3 , COL6A3 , COQ10B , CPEB2 , CREBRF , CSRNP1 , CYBRD1 , DOCK4 , DUSP1 , DUSP5 , DUSP8 , EGR1 , EGR2 , EMP1 , FABP4 , FAM177A1 , FOS , GALNT4 , GASK1B , GBP3 , GDF15 , GJA1 , GLCE , GLIPR1 , GNG11 , GPR137B , GPR137C , H2AC6 , H2BC21 , H2BC4 , HBEGF , HECW2 , HNMT , ICAM1 , IFI16 , IL1A , IL1B , IL6ST , IRF9 , ITGB8 , JUN , KCNJ2 , KITLG , KLF6 , KYNU , LIMK1 , MAFF , MEIS3P1 , MIR22HG , MMP1 , MTSS1 , NBEAL1 , NCEH1 , NFXL1 , NRP1 , NUAK1 , OSTM1 , OTUD1 , PHLDA1 , PID1 , PLAU , PPCS , PPP1R15A , PRTFDC1 , RASGRP3 , RHOB , RHOC , RIN2 , RIT1 , RND3 , RNF141 , RTN1 , SAMD9L , SCG2 , SETBP1 , SLC38A6 , SLC7A11 , SQSTM1 , STAM2 , STC1 , TFPI , TFPI2 , TGIF1 , TLR6 , TP53INP1 , TTLL7 , TWF1 , UPP1 , USP53 , VSIR , VWA5A , WNT5A , ZEB2 , ZFP36 , ZFP36L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P53 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , ABCC2 , ACP5 , ACTA2 , ADA , ADCY1 , AJAP1 , ARMC2 , BCHE , CA12 , CAPN3 , CASP1 , CDKN1A , CFI , CHGA , CPS1 , CRYAB , CTSL , DOCK2 , ECM1 , ELOVL2 , FAS , FBLN5 , FDXR , FRMD4B , GAS7 , GFRA1 , GLDC , GLS , GPNMB , GPR137B , GPRC5B , GREB1 , GSDME , HOXD8 , HSPA12A , HSPA2 , IFI16 , IGFBP7 , IL1R1 , ITGA4 , KBTBD11 , KCNAB2 , KCNJ8 , L1CAM , LYST , MATK , MGLL , MITF , NAV3 , NCALD , NEFL , NEFM , NID1 , NINJ1 , NR4A1 , NRCAM , NSG1 , PDE1A , PDE4B , PMEL , PTPRM , RENBP , RHOQ , SLC16A4 , SLC6A15 , SOCS3 , SOX4 , SPP1 , ST3GAL5 , ST3GAL6 , ST8SIA1 , STAT6 , STOM , TAGLN3 , TFPI2 , TNS2 , TP53TG1 , TRIM22 , TRIM38 , TSPAN7 , VCAN , VIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.df.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADVL , ADGRE5 , AKAP12 , AKR1C3 , ANKRD46 , ASPH , AURKB , BCL2L1 , BCL3 , BCL6 , BORA , CDKN2B , CHRNA5 , COL6A3 , CORO1A , CRYZ , CUX2 , CXCL8 , DKK1 , DLGAP5 , DPYD , DPYSL2 , DSN1 , E2F8 , EHBP1L1 , ELK3 , EMP3 , FUT8 , G6PD , GCH1 , GNG11 , HS3ST3A1 , HSD17B2 , HSPA2 , IFI35 , IFI44 , IFI44L , IFIT1 , INHBA , INPP4B , IRF9 , JAK2 , LGALS3BP , LOXL2 , MAP3K6 , MMP1 , MVP , NAT1 , NRP1 , PDLIM2 , PID1 , PITPNC1 , PLAT , PLAU , PLCH2 , PLIN3 , PLPP2 , PROCR , PTPRG , PXDN , RAC2 , RETSAT , REXO5 , RPS6KA5 , RRAD , SERPINE1 , SLC22A4 , SLC2A10 , SMARCD3 , SMYD3 , SPAG4 , SRPX , STX4 , SUGCT , TFPI2 , TLR2 , TM4SF1 , TMEM158 , TP53I3 , VCAN , VEGFC</t>
+    <t xml:space="preserve">AATK , ABLIM3 , AHNAK2 , ALDH1A3 , ANGPTL4 , ANKRD46 , ANPEP , ARL4C , ATXN1 , C3orf52 , CDCP1 , CDH13 , CLIP1 , CORO2B , CROT , CXCL8 , DCBLD2 , DNAJC12 , DUSP3 , DUSP8 , EDN1 , ERAP2 , F2RL1 , FLVCR2 , FXYD6 , GPM6B , GPR37 , HBEGF , HS3ST3A1 , IL13RA2 , IL6R , ITGA2 , KIAA0513 , KLF4 , L1CAM , MAN2A1 , MMP10 , MTHFD2L , NOVA1 , NPAS2 , NTSR1 , OSGIN1 , OSTM1 , PAMR1 , PAQR5 , PCBP3 , PCDH9 , PDGFA , PPP2R1B , PTBP2 , PTHLH , RGS16 , SETBP1 , SHISAL1 , SLC2A3 , SLC35D2 , SLC6A15 , ST6GAL1 , TBC1D19 , TOR4A , TSPAN7 , TTLL7 , TUB , VWA5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lte2 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC3 , ANXA6 , AOX1 , AQP3 , ASPH , ASRGL1 , BMP7 , CDKN3 , CEMIP , CHST11 , CLIC3 , CLMN , CREB3L2 , CXCR4 , CYFIP2 , DAB2 , DPYSL2 , DRAM1 , DUSP4 , EDN1 , EHD3 , EPAS1 , EPHX1 , FERMT2 , GALNT12 , GCLM , GLTP , GNA14 , HSD17B14 , IL1R1 , MAOA , MGAT4A , NOVA1 , NPC2 , NUCB2 , ORAI3 , P4HA2 , PBK , PCDH9 , PLCB4 , PLPP2 , PPFIA3 , PPP1R3C , PROS1 , PRPS1 , PSTPIP2 , RAB27A , RAB29 , RCAN1 , REEP1 , RIN2 , RPS6KA5 , SASH1 , SCARA3 , SDCBP , SEC23A , SLC2A10 , SOAT1 , SORL1 , TENT5C , UST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Nomo Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD14B , ALX3 , ANKLE1 , ANPEP , ANXA3 , APBB2 , APOBEC3C , BCL2 , BEND5 , BEND6 , BEX2 , BTN3A3 , C10orf95 , C16orf74 , CAMK1D , CD24 , CHPT1 , CKMT1A , CRYBG1 , CYFIP2 , DDAH1 , DLX6-AS1 , DSG2 , ENHO , FAM117B , FANCE , FBLN7 , FBN2 , FDXR , GALNT12 , GCH1 , H1-0 , HEATR5A , HES6 , HOXD13 , HPDL , JDP2 , JPH1 , KLF5 , LAMP5 , LPCAT2 , MANSC1 , MGAT4A , MICAL2 , MTARC1 , MTHFD2L , MTURN , NEDD4 , NHSL2 , NUDT11 , PADI2 , PALD1 , PAWR , PCYOX1 , PDGFRL , PIK3R3 , PLXND1 , PNMA2 , POLD1 , PSTPIP2 , PTGER2 , RET , RMI2 , RNF144A , SCD , SDK2 , SEMA3C , SIDT2 , SLAIN1 , SLC16A14 , SLC16A4 , SLC35F1 , SLC37A4 , SLC39A14 , SOBP , STAR , STX11 , TCTA , TET1 , TEX15 , THEM6 , TIGD1 , TRIM58 , TSPAN2 , VAT1 , VAT1L , ZEB1-AS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc J1 Up Late.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATF3 , BGN , CCN1 , CCN2 , CDC42EP1 , CITED2 , COL4A1 , COL4A2 , CRIM1 , CTSC , DAB2 , DLK1 , DRAM1 , F3 , FGF5 , FHL2 , FLVCR2 , FST , GADD45B , GATA4 , GLIPR1 , GNG12 , GPRC5C , GRINA , GSN , HKDC1 , HMGA2 , HS3ST1 , HTRA1 , IGFBP4 , LGMN , LMO7 , LOXL2 , METTL27 , MORC4 , NEU1 , P4HA1 , P4HA2 , PARVA , PCDH1 , PDIA5 , PEG3 , PHLDA1 , PLXNB2 , PODXL , PRICKLE1 , PRXL2A , RAB11FIP5 , RAMP2 , RHOU , SEL1L3 , SERPINE2 , SESN3 , SLCO2A1 , SPOCK1 , TAX1BP3 , TCN2 , TNFRSF12A , VIL1 , WLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tbk1.Dn.48hrs Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1D , BCL2 , BIRC2 , COL4A1 , CRYZ , DUSP22 , DUSP4 , GALE , HSPA1A , IER3 , IL13RA1 , INPP4B , MSRA , PAFAH1B3 , PDGFA , PSMB8 , RALB , ST3GAL5 , STX1A , TRIB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADAM12 , ADAMTS1 , AGRN , ANXA11 , ANXA6 , ARL1 , BHLHE40 , CAP1 , CD44 , CELSR1 , COL18A1 , CREB3L2 , CTSC , DKK3 , DUSP14 , F2RL1 , FEZ2 , FLNA , FURIN , GADD45A , H2BC4 , HS3ST1 , HSPA5 , IGFBP3 , MICAL2 , MVP , NEDD9 , P4HA1 , PLXNA2 , PPP2R1B , PSMB10 , S100A16 , SEC23A , SLC7A5 , SLCO2A1 , SMIM3 , ST8SIA2 , TMCC3 , TNC , USP18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pgf Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTL6B , ARC , ATP1A3 , ATP2B2 , BCAM , CAMK2B , CEBPA , COL18A1 , CTF1 , DLEC1 , DLGAP1 , DPF1 , ELAVL3 , ENPP2 , FZD7 , GATA4 , GFRA2 , GRIA1 , GRM2 , HOMER2 , IGFBP6 , ITGB4 , KCNAB2 , KCNC3 , KCNN4 , KCNQ3 , LOXL1 , MAP1A , MAST1 , MSI1 , MTSS2 , NCAM1 , NELL2 , NFKB2 , NOS1AP , NPAS3 , NR6A1 , NUCB1 , OBSCN , PAIP2B , PKLR , PXN , RELB , RIMS3 , S100A4 , SDC4 , SLC29A2 , SLC30A10 , SLC6A15 , SPTB , SSTR2 , THY1 , TMEM158 , TMEM97 , TNFAIP3 , TNFSF12 , TROAP , UBE2H , ZFHX2 , ZNF185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camp Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK5 , AKT3 , ANXA1 , ARHGAP5 , ATP2B4 , ATP8A1 , BACH2 , BSN , CAMK2D , CAPN12 , CASP7 , CDCA7L , DCAF6 , DDAH1 , DGCR5 , ENO2 , ESYT1 , FOXN3 , FSTL1 , GAL3ST3 , GEM , GLS , GNG12 , HSPA1A , IL4R , IL7R , JARID2 , KBTBD11 , KCNN4 , LINC01089 , LRRFIP1 , MAP2 , MBD2 , NAP1L2 , NFKB1 , NUDT11 , PAK3 , PALLD , PAM , PCLO , PHLDB1 , PINK1 , PLS3 , RAB31 , RRAD , RREB1 , SEL1L3 , SLC2A3 , SLC35E2A , STXBP1 , SYPL1 , SYT11 , THSD7A , TIMP2 , TMBIM1 , TMEM97 , TMSB4X , TUBB2B , UBE2QL1 , UNC79 , ZFP36 , ZMIZ1</t>
   </si>
   <si>
     <t xml:space="preserve">Atf2 Up.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCA8 , ABCC3 , ADORA2B , BHLHE40 , C1RL , CCL2 , CCP110 , CD200 , CD302 , CD68 , CDH13 , CEMIP , CFB , CFH , COMP , CRLF1 , CXCL12 , CYBRD1 , DENND2D , DEPP1 , DNAJC12 , EDNRA , EFEMP1 , ERAP2 , EVC , FBLN2 , FGF7 , FOS , GALNT12 , GAS1 , GASK1B , GCH1 , GPR37 , GPRC5B , HEXIM1 , HKDC1 , IL1R1 , IL1RAP , IL33 , ITGBL1 , ITIH5 , KCNJ2 , KLHL21 , LIMCH1 , MN1 , MYO1D , NEAT1 , NFIB , NPPB , PC , PDLIM3 , PELI2 , PID1 , PIGN , PLAAT3 , PLEK2 , PLSCR4 , PNMA2 , PPL , PTGS2 , PTX3 , RNASE4 , S100A3 , SCD , SCRG1 , SDC3 , SIK1 , SLC12A8 , SLC39A8 , SLCO4A1 , SNCAIP , SPINT2 , STON1 , SVEP1 , TPD52 , VCAM1 , VTN , ZC3H12A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rb Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADAM12 , AGRN , ANXA11 , ANXA6 , ARL1 , ATF5 , BHLHE40 , BST2 , CALCB , CAP1 , CAV1 , CELSR1 , COL18A1 , CREB3L2 , CTSC , DDIT3 , DKK3 , DUSP14 , F2RL1 , FEZ2 , FLNA , FURIN , GADD45A , H2BC4 , HS3ST1 , HSPA5 , IGFBP3 , IL33 , LAMB3 , LAMC2 , LIFR , LRRC4 , MICAL2 , MMP9 , MVP , NEDD9 , P4HA1 , PDGFB , PPP2R1B , PSMB10 , RASL11B , S100A16 , SEC23A , SLC7A3 , SLC7A5 , SLCO2A1 , SMIM3 , ST8SIA2 , TLL1 , TMCC3 , TMEM140 , TMEM42 , TNC , USP18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tgfb Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCG1 , ADAM22 , AKAP12 , ANK1 , BCOR , BHLHE40 , CCN2 , CDKN2B , CHST3 , CLCF1 , CRYAB , CST6 , CYP2J2 , DACT1 , DDC , DGCR11 , DLC1 , DPY19L1 , EDN1 , ELK3 , ELL2 , EPHA4 , F2RL1 , FAT4 , FERMT2 , FGF1 , FOXD1 , GADD45B , HLX , HRH1 , HTR1D , IL11 , IRS1 , ITGA5 , ITGB6 , JUN , KCNN4 , KLF4 , KLF7 , LARP6 , LIF , LIPG , LMCD1 , LTBP2 , LYPD1 , MMD , NFATC4 , NGF , PAIP2B , PDGFA , PDGFB , PHLDB1 , PIK3CD , PMP22 , PPP1R13L , PXDC1 , RHOB , RNASE4 , RRAD , S100A3 , SCHIP1 , SEC14L2 , SLCO2A1 , SMOX , SMURF2 , SNAI1 , SPHK1 , SPSB1 , SSBP3 , STC1 , TAGLN , TBX3 , TLE3 , TNFAIP8 , TUBB4A , UBL3 , WNT4 , YIPF5 , ZFP36L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.300 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , ANGPTL4 , ANK3 , ANO1 , ARHGAP24 , ASIC4 , ASTN1 , ATP1A2 , BEX1 , CALB1 , CDK5R1 , CEL , CFAP69 , CHGA , CHGB , COL26A1 , CTNNA2 , DBH , DCBLD2 , DNM3 , DOCK4 , DYNC1I1 , EFCAB6 , EVI2A , GLDC , GPR19 , HAS2 , HTR7 , ITGA2 , ITGBL1 , KCNH2 , KIF5A , KIF5C , LMO3 , MMP1 , MMP11 , NAP1L2 , NAV3 , NME5 , NOL4 , NRCAM , PDE2A , PEG3 , PTX3 , RBP4 , RREB1 , RTN1 , SCG3 , SCN1B , SIGLEC15 , SLC6A15 , SLCO5A1 , SNAP25 , SNAP91 , SPP1 , ST3GAL6 , STC1 , TERT , TFPI , TOX3 , TRIB2 , TRIM36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snf5 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , ANGPTL4 , ANK3 , ANXA8 , ARHGEF28 , C1QTNF1 , CARD10 , CBR3 , CD99L2 , CDH10 , CDKN2A , CELF4 , CHODL , CNTN1 , CRMP1 , CYP7B1 , DSG2 , EFEMP1 , FABP4 , FADS3 , FAH , FBLIM1 , FOXD1 , FRZB , GDNF , GRIA3 , IL11 , ITGA3 , IVL , KCNAB1 , KIRREL1 , LMOD1 , LOXL4 , MALAT1 , MGST2 , MMP10 , MMP3 , NFKBIZ , NIPAL2 , NNMT , NPR1 , NPR3 , NSG1 , OTUD7A , P2RX5 , PAPPA , PCOLCE2 , PRKG2 , PTPRK , PTPRVP , RAG2 , RBP4 , RFX3 , RGS16 , RPS6KA2 , RRAD , SH3RF1 , SLC16A3 , SNCA , SPEG , STAR , STMN4 , SYTL2 , TCIM , TFPI2 , TNNT2 , TPD52L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc J1 Up Late.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD5 , APOM , ARAP2 , ARHGEF28 , BGN , CCN1 , CCN2 , CDC42EP1 , CITED1 , CITED2 , COL4A1 , COL4A2 , CRIM1 , CRYAB , CTSC , CTSH , CUBN , DAB2 , DLK1 , DRAM1 , ENPP5 , F3 , FGF5 , FHL2 , FLVCR2 , FRZB , FST , FUT8 , GADD45B , GLIPR1 , GNG12 , GRINA , GSN , GYG1 , HKDC1 , HMGA2 , HS3ST1 , HTRA1 , IGFBP4 , LGMN , LMO7 , LOXL2 , LPAR3 , METTL27 , MORC4 , MYO5B , NEU1 , P4HA1 , P4HA2 , PARVA , PCDH1 , PDIA5 , PEG3 , PHLDA1 , PLXNB2 , PODXL , PTH1R , RAB11FIP5 , RAMP2 , RBP4 , SEL1L3 , SERPINE2 , SGCE , SLC39A8 , SLCO2A1 , SNAI1 , SPOCK1 , TAX1BP3 , TCN2 , TDRD7 , TGFBR3 , TMED3 , TNFRSF12A , TNNT1 , TUFT1 , WLS</t>
+    <t xml:space="preserve">ABCA8 , ABCC3 , ADAM15 , ADORA2B , BHLHE40 , CD200 , CDH13 , CDK5RAP2 , CEMIP , CRLF1 , CXCL12 , CYBRD1 , DENND2D , DEPP1 , DNAJC12 , EFEMP1 , ERAP2 , EVC , FBLN2 , FGF7 , GALNT12 , GAS1 , GASK1B , GCH1 , GPR37 , GPRC5C , HEXIM1 , HKDC1 , IL1R1 , IL1RAP , KCNJ2 , KLHL21 , LIMCH1 , MN1 , MYO1D , NFIB , PC , PCSK7 , PDLIM3 , PELI2 , PID1 , PIGN , PLA2G4A , PLAAT3 , PNMA2 , PTGIS , PTX3 , S100A3 , SCD , SCRG1 , SDC3 , SGCG , SLC12A8 , SLCO4A1 , SNCAIP , SPINT2 , TPD52 , VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akt Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADGRL1 , ANGPTL4 , AXIN2 , BLVRB , C1R , C1S , CAP2 , CD248 , CNN2 , CSDC2 , DRAM1 , EDARADD , EFEMP1 , EFEMP2 , FAH , FANK1 , FAS , FBXO32 , GAS1 , GNA14 , HEBP1 , HTRA1 , IFFO1 , IL13RA1 , IL17RC , IRS1 , KCNK3 , KCNN4 , KLF2 , NCAM1 , NID1 , PDE4B , PDE9A , PDIA5 , PDLIM3 , PLA2G4A , PLTP , PPP1R3C , PROM1 , PTGIS , RECK , S1PR3 , SASH1 , SATB1 , SCARA3 , SIX5 , SLC18A1 , SLC37A4 , SLC39A13 , SLC7A5 , SNHG6 , SULT1E1 , TCAF2 , TNS2 , TP53I13 , TSPAN4 , ZFYVE21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Skm Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD14B , ADAMTS5 , ANKLE1 , ANPEP , APBB2 , ARHGEF26 , BCL2 , BEND5 , BEX2 , C10orf95 , CALD1 , CAST , CDH7 , CEMIP , CHPT1 , CLTCL1 , CPED1 , CRIM1 , CRIP2 , CRYBG1 , CYFIP2 , CYP7B1 , FAM117B , FBLIM1 , FRMD5 , GALNT12 , GPM6B , GPR37 , GRB10 , GRB14 , HMGA2 , JPH1 , KLRG2 , LRATD2 , MANSC1 , MCTP2 , MTARC1 , MTURN , N4BP2L1 , NHSL2 , NID1 , NPR3 , NR2F2 , NUDT11 , OGDHL , PADI2 , PAWR , PDGFRL , PHACTR3 , PODXL , PPP1R3C , PRDM11 , PROCR , PYROXD2 , RAB27B , RAB38 , RGS16 , RIPOR2 , SBDS , SCD , SERPINB8 , SETMAR , SH3D19 , SH3GL3 , SLC35F1 , SLC6A15 , SLITRK5 , SNTB1 , SORL1 , STAR , STING1 , SYNJ2 , TBC1D30 , TENT5C , TEX15 , THBS4 , TMEFF1 , TNFAIP8 , TONSL , TPD52 , VCL , ZEB1-AS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc2 Ezh2 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTS5 , APLP1 , AURKB , CACNA2D2 , CDC25A , CDT1 , CENPF , CENPU , CXCL12 , DLGAP5 , DNA2 , DOC2B , ELL2 , EZH2 , FKBP5 , FOSL2 , FOXN3 , GAS1 , HAS2 , HMOX1 , HOXD11 , IFIT1 , KIF15 , KIF4A , KNTC1 , LBR , LIN7A , LMNB1 , LMOD1 , LRRC32 , MCM10 , MCM2 , MYBL2 , MYT1L , NCAPH , NFIB , NGF , NLGN1 , NPAS1 , NPR3 , NR6A1 , OIP5 , OLFML2B , PAN2 , PEAK1 , PLCD1 , PRIM1 , SCN3A , SKP2 , SLC16A10 , SULF1 , SYN1 , SYP , SYT11 , TBC1D2 , THBS2 , TRPM4 , TTK , WDR76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il2 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ADAM19 , AHR , AMIGO2 , ATG101 , CALML4 , CCDC85B , CDC25A , CDCP1 , CNKSR2 , CXCL12 , DUSP4 , EHD2 , F2RL2 , FOSL1 , FOSL2 , GABRB3 , GADD45B , GFAP , HEG1 , IL1A , INSR , IRS1 , ITGA9 , KCNK5 , KIF13A , KIF1C , KLF6 , LIF , LMO3 , MAFF , NR2F2 , PAK6 , PLEC , PLPP2 , PTCH1 , REST , RGS16 , RHBDF2 , RHOB , RNF144A , SLC1A5 , SLC29A2 , SLC2A3 , SLC66A1 , SLC7A5 , SLCO4A1 , SOCS1 , SPHK1 , STX11 , TLR3 , TM4SF1 , TMEM158 , TNFAIP8 , TNFRSF12A , TPBG , VDR , WDR62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat.100 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , CAVIN1 , CHODL , DBNDD1 , DKK1 , DNAJC3 , DUSP4 , EEF1A2 , EFEMP1 , ENO2 , ENPP2 , FLVCR2 , IRS1 , ITGA9 , RBP1 , RUNX1 , SLC7A8 , SORBS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stk33 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD14B , ANKLE1 , ANPEP , ANXA3 , APBB2 , ARHGEF26 , BCL2 , BEND5 , BEND6 , BEX2 , BTN3A3 , C10orf95 , C12orf75 , C16orf74 , CAST , CHPT1 , CLTCL1 , CRYBG1 , CYFIP2 , DDAH1 , DSG2 , ENDOD1 , ENHO , FAM117B , FANCE , FBLN7 , FBN2 , FDXR , GALNT12 , GPM6B , HES6 , HPDL , JPH1 , KBTBD11 , KLF5 , KLRG2 , LAMP5 , LPCAT2 , LRATD2 , MANSC1 , MGAT4A , MICAL2 , MTARC1 , MTURN , NHSL2 , NR2F2 , NUDT11 , OGDHL , PADI2 , PALD1 , PAWR , PCYOX1 , PDGFRL , PIK3R3 , PLXND1 , PNMA2 , PODXL , POLD1 , PSTPIP2 , RET , RGS16 , RIPOR2 , RMI2 , RNF144A , SCD , SETMAR , SH3GL3 , SIDT2 , SLC35F1 , SLC37A4 , STAR , STX11 , TCTA , TENT5C , TEX15 , TMEFF1 , TNFAIP8 , TRIM58 , TSPAN2 , VAT1L , VCL , ZEB1-AS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat Bild Et Al Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKRD28 , ARPC2 , EFR3A , GCLM , GRID1 , IER5 , IL1A , IL1RAP , IRAK2 , ISCU , LNPEP , MACROH2A1 , PTHLH , SMURF2 , SORL1 , STARD13 , TNFAIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Src Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL4 , ARSJ , ATAD2 , CAPN12 , CARNMT1 , CDCA7 , CENPH , DEPP1 , DISP2 , DPYD , E2F8 , EMB , EZH2 , FANCL , FRMD4B , GDPD3 , GRID1 , HS3ST3A1 , IFIT1 , IL7R , IRAK2 , IVL , LIG1 , LINC00842 , MAP3K6 , MCM3 , MGARP , MIR17HG , MMP1 , MMP10 , MMP3 , MN1 , NBEAL1 , NID2 , NRP1 , PAK3 , PC , PHLDA2 , PLAT , PLK4 , PRR19 , PTBP2 , S1PR3 , SH3TC2 , SLC7A14 , SOAT1 , ST8SIA2 , STK17B , SUV39H2 , SYT1 , TMOD1 , ZNF135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akt Up Mtor Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4GALT , ADORA2B , ATF3 , BMP8B , C3orf52 , CARD19 , CDKN2B , CLMN , CRLF1 , CTNS , DUSP1 , DUSP8 , EDN1 , GCH1 , GIPC1 , GLDC , GPD2 , GPX8 , H4C8 , HBEGF , HCN2 , HIC2 , IFIT1 , IL1R1 , KCNK5 , KCNQ1 , KCTD9 , KLF6 , LGMN , LYPD1 , MAN2B2 , METRNL , MGARP , MPP2 , MVP , MYCN , NEU1 , NFKB2 , NIBAN1 , PLAT , PON2 , PTPRJ , PYGL , RUNDC3A , SEC14L2 , SLC44A1 , SPHK1 , TESC , TGIF1 , TMCC3 , TNFRSF12A , VAMP5 , VANGL2 , VAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raf Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABAT , ABCA12 , ACKR3 , APBB2 , ASCL1 , BAG3 , BCL2 , CA12 , CELSR2 , CLIC3 , COL9A3 , CRABP1 , CRYBG1 , DKK1 , DLC1 , DNAJC12 , ELOVL2 , EPB41L4B , GDAP1 , GPC4 , GPD2 , GREB1 , H4C8 , HSPB8 , ID1 , IGFBP4 , INPP4B , IRS1 , LRIG1 , MGP , MICB , MXI1 , MYB , MYLK , MYO10 , OSTM1 , PALLD , PCSK6 , PDGFRL , PLCB4 , PPM1E , PPP1R3C , PTBP2 , PXDN , SCUBE2 , SGCG , SH3BGRL , SHROOM2 , SMAD7 , SNAP23 , SOX4 , SOX9 , SYTL2 , TBC1D30 , TGFB2 , TM4SF1 , ZBTB10 , ZHX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegf A Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AASS , ACE , ADAM9 , AMPH , ASPH , ATP13A3 , BAK1 , BCL10 , BUB1B , CCNB2 , CDKN3 , CENPA , CENPE , CEP131 , CNTFR , CRYZ , DHFR , DKK1 , DLGAP5 , EXO1 , FKBP5 , GPR37 , ITGA2 , ITGB3 , KIF11 , KIF22 , LMNB1 , LRRC17 , LRRFIP1 , MAD2L1 , MAFK , MEST , MPHOSPH6 , MT1X , NDC80 , NEK7 , NRP1 , OSTF1 , PCDH7 , PGAP1 , PLCL1 , PLK4 , RAB3B , RNF6 , SAT1 , SEL1L , SETBP1 , SMC4 , SPAG5 , TGFBI , TMPO , TTK , TWF1 , UFL1 , UGP2 , VEGFC , ZNF124 , ZNF253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crx Nrl Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACVR2B , AHRR , ARHGAP10 , B4GALT1 , BCL2L11 , BICDL1 , BST1 , BUB1B , CAMK1D , CKMT1A , CUTALP , EXT1 , FXYD6 , GADD45A , GALNT10 , GFAP , HSPA1A , IER3 , KCNN4 , KLHL36 , LRRC2 , MEST , NRL , PAQR4 , PDIA5 , PIP4K2C , PLEKHA2 , PLPP2 , PROSER2 , PSD , REC8 , RFX2 , SEC14L2 , SLC16A3 , SLC29A2 , SNTB2 , ST8SIA1 , STK17B , TNFAIP3 , TNIP2 , TNS2 , UBXN11 , WWTR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crx Nrl Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPH , C14orf132 , CAMK2B , CAP1 , CHRNA3 , CHRNB4 , CLIC4 , CLPB , CPLX2 , CTBS , ECE1 , ELOVL2 , FMN1 , FRMD6 , GDPD3 , GREB1 , GSDME , HEBP1 , HS3ST1 , INPPL1 , INSM2 , KIF5C , METRN , MYOCD , NECTIN3 , NFKB1 , NSG1 , NTN4 , PAM , PLEC , QSOX1 , RAB27B , RASGRF2 , RREB1 , SDC4 , TMEM158 , TNC , TNFRSF12A , TSPAN33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pdgf Erk Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11 , ANXA7 , AQP3 , C17orf75 , CALML4 , CDK6 , CEP131 , CETN2 , CHEK2 , COL1A1 , CORO2B , CPS1 , DDN , FLI1 , FSTL4 , GAP43 , INHBA , KBTBD11 , LEPROT , LRPAP1 , LUZP2 , MAML3 , MAOA , MAP2 , MID1 , MTHFR , MYO1E , NAGLU , NRG1 , PAN2 , PHLDA2 , PPIC , PSMB10 , REST , RRBP1 , RTCA , SLC39A7 , SPAG5 , ST6GAL1 , TCEAL2 , TP53I3 , TSPAN9 , ZNF185 , ZNF84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akt Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACOT9 , ADORA2B , ATF3 , C3orf52 , CARD19 , CDKN2B , CLMN , CRLF1 , EDN1 , GCH1 , GIPC1 , GPD2 , GPX8 , H4C8 , HIC2 , IFIT1 , IFIT2 , IFIT3 , IL1R1 , KCNK5 , KCNQ1 , KLF6 , LGMN , MAN2B2 , METRNL , MGARP , NEU1 , NIBAN1 , NKAIN1 , P2RX5 , PDGFD , PDK1 , PFKP , PLAT , PON2 , PTPN14 , PTPRJ , PTRH1 , PYGL , RUNDC3A , SEC14L2 , SECTM1 , SPECC1 , SPHK1 , TESC , TMCC3 , TNFRSF12A , UBE2C , VAMP5 , VAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mel18 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOE , AQP3 , B3GAT1 , BAG3 , CDH10 , COL9A3 , CRABP1 , CRABP2 , CUX2 , DDC , DDX60 , DLK1 , DPYD , EEF1A2 , FRMD4B , GNG7 , GPR137B , H4C8 , IFIT1 , IFIT2 , IL1R1 , MAF , MPPED2 , MVP , NDRG2 , NMNAT2 , PDE4B , PDE5A , PEG3 , PHYH , PID1 , PLEKHA4 , PROM1 , SEMA3E , SH3BGRL , SLC16A4 , SNCAIP , STK17B , SULF1 , TCEAL2 , TENT5A , TMOD1 , UNC5C , ZCCHC24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tbk1.Dn.48hrs Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOE , ARL4C , CDKN2A , CEBPA , CHEK2 , DDR1 , DUSP3 , EDN1 , FCHO1 , FKBP14 , FSD1 , IGFBP3 , LBR , LRPAP1 , MYLK , SCP2 , ZMIZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cahoy Oligodendrocutic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHR , CCN2 , CLN8 , CRIP2 , CSDC2 , DKK3 , DOCK10 , EFHD2 , FBP1 , FSTL1 , GAB3 , GNG8 , IFFO1 , KIAA1958 , LCORL , LHFPL6 , NRP1 , P4HA2 , PHLDB1 , PLXNB3 , PRKAG2 , PSTPIP2 , RNASEH2B , RNF122 , SEMA3D , SEMA5A , SLC35B2 , SPEG , TENM1 , TSPAN2 , ZNF536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il15 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , AHR , APLP1 , CALML4 , CCDC85B , CDC25A , CPA4 , CXCL12 , DUSP4 , ECM1 , FAM3C , FOSL1 , GADD45B , HEG1 , HOXC8 , HRH3 , HS3ST1 , HS3ST3B1 , HSD17B14 , IL1A , IRS1 , KCNJ2 , KCNJ9 , KIF1C , LIF , MAF , MAFF , MAFK , NR2F2 , PAK6 , PER2 , PLEC , PNMT , PSG4 , PTCH1 , REST , RGS16 , RHOB , RNF144A , SHROOM2 , SLC1A5 , SLC29A2 , SLC66A1 , SLC7A5 , SLCO4A1 , SOCS1 , SPOCK1 , TET3 , TLR3 , TMEM158 , TNFAIP8 , TNFRSF12A , TPST2 , VDR , ZBTB7A</t>
   </si>
   <si>
     <t xml:space="preserve">Nrl Dn.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ACVR2B , AHRR , ALPL , APC2 , ARG2 , ARHGAP10 , B4GALT1 , BCL2L11 , BCL3 , BICDL1 , BST1 , CALN1 , CALU , CDK5R2 , CLDN23 , CNGB1 , CSDC2 , DHRS3 , DIRAS1 , DPF3 , DUSP14 , ELAVL3 , EXT1 , GADD45A , GALNT10 , GALNT7 , GAS7 , GRIK5 , GRIP1 , HIC2 , IGFBP5 , KCNN4 , KLHL36 , LMO1 , LRRC2 , MKNK1 , NRL , NUF2 , PDIA5 , PLA2R1 , PLEKHA2 , PLEKHF2 , PLPP2 , PROSER2 , RHBDL3 , RNF207 , SEC14L2 , SLC24A1 , SLC29A2 , SNTB2 , SPEN , ST3GAL1 , ST8SIA1 , STK17B , STYX , TNFAIP3 , TNNT2 , ZFP36L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rps14 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR1 , ADD2 , AGAP1 , ART4 , ATAD2 , ATP1B2 , BAG2 , BAG3 , C14orf132 , CBS , CCNB2 , CLCN4 , COBLL1 , COLEC11 , CRMP1 , CYBRD1 , DBH , DDN , DEPDC1 , DGCR11 , DLGAP5 , DOCK9 , DYRK3 , E2F8 , ENG , EPB41 , ERCC6L , ESPL1 , EXO1 , FBXO5 , FICD , GAL , GINS2 , ID1 , INCENP , KANK2 , KIF15 , KIF20A , KIF2C , KIF5A , MACROD1 , MAMLD1 , MCM10 , MCM5 , MKI67 , MSH2 , MYBL2 , MYLIP , NCAPH , NDC1 , NEFH , NID2 , NMU , ORC1 , PBK , PC , POLD1 , PRC1 , RAP1GAP , S100A3 , SH3TC2 , SLC29A1 , SLC29A2 , SPHK1 , SPTB , STEAP3 , STMN2 , SUV39H2 , TFAP2B , TGM2 , THEM6 , TLX2 , TMSB15A , TUBB2B , ZNF74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoxa9 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTA2 , ADAM9 , AGTPBP1 , ANKRD46 , ARL4C , ATXN1 , BST1 , CARD9 , CCNA1 , COL6A3 , COQ10B , CRISPLD2 , CSPG4 , CTSL , CXCL8 , CYLD , DYNLT3 , FAM98A , FAS , FCGRT , FDXR , FNDC3B , FOS , FUCA1 , GADD45A , GALNT7 , GAS7 , GDF15 , GLIPR1 , GNS , GPR137B , H2AC6 , H2BC12 , H2BC9 , HLA-DMA , ICAM3 , IER5 , IFI16 , IFI30 , IL13RA1 , ISG15 , JAK2 , KLF4 , MARCHF2 , MYOF , NAGK , OSTM1 , OTULINL , PARP12 , PIK3R3 , PLK2 , RBM47 , SCHIP1 , SCPEP1 , SERPINB8 , SGK3 , SLC22A18 , SLC22A4 , SLC30A1 , SLC46A3 , ST3GAL6 , TAX1BP3 , TDRD7 , THBS4 , TIGAR , TNFRSF10B , TP53I3 , TP53TG1 , TPK1 , TRIM22 , TRPM4 , TSPOAP1 , TWF1 , UGGT2 , VCAN , ZMAT3 , ZNF107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atf2 S Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA8 , ABCC3 , ADAM22 , ADARB1 , ANGPTL4 , ATF5 , BMPR1B , C1RL , CCL2 , CD302 , CEMIP , CLGN , COBLL1 , COL7A1 , COMP , CRIP2 , CRLF1 , DNAJC12 , EFEMP1 , ENO2 , EVC , FBLN2 , FGF7 , FOS , GALNT12 , GAS1 , GCH1 , HSD17B1 , IL1R1 , IL1RAP , IL33 , IL4R , ITGBL1 , ITIH5 , ITPR1 , KBTBD11 , KCNAB2 , KRT8 , LAMA2 , MN1 , MYO1D , NEAT1 , NFIB , NGF , NPPB , OSMR , PADI2 , PDLIM3 , PID1 , PLAAT3 , PLEK2 , PLSCR4 , PNMA2 , POLE , PPL , PTGER2 , PTGS2 , SDC3 , SERPINB7 , SIK2 , SLC12A8 , SLC39A8 , SLC4A2 , SNCAIP , SORBS1 , SPINT2 , ST3GAL6 , STMN2 , SVEP1 , TENM4 , TLE3 , TNNT2 , TPD52 , VCAM1 , VTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lte2 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCC3 , ACTG2 , AKAP12 , ANKMY2 , ANXA6 , AOX1 , AQP3 , ASPH , ASRGL1 , BMP7 , C1orf115 , CD302 , CDKN3 , CEMIP , CLIC3 , CREB3L2 , CXCR4 , DAB2 , DPYSL2 , DRAM1 , DUSP4 , EDN1 , EHD3 , EPAS1 , EPHX1 , EPN3 , EPS8L1 , FERMT2 , GALNT12 , GCLM , GCNT1 , GLTP , HSD17B14 , IGFBP5 , IL1R1 , LMO4 , MAOA , MBP , MGAT4A , MMP9 , NOVA1 , NPC2 , NUCB2 , NUDT4 , ORAI3 , P4HA2 , PBK , PCDH9 , PHACTR2 , PLAGL1 , PLPP2 , POLE2 , PPFIA3 , PPP1R3C , PROS1 , PRPS1 , PSTPIP2 , RAB27A , RAB29 , RCAN1 , REEP1 , RHOQ , RIN2 , RLN2 , RPS6KA5 , SASH1 , SCARA3 , SDCBP , SEC23A , SLC2A10 , TENT5C , TNNT1 , TNS3 , TST , UST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc2 Ezh2 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS5 , APLP1 , AURKB , BUB1 , CACNA2D2 , CDC25A , CDC45 , CDT1 , CENPF , CENPU , CORO1A , CPEB1 , CXCL12 , DEPDC1 , DLGAP5 , DNA2 , DOC2B , DSCC1 , ELL2 , EPHX2 , EZH2 , FKBP5 , FOSL2 , GAS1 , GUCY1A2 , HAS2 , HAUS5 , HELLS , HMMR , HOXD11 , IFIT1 , IL17RB , KCNS1 , KIF15 , KIF4A , KNTC1 , KRT81 , LBR , LMNB1 , LMOD1 , LRRC32 , LRRC61 , MCM10 , MCM2 , MIS18BP1 , MSH5 , MXD3 , MYBL2 , MYT1L , NCAPH , NFIB , NGF , NPAS1 , NPR3 , NR6A1 , OIP5 , OLFML2B , PEAK1 , PLCD1 , PRIM1 , PSRC1 , RFC4 , SCN3A , SKP2 , SLC16A10 , SULF1 , SYN1 , SYP , SYT11 , TACC3 , TBC1D2 , THBS2 , TPD52L1 , TRPM4 , TTK , WDR76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Skm Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTA2 , ADM , ANXA1 , ARHGAP42 , ARID5B , ASPH , BBS12 , BCL3 , C5AR1 , CCN3 , CD101 , CD36 , CD58 , CDKN1A , CDKN1C , CFL2 , CLDN1 , CMTM1 , CMTM3 , CPEB2 , CREBRF , CYBRD1 , DNAJB4 , DUSP1 , DUSP5 , DUSP8 , EGR1 , EMP3 , ERMAP , ERRFI1 , EVI5 , FABP4 , FAM177A1 , FCHSD1 , FOS , GBP2 , GBP3 , GDPD1 , GLIPR1 , GNG11 , GPR137B , GPR137C , H2AC6 , H2BC21 , H2BC4 , H4C8 , HBEGF , HECW2 , IFI16 , IL15 , IL1A , IL1B , IRF1 , IRF9 , ITGB8 , KCNJ2 , KITLG , KLF6 , LGALS1 , MAP2 , MFAP3L , MIR22HG , MPPED2 , MYEF2 , NBEAL1 , NFKBIZ , NFXL1 , NMNAT1 , PALLD , PHLDA1 , PID1 , PLAU , PLK2 , PLXNB2 , PPCS , PRTFDC1 , PTPRM , RAB7B , RASGRP3 , RHOB , RHOC , RIT1 , RND3 , RNF141 , RTN1 , SETBP1 , SH2B3 , SLC38A6 , SLC7A11 , SQSTM1 , STAM2 , STOX2 , TFPI , TFPI2 , TGFB1I1 , TK2 , TLR6 , TP53INP1 , TTLL7 , TWF1 , UPP1 , VSIR , ZFP36 , ZNF675 , ZNF718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crx Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA2 , ARHGEF28 , BACH2 , BCL3 , C1QTNF6 , CAMK2B , CDKN1A , CEBPB , CEBPD , CHRNA3 , CHRNB4 , COL4A2 , DUSP16 , EGR1 , FKBP5 , FMN1 , FOXD1 , FRMD6 , GDAP1L1 , GLIPR2 , GNG11 , H6PD , HLA-B , HSD17B2 , INSM1 , INSM2 , KDELR3 , LRRC4 , MAP3K8 , NFKB1 , NUPR1 , OSMR , PHOX2B , PLAT , PLEC , RAI14 , RBP4 , RNASE4 , S100A16 , S100A6 , SEL1L3 , SEMA5B , SH3BP4 , SOCS3 , SPSB2 , TAGLN2 , TECTA , TGM2 , TIMP1 , TLE1 , TMBIM1 , TMOD1 , TNFRSF12A , TUBB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vegf A Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AASS , ACE , ADAM9 , ADTRP , AMPH , ANGPT2 , ASPH , ATP13A3 , BAK1 , BCL10 , BIRC5 , BUB1 , BUB1B , CCNB1 , CCNB2 , CDC42EP2 , CDC45 , CDKN3 , CENPA , CKS2 , CNTFR , CRYZ , DBF4 , DHFR , DKK1 , DLGAP5 , EXO1 , FABP4 , FKBP5 , GPR37 , HMMR , ITGA2 , ITGB3 , KIF11 , KIF22 , LMNB1 , LRRC17 , LRRFIP1 , MAD2L1 , MAFK , MCM4 , MEST , MMP14 , MT1X , NCOA3 , NDC80 , NEK7 , NRP1 , OSTF1 , PCDH7 , PGAP1 , PLCL1 , PLK4 , RAB3B , RFC4 , RND3 , RNF6 , SAT1 , SEL1L , SETBP1 , SMC4 , SPAG5 , SULT1B1 , TGFBI , TLE3 , TMPO , TSPAN8 , TTK , TWF1 , UFL1 , UGP2 , VEGFC , VRK1 , ZNF124 , ZNF253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tgfb Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADRB2 , ANGPTL4 , ANKMY2 , ARID5B , AVPI1 , BCL6 , BDKRB2 , BIRC3 , C14orf93 , CAVIN2 , CHST7 , CITED2 , COL4A1 , CXADR , DUSP4 , ENTPD7 , EVI2A , EYA4 , FBXL15 , FNDC3B , FRMD4B , FRS3 , FSTL3 , GATA3 , GCH1 , GPR39 , HS3ST1 , HSF2 , HSPG2 , ID1 , IFIT1 , IFIT2 , IFIT3 , IRF1 , ISL1 , JADE2 , KIF18A , KITLG , MIR22HG , MITF , MN1 , MPPED2 , NPAS1 , NR2F2 , NUDT18 , PAQR5 , PCBP3 , PGBD5 , PIK3R3 , PSG2 , PTCH1 , PTX3 , RAB33A , RAB38 , RAI2 , RASGRF1 , RBM47 , RGL1 , RPP25 , SERTAD2 , SH3TC2 , SKP2 , SLC30A1 , SMAD7 , SPRY1 , STK38L , TMCC2 , TRPM4 , TUFT1 , UGT8 , ZNF292 , ZNF395 , ZNF74</t>
+    <t xml:space="preserve">ACVR2B , AHRR , APC2 , ARHGAP10 , B4GALT1 , BCL2L11 , BCL3 , BICDL1 , BST1 , CALN1 , CALU , CDK5R2 , CSDC2 , DIRAS1 , DUSP14 , ELAVL3 , EXT1 , GADD45A , GALNT10 , GALNT7 , HIC2 , KCNN4 , KLHL36 , LMO1 , LRRC2 , NRL , NUF2 , PDIA5 , PLEKHA2 , PLEKHF2 , PLPP2 , PROSER2 , RFX2 , SEC14L2 , SLC29A2 , SNTB2 , SPEN , ST8SIA1 , STK17B , STYX , TNFAIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atf2 S Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABLIM3 , ADAMTSL4 , ALX3 , ANXA3 , APOL6 , ARSJ , ASIC4 , ATP2B2 , CD24 , CD8A , CDKN3 , CENPU , CLDN1 , CRYBG1 , CXCL8 , DBNDD1 , DLEC1 , DYSF , ENDOG , EPX , EZH2 , FNDC11 , FOXM1 , FSD1 , GNA14 , HOXD10 , INA , ITGA6 , KIF20A , LRRC17 , LRRTM2 , MBOAT7 , MMP1 , MPZ , NEFM , NFE2L3 , NIPAL3 , NLGN1 , NNAT , NQO2 , PLAU , PLCB4 , PLEKHA2 , PMEL , PSMB9 , RPL39L , S100A4 , SCIN , SEMA5A , SSPN , STEAP1B , TBC1D19 , TOP2A , TRPC4 , UPP1 , WNT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Csr Early Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR3 , ATG101 , BCAR1 , BCAR3 , BDKRB1 , CD274 , CEMIP2 , DCBLD1 , EHD4 , ELK3 , F3 , FJX1 , FOXD1 , FRMD6 , FZD8 , GAL , GATA2 , HBEGF , HPCAL1 , IL11 , INHBA , ITPRIPL2 , MAP2K3 , NSG1 , NT5E , PCSK7 , PHLDB1 , PLAUR , PXN , REST , RGMB , RIPK2 , SCHIP1 , SHB , SLC30A1 , SLC37A4 , SMAD7 , SMARCA4 , SMTN , SOX9 , STC1 , TENT4A , TMEM200A , TNFRSF12A , ZBTB12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc J1 Up Early.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMH , ANGPTL4 , ANXA1 , ANXA3 , ANXA5 , BCL3 , BMP1 , C11orf24 , C16orf74 , CCN1 , CEBPD , CNN1 , CRYL1 , DNAJC30 , DPYSL5 , EDN1 , EPOP , GAP43 , GBP1 , GBP2 , GNA14 , H2BC4 , ID1 , IGFBP3 , KLF4 , LIMS2 , LPP , LUC7L3 , MAPT , MYC , NUDT11 , PAFAH2 , PPCS , PPP2R3A , PTGIS , RAB33A , RELB , SERPINE1 , SLC30A1 , SLC66A1 , SOCS3 , TAGLN , TCF15 , TNFRSF12A , TRAIP , TRIB3 , UBA7 , VWA5A , ZFP36 , ZFP36L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc2 Eed Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , AKR1C3 , ANGPTL4 , ANKRD46 , ARL4C , ATF3 , ATXN1 , C1orf21 , CDHR2 , CDKN1C , CHST11 , CLGN , CLIP1 , CORO2B , CTSO , DCP2 , DEPP1 , DNAJC12 , DUSP8 , ELF1 , ENPP2 , EVI5 , FUCA1 , GPC5 , GPR37 , H1-2 , H2AC6 , H2BC21 , H2BC4 , HIC2 , HOXC8 , IL13RA2 , KCNQ2 , KIF1B , MAP3K7CL , MTHFD2L , MTSS1 , NIBAN1 , OBSCN , ORAI3 , OSGIN1 , OSTM1 , PDGFA , PTBP2 , RBM47 , SATB1 , SCG2 , SEMA6D , SERPINB7 , SLC12A8 , SLC30A10 , SLC35D2 , SLC6A15 , VTN , ZNF91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc J1 Up Late.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMH , ANGPTL4 , BCL3 , BHLHE40 , CALML4 , CAVIN1 , CRMP1 , DDC , DLC1 , DNASE2 , E2F8 , EDN1 , ENDOG , EVC , FOXN4 , GAP43 , GLI1 , GNG3 , ICAM1 , INA , KLF4 , MMP11 , MYC , NEFH , NIBAN1 , NNAT , NR0B1 , PASK , PCOLCE2 , PDGFC , PHLDA2 , POLA1 , POLE , PPCS , PTGIS , RASGRP2 , RASIP1 , SLC1A5 , SNTB2 , SOCS3 , SULT4A1 , TAF13 , TCF15 , TET1 , TRAIP , TUBB2B , VEGFC , ZFP62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc V6.5 Up Late.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARFGAP3 , ARID3B , ARMH4 , BAIAP2L1 , COL4A1 , COL4A2 , DAB2 , DKK1 , FGF5 , FGFRL1 , FZD8 , GAS1 , GATA4 , GPRC5C , GRINA , GSC , H1-0 , HEXA , HLA-B , IER5 , KDELR3 , KIF21A , LGMN , LOXL2 , MACROD1 , MOSPD1 , MYLIP , NAGLU , NUDT11 , P4HA1 , P4HA2 , PDLIM3 , PKDCC , PLOD2 , PLXNB2 , PODXL , PRICKLE1 , PRXL2A , RAMP2 , RECK , RHOU , RIPK4 , SATB1 , SEL1L3 , SH3RF1 , SIL1 , SIX5 , STX7 , TCN2 , TSPAN7 , VIL1 , WLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myc Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGER , AKR1C3 , ANGPTL4 , BCAR1 , C16orf74 , CDCA8 , DEPP1 , DUSP18 , GBP3 , GPRC5A , GRID1 , H2AC6 , HEG1 , IL1R1 , IRAK2 , KLF12 , KRT80 , LINC00842 , LMTK3 , MAP3K6 , MCHR1 , MGARP , MMP1 , MMP3 , MN1 , MTMR11 , NBEAL1 , NID2 , NR6A1 , NRP1 , PAK3 , PC , PDZD2 , PLAT , PLEKHA2 , PODN , PPM1N , PRRT2 , REC8 , SAMD9 , SPOCD1 , SPTB , SYT1 , TEP1 , TGM2 , TLR2 , TRIM56 , TRPM4 , WNT5B</t>
   </si>
   <si>
     <t xml:space="preserve">Csr Late Up.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCA6 , ADORA2B , ANKRD29 , APOL3 , BACH1 , BCL10 , C1orf115 , CAVIN2 , CCL2 , CCN3 , CDC42EP2 , CFH , CHST2 , DDX60L , DRAM1 , EBP , EPHB6 , ERMP1 , F8 , FDXR , FTH1 , GAS1 , GAS6 , GFRA1 , GLI3 , GLT8D2 , GSN , IGDCC4 , IL1B , ITGB8 , KLHL29 , L1CAM , LPAR3 , LRIG1 , MAMLD1 , MME , MOB3C , NTN4 , OLFML2A , PAMR1 , PDE5A , PDP1 , PLAAT4 , PLBD2 , PLCD1 , PRRT2 , PYROXD2 , SCD , SLC22A18 , SMIM29 , SNTB1 , SOD2 , SUMF1 , SVEP1 , TNXB , TP53INP1 , TRIM22 , VAMP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.50 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANGPTL4 , CALB1 , CHGB , DOCK4 , DYNC1I1 , GLDC , HTR7 , ITGA2 , KIF5C , LMO3 , MMP11 , NRCAM , PEG3 , RBP4 , RREB1 , SCG3 , SIGLEC15 , SNAP25 , SNAP91 , ST3GAL6 , STC1 , TERT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crx Nrl Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACVR2B , AHRR , ALPL , ANKRD33B , ARG2 , ARHGAP10 , B4GALT1 , BCL2L11 , BICDL1 , BST1 , BUB1B , CCDC107 , CKMT1A , CNGB1 , CUTALP , DHRS3 , DPF3 , EPS8L1 , EXT1 , FXYD6 , GADD45A , GALNT10 , GAS7 , IER3 , KCNN4 , KLHL36 , LRRC2 , MEST , NRL , PAQR4 , PDIA5 , PIP4K2C , PLA2R1 , PLEKHA2 , PLPP2 , PROSER2 , PSD , REC8 , RNF207 , RTBDN , SEC14L2 , SLC16A3 , SLC24A1 , SLC29A2 , SNTB2 , ST3GAL1 , ST8SIA1 , STK17B , TNFAIP3 , TNIP2 , TNNT1 , TNNT2 , TNS2 , WWTR1 , ZFP36L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atf2 S Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABLIM3 , ADAMTSL4 , ADRB2 , ANXA3 , APOL6 , ARSJ , ASIC4 , ATP2B2 , B3GALT2 , C1orf115 , C3AR1 , CACNA2D3 , CCDC81 , CD24 , CD8A , CDKN3 , CENPU , CLDN1 , CRYBG1 , CUBN , CXCL8 , DBNDD1 , DYSF , ENDOG , EZH2 , FAT4 , FOXM1 , FSD1 , GPR63 , GSG1 , HOXD1 , HOXD10 , HTR2B , IL17RB , IL20RA , IL32 , INA , ITGA6 , ITIH3 , KIF20A , KRT81 , LRRC17 , MBOAT7 , MMP1 , NEFL , NEFM , NFE2L3 , NIPAL3 , NNAT , NQO2 , NRXN3 , PCNT , PLAU , PLEKHA2 , PMEL , PPM1H , PSMB9 , RASGRP1 , RPL39L , S100A4 , SCIN , SEMA5A , SSPN , STEAP1B , TBC1D19 , TCIM , TNFSF18 , TNFSF4 , TOP2A , TRPC4 , UPP1 , WNT5B , ZFR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il2 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ADAM19 , AHR , AMIGO2 , ATG101 , CALML4 , CDC25A , CDCP1 , CNKSR2 , CXCL12 , DHRS3 , DUSP4 , EGR1 , EGR2 , EHD2 , F2RL2 , FLT3LG , FOS , FOSL1 , FOSL2 , GABRB3 , GADD45B , HABP4 , HEG1 , IL1A , INSR , IRS1 , ITGA9 , KCNA3 , KCNG1 , KCNK5 , KIF13A , KIF1C , KLF6 , LIF , LMO3 , MAFF , MEGF6 , NR2F2 , PAK6 , PDE4A , PLEC , PLPP2 , PPP4R4 , PTCH1 , PTH1R , RAC3 , REST , RGS16 , RHBDF2 , RHOB , RNF144A , RPP25 , SLC1A5 , SLC29A2 , SLC2A3 , SLC7A5 , SLCO4A1 , SOCS1 , SPHK1 , SPP1 , STX11 , TLR3 , TM4SF1 , TMEM158 , TNFAIP8 , TNFRSF12A , TNFRSF9 , TPBG , VDR , VSNL1 , WDR62</t>
+    <t xml:space="preserve">ADORA2B , BCL10 , CAVIN2 , CCN3 , DDX60L , DENND11 , DRAM1 , EPB41L4A-AS1 , EPHB6 , ERMP1 , FDXR , FTH1 , GAS1 , GAS6 , GLT8D2 , GSN , IGDCC4 , ITGB8 , L1CAM , LRIG1 , MAMLD1 , MLLT6 , MME , MOB3C , NBEA , NTN4 , OLFML2A , PAMR1 , PDE5A , PDP1 , PLBD2 , PLCD1 , PRRT2 , PRXL2A , PYROXD2 , SCD , SLC22A18 , SMIM29 , SNTB1 , SUMF1 , TNXB , VAMP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akt Up Mtor Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL4 , BDH1 , BLVRB , BMP7 , C1R , CAP2 , CD200 , CD248 , CPLX2 , DPYD , EFEMP1 , FAS , FBN1 , FEZ2 , FKBP10 , FMC1 , GAS1 , GNA14 , IL13RA1 , IL17RC , IRS1 , ITGA6 , JPH3 , KCNAB3 , KCNK3 , KCNN4 , LRRC1 , MAZ , MCM6 , MGAT4B , MLPH , MYB , NID1 , PDIA5 , PHLDA2 , PLA2G4A , PPP1R3C , PROM1 , RTN1 , S1PR3 , SASH1 , SATB1 , SLC18A1 , SLC37A4 , SLC7A5 , SNHG6 , TM4SF1 , TMEM97 , TP53I13 , TSPAN4 , VCAN , WEE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.lung.breast Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ADAMTS6 , ANGPTL4 , BMP6 , CALB1 , CTNNA2 , CXCL8 , DOCK4 , FNDC8 , HAS2 , HBEGF , HOXD11 , IGFBP3 , IL13RA2 , INHBA , ITGA2 , KCNC1 , KIF5A , KIF5C , LIF , MGLL , MMP1 , MMP10 , NAV3 , NELL2 , NRL , OSGIN1 , PDCD1LG2 , PDE2A , RREB1 , SEMA3B , SLCO4A1 , SLCO5A1 , SNAP25 , SNAP91 , ST3GAL6 , STC1 , TAGLN3 , TERT , TNFAIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc V6.5 Up Late.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL4 , ANXA1 , AVPI1 , BCL3 , BDH1 , BGN , C11orf24 , C16orf74 , CALML4 , CAVIN1 , CBR3 , CRMP1 , DYRK3 , E2F8 , EPOP , FAM169A , FBLN2 , GADD45A , GLI1 , ICAM1 , INHBA , KIF18A , KLF4 , LGALS3 , LOX , MANBA , MGP , MSC , MYC , NEFH , NR0B1 , NUPR1 , PCOLCE2 , PDGFC , PLEKHA4 , POLA1 , RASGRP2 , RASIP1 , S100A4 , S100A6 , SERPINE1 , SGK1 , SOCS3 , SPTBN4 , SULT4A1 , TCF15 , TIMP1 , TM4SF1 , TRIB3 , TTC39B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eif4e Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM9 , ALPK1 , ANGPTL4 , CTSC , DENND2D , DOCK1 , EPDR1 , FAS , FNDC3B , FRMD4B , FUCA1 , FZD3 , GALNT5 , IQGAP1 , ITPRIP , KLHL21 , LMO7 , LOXL1 , MYO10 , PLAU , SEMA4D , SGPP2 , SLC46A3 , SQOR , STRBP , SVIL , TPD52 , TRIM47 , UBA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat Bild Et Al Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN4 , AXIN2 , B4GALT1 , CALR , CASP4 , CD151 , CTSD , HMGB1 , KLHL15 , PALMD , RPS6KA1 , SIRPA , TAGLN , WIPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc J1 Up Early.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4GALT , ABCG1 , ADCYAP1R1 , ALX3 , AMPH , AQP3 , ARMH4 , BMP7 , C14orf132 , CARD19 , CD82 , COL26A1 , COQ8A , CXCL12 , DAB2 , EDARADD , EPHB3 , FGFRL1 , FOSL1 , GADD45B , GPRIN1 , GRINA , HES6 , IL15 , LOXL2 , METTL27 , MPP2 , MYB , NAGLU , NANOS1 , NEK2 , NSG1 , P4HA1 , P4HA2 , PHOX2B , PIK3R1 , PRXL2C , SERPINE2 , SESN3 , SHFL , SIL1 , SLC18A1 , SLC8B1 , STC1 , TLE6 , TMEM38A , TRIB2 , TXNDC16 , VSIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notch Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTS1 , AMPH , ATP1B2 , ATP8A1 , CALB1 , CAVIN2 , CDHR2 , CDKN1A , CLMN , COL4A1 , CPEB3 , CTF1 , DLGAP1 , FKBP9 , GRIN1 , GSN-AS1 , HMOX1 , HPCAL4 , HSPA1A , IFIT1 , KCNH2 , KCNK12 , KCNN4 , KLHL21 , KRT18 , LMO3 , MAP3K1 , MN1 , NPTX1 , NR6A1 , P2RX3 , P3H3 , PAIP2B , PIAS3 , PNPLA3 , PPP1R13L , PRKG1 , RAB23 , RAG2 , RFPL1 , RPS6KA4 , RRAD , RUNX2 , SLC30A10 , SLC9A7 , SPTBN2 , STAT2 , TENM1 , TGFB1I1 , TNS1 , TPPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snf5 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANPEP , APOE , ARMH4 , ATP1B1 , AURKB , C1R , C1S , COL26A1 , CORO1C , CXCR4 , DLK1 , DTL , FNBP1 , FNDC1 , GBP1 , HLA-B , IER5L , IFI44L , IFIT1 , IFIT2 , KIF20A , LAMB2 , LGALS3BP , LGR5 , MEST , NCAN , OTULINL , PLD4 , POFUT2 , PRPS1 , PRRX2 , PSMB8 , PSMB9 , RIPOR2 , SCG2 , SEMA4D , SLC1A5 , SLC2A3 , SP110 , SRPX , TAP2 , TAPBP , TGFB3 , TMEM267 , UBE2C , VAMP5 , ZNFX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yap1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8orf58 , CDK14 , DLX5 , FAM167A , FLOT1 , GTPBP3 , KCNK12 , MAML2 , MOCS2 , MSN , MYLK , SEMA3C , SHISA4 , SNAP23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclin D1 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANPEP , BLM , BMP1 , CEBPD , CHGA , CHRNA5 , COL4A2 , CTF1 , DCAF7 , DNASE2 , EPHA2 , FDXR , FHL2 , GADD45A , GALNS , HNRNPA0 , HSPG2 , HTR6 , ID1 , KCNAB2 , KIF22 , KLF4 , MKI67 , MSN , MYL6 , MYT1 , NCSTN , NSG1 , OPRD1 , PCSK7 , PDE2A , PLOD1 , PPIB , PTPN3 , RAB31 , RPS6KA1 , RRAS , SELPLG , SHC3 , SLC12A4 , SLC6A9 , SMOX , SMTN , SYN1 , TAGLN , TAP1 , TGFB1 , THY1 , TK2 , ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.lung Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , ADAMTS3 , ADCYAP1R1 , ANGPTL4 , CXCL8 , CYP2J2 , DCBLD2 , DOCK2 , DOCK4 , FNDC8 , GRIP2 , HBEGF , HOXD11 , HS3ST3A1 , HTR7 , IL13RA2 , INHBA , ITGA2 , KIF5C , LRIG1 , MMP1 , N4BP2L2-IT2 , NAV3 , NELL2 , NGF , NRP1 , OGDHL , PDCD1LG2 , RREB1 , SIGLEC15 , SLC18A1 , SLC6A11 , SLCO4A1 , SLCO5A1 , ST3GAL6 , TMEM158 , ZNF749 , ZNF821</t>
   </si>
   <si>
     <t xml:space="preserve">Egfr Up.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ACKR3 , ANK3 , APBB2 , ARMC9 , ASCL1 , BCL2 , BDH1 , BDKRB2 , BRIP1 , BST2 , CASP6 , CAV1 , CELSR2 , CENPU , CHN1 , COL9A3 , CTSH , CYBA , DCAF6 , DDX60 , DEPDC1 , DLC1 , DNAJC12 , DTL , E2F8 , ELOVL2 , ENPP4 , EPB41L2 , EPS8 , EZH2 , FANCL , GFRA1 , GRB10 , GREB1 , H2AC6 , H2BC9 , H4C8 , HEBP1 , HERC6 , ID1 , IFI44 , IFI44L , IFI6 , IGF1R , IRS1 , ITPRID2 , KIF11 , KIF5C , LTBP1 , MATN2 , MICB , MOCOS , MYB , NCAPG2 , NDC1 , NMU , PCYOX1 , PDLIM3 , PEG10 , PTBP2 , RASGRP1 , RCN1 , RPP25 , SGK3 , SLC27A2 , SLC39A8 , SMAD7 , TENM1 , TMEM106B , TMEM187 , TRIM24 , ZNF107 , ZNF273 , ZNF43</t>
+    <t xml:space="preserve">ACKR3 , ADD3 , APBB2 , ASCL1 , BCL2 , BDH1 , BDKRB2 , BRIP1 , CADM1 , CASP6 , CELSR2 , CENPU , CHN1 , COL9A3 , DCAF6 , DDX60 , DLC1 , DNAJC12 , DTL , E2F8 , ELOVL2 , EPS8 , EZH2 , FANCL , GRB10 , GREB1 , H1-2 , H2AC6 , H2BC9 , H4C8 , HEBP1 , ID1 , IFI44L , IRS1 , ITPRID2 , KIF11 , KIF5C , LTBP1 , MICB , MYB , NMU , NREP , PCYOX1 , PDLIM3 , PEG10 , PTBP2 , RCN1 , SGCG , SMAD7 , TENM1 , TRIM24 , ZNF273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il2 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL4C , BICDL1 , BTN3A3 , CBLN1 , CDKN1C , CHGB , CHRNB4 , CUX2 , DEPTOR , DLEC1 , EFNA4 , FUT9 , FZD3 , H2AJ , HKDC1 , ISL1 , JCAD , MACROH2A2 , MAP2K6 , MTARC1 , MYCT1 , MYLK , NAP1L2 , NUAK1 , PAK3 , PBXIP1 , PCSK5 , PIK3R3 , PLA2G4C , PLCD1 , PLCL1 , PRKG1 , PROM1 , RABEP2 , RASGRP3 , RIN2 , SCHIP1 , SCN3A , SEC14L2 , SEMA6D , SLC17A5 , SNAI2 , SNPH , SPATA1 , SYT1 , TAGLN3 , TRIB2 , TSPAN7 , UNC93B1 , ZNF695 , ZSCAN16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rela Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APBA2 , ATF3 , CDK5R2 , CDKN2B , CHST1 , CTF1 , DEPP1 , DLGAP1 , DUSP8 , DYSF , F3 , FGF2 , FOSL1 , GADD45B , HOOK1 , JUN , KCNQ4 , KLF6 , LGMN , LMO7 , MTMR11 , NOL4 , NOVA1 , PDE5A , PDK1 , PODXL2 , PPP1R15A , PRDM11 , PRKG1 , RIPK1 , RREB1 , SIRPB1 , TNC , TPMT , TRIM38 , VDR , ZFP36 , ZFP36L1 , ZFP37 , ZNF286A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Csr Early Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTSL4 , ARL4D , C14orf132 , CAVIN2 , CKB , COL1A1 , DENND11 , ERAP2 , HSPG2 , IFIT2 , KBTBD6 , MAB21L1 , MOSPD2 , NPHP3 , OTUD1 , PAN2 , PAPLN , PDE5A , PLCD1 , PRRT2 , SIX1 , SIX5 , SKP2 , SLC16A7 , SLC7A14 , SLC9A7 , SNPH , STAT2 , STOX1 , SULF1 , TENT5C , TRIM56 , WEE1 , ZNF33A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erbb2 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM9 , ADD3 , AMIGO2 , ANXA3 , ASCL1 , ATP8B1 , BCL2 , CASP6 , CENPE , CLIC3 , COL9A3 , DDX60 , DLC1 , DNAJB14 , DTL , FHL2 , FLNB , GREB1 , HSPB8 , IFI44L , IFIT1 , IRS1 , ITPRID2 , KIF5C , KRR1 , LAMB1 , LRIG1 , MAD2L1 , MBNL2 , MGP , MSH2 , MTCL1 , MYB , MYC , NCAPG , NRCAM , PEG10 , PLK4 , PTBP2 , RAB31 , RTCA , SMAD7 , SMC3 , STK17A , TIAM1 , TM4SF1 , TMED5 , TTK , TVP23B , UBA6 , ZBTB10 , ZNF84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hinata Nfkb Immu Inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CXCL8 , ICAM1 , IRF1 , NFKB1 , PTX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.df.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHR , ARHGAP26 , ARID3B , BCAM , BDKRB1 , CAMKV , CLDN1 , CNTFR , COPZ2 , CXADR , EPB41L4B , FANCE , FBN2 , GAP43 , GLIPR1 , H2BC9 , HOMER2 , HOXC8 , IGFBP3 , KLF15 , KLF4 , MALT1 , MMP25 , MPP3 , NGF , PAK3 , PAX5 , PCBP3 , PCLO , PDGFA , PER2 , PTPN14 , PXDC1 , RET , RNF122 , SEMA3C , SEMA6A , SEZ6L , SF3A2 , SIRPA , SLC30A3 , SMAD7 , STX3 , SYNE1 , SYP , TAGLN , TGFB3 , TNC , TNXB , VWA5A , ZFHX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esc V6.5 Up Early.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTSL4 , AGER , ARID3B , CELSR3 , CEP131 , CHD7 , CRAT , DEPTOR , DLC1 , DLL3 , ECE1 , ENG , ENPP2 , FBP1 , FGF5 , GDPD3 , GRM8 , HES6 , KCNC1 , KIF21A , LRIG1 , MAGI3 , MBOAT1 , MYB , NRL , OPRD1 , OTUD7A , PARP6 , PRICKLE1 , PSMB9 , RUNX1 , SASH1 , SATB1 , SH3RF1 , SIMC1 , SLC16A3 , SLC29A4 , SOX11 , SUV39H2 , SYT3 , SYTL2 , TERT , TMCO4 , TMEM158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb P107 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL , ANXA1 , ANXA4 , ARL1 , ARPC1B , BDH1 , CAP1 , CLIP4 , CRABP2 , CTSL , CXCL12 , DENND11 , EDN1 , ELOVL1 , GBE1 , GNG12 , H2BC4 , LACTB2 , MBNL3 , MYO1D , NFE2L1 , NMI , NRBP1 , NUCB2 , PAFAH1B3 , PANK1 , PEX3 , RHOU , S100A16 , SCD , STAT6 , STX7 , TLR2 , TPRG1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crx Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPK2 , ARHGAP10 , ARMH4 , B4GALT1 , BCAR3 , BICDL1 , BST1 , BUB1B , C16orf74 , CKMT1A , CSGALNACT2 , CUTALP , DUSP14 , FAAH , GPSM3 , HSPA1A , IER3 , JAG1 , MYLK , NAT1 , PAQR4 , PDIA5 , PFKFB2 , PLEKHF2 , PLPP2 , RAD51 , SGCG , SNTB2 , ST8SIA1 , STK17B , STRA6 , SUV39H2 , TNFAIP3 , UBTD1 , UBXN11 , VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pten Dn.v2 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABLIM2 , ARHGAP33 , BCOR , CCDC88C , CEBPA , COPZ2 , COQ8A , CORO2B , CRIP2 , ENTPD7 , EVA1B , FGFR3 , GPRC5C , LOXL1 , MAFK , MID1 , MRC2 , NECTIN3 , NIPAL3 , NREP , NUDT18 , OGDHL , RASA3 , RECQL4 , RIC3 , SCGN , SERPINH1 , SGK1 , SMAD7 , SPDL1 , SPHK1 , STMN1 , TACC2 , TERT , TGFBI , THEM6 , TRPM4 , ZNF124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegf A Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADARB1 , ARC , ARL4C , ATF3 , CABP1 , CACNB1 , CORO2B , DBH , DCX , DSG2 , DUSP8 , ECM1 , EMILIN1 , ENO2 , ENO3 , ENPP2 , EPHX1 , FEV , GLI1 , HS3ST1 , ICAM1 , ITGB4 , JCAD , KCNC3 , LMOD1 , MMP2 , MN1 , MTMR11 , MTSS1 , NEDD9 , NFKB2 , NINJ1 , OPRD1 , OPTN , PER2 , PHLDA1 , PLA2G4C , PLTP , PSMB8 , PTPRJ , RELB , RFPL1 , SDC4 , SEMA5A , TAGLN , THY1 , TNFSF12 , TNS2 , TUB , UBA7 , ZCCHC24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtor Up.n4.V1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM9 , ADARB1 , ANXA3 , APOL6 , ATF3 , BHLHE40 , CALML4 , CAMKV , CEBPB , CLIC4 , CLPB , CYTL1 , DDN , DNMT3B , EAF2 , FAH , FAS , FGF1 , GALE , GAS2L1 , GBE1 , GCH1 , GPRC5C , GRM2 , HERPUD1 , IDH3A , IL21R , IL7R , ITPR1 , LGMN , LIMA1 , MAP1A , MGAT4A , NIBAN1 , NQO2 , PTPRK , RIMS3 , RIT1 , SLC1A5 , SLC39A14 , SLC3A2 , SLC6A9 , SLC7A11 , SLC7A5 , SLCO4A1 , SQOR , SSTR2 , STX4 , TM6SF1 , TRIB3 , UGCG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gcnp Shh Up Late.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AURKB , BOK , CASP4 , CDC25A , CDCA7 , CLIC4 , CLIP4 , DLGAP5 , E2F8 , ELAVL2 , ELOVL2 , FANCC , FRMD6 , GBP2 , HIGD1A , IDH2 , INCENP , KIF2C , KIFC1 , LBR , LIG1 , LOXL2 , LUC7L3 , MBD2 , MCM10 , MCM6 , MIOS , MUC1 , MYB , NECTIN2 , NPAS1 , NPTX1 , PAN2 , PRC1 , RAG2 , SGO1 , SINHCAF , SIX4 , SLC29A1 , SMC4 , SQOR , SYT4 , TEAD3 , TMOD3 , TOP2A , TOP2B , VCAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc2 Eed Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLP1 , ARHGAP19 , ARRB2 , BUB1B , CDCA8 , CEP131 , CHST3 , CLPB , CSDC2 , CSPG4 , CXCL12 , DLK2 , ENO2 , FKBP5 , FOSL2 , FZD8 , GLI1 , GNAI2 , GSDMD , H1-10 , HMOX1 , IDH2 , INCENP , INKA2 , KIF4A , LIN7A , LMOD1 , MAP3K6 , MCM10 , MCM2 , MICALL2 , MYBL2 , PACS1 , PC , PDCD1LG2 , PEAK1 , PLAAT3 , PLXNB3 , PNPLA3 , POLD1 , PTGER2 , RECQL4 , RIPK1 , SCD , SEMA3B , SLC12A4 , SYN1 , TEDC2 , TRPM4 , UTRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Csr Late Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEX1 , BHLHE40 , CCND3 , CDC7 , CDCA8 , CHEK2 , CXCL12 , DCBLD1 , DRAP1 , EZH2 , FAM83D , FKBP1A , FOXM1 , GREM2 , HERC4 , HMGB1 , IGFBP3 , IL7R , ITGA6 , KIF22 , KRT18 , LTBP2 , MAZ , MCM3 , MMP3 , MT1X , MYBL2 , NSG1 , NUF2 , PBK , POLD1 , PRIM1 , PSMD2 , S1PR1 , SERPINB7 , SLC16A3 , TAGLN3 , TIMP1 , TMEM130 , TPM2 , TRPC4 , UBE2C , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mek Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA12 , AMIGO2 , APBB2 , ARMCX3 , ASCL1 , ATF3 , ATP8B1 , BCL2 , CASP8 , CHN1 , COL9A3 , DCAF6 , DDX60 , DLC1 , GDAP1 , GREB1 , H1-2 , H2AC6 , H2BC9 , H4C8 , HSPB8 , IFI35 , IFI44L , IFIT1 , INPP4B , ISG15 , ITPRID2 , KIF5C , LRIG1 , MGP , MOCS2 , MTCL1 , MYB , MYC , MYLK , NREP , OAS3 , PTBP2 , RAB29 , SGCG , SMAD7 , SP100 , SP110 , STXBP3 , TAP1 , TM4SF1 , TOP2B , USP18 , ZBTB10 , ZNF84</t>
   </si>
   <si>
     <t xml:space="preserve">Bmi1 Dn Mel18 Dn.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCA4 , APOE , AQP3 , BST2 , C1orf54 , CDH10 , COL14A1 , COL9A3 , CRLF1 , CTSH , CUX2 , CYTL1 , DDX60 , DLK1 , DOK5 , DPYD , DYNLT3 , EPHA4 , EVI5 , EYA4 , FCGRT , FOS , GAS7 , GNPTAB , GPR137B , H2BC21 , IFI6 , IL1R1 , IRF9 , LEPR , LMO3 , MAP7 , NEAT1 , NEFH , NMNAT2 , OGDHL , PCSK1 , PDE4B , PDE5A , PEG3 , PIGN , PNMA8A , PRDX2 , RBP4 , S100A4 , SECTM1 , SEMA3E , SLC16A4 , SOX2 , SPINT2 , SSPN , STON1 , TCEAL2 , TMOD1 , TSPAN1 , UNC5C , ZNF423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mel18 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOE , AQP3 , B3GAT1 , BAG3 , BST2 , C1orf54 , CDH10 , COL14A1 , COL9A3 , CRABP1 , CRABP2 , CUX2 , DDC , DDX60 , DLK1 , DOK5 , DPYD , EEF1A2 , EGR1 , EYA4 , FOS , FRMD4B , GAS7 , GPR137B , H4C8 , IFI6 , IFIT1 , IFIT2 , IL1R1 , IRF9 , MAF , MAP7 , MPPED2 , MVP , NMNAT2 , PDE4B , PDE5A , PEG3 , PHYH , PID1 , PLEKHA4 , PNMA8A , RBP4 , SEMA3E , SH3BGRL , SLC16A4 , SNCAIP , SOX2 , STK17B , STON1 , SULF1 , TCEAL2 , TENT5A , TMOD1 , TSPAN1 , UNC5C , ZCCHC24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akt Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADGRL1 , ALPL , ANGPTL4 , AXIN2 , BLVRB , C1R , C1S , CAP2 , CAV2 , CBS , CD248 , CNN2 , CSDC2 , DPT , DRAM1 , EFEMP1 , EFEMP2 , FAH , FANK1 , FAS , FBXO32 , FUT8 , GAS1 , GHR , HEBP1 , HTRA1 , IL13RA1 , IL17RC , IRS1 , ITGBL1 , ITIH5 , ITPKB , KCNK3 , KCNN4 , KLF2 , KRT15 , LIMD1 , MATN2 , MERTK , MOCOS , NCAM1 , NID1 , PADI3 , PDE4B , PDIA5 , PDLIM3 , PLEK2 , PLPP3 , PLTP , PPP1R3C , RAMP1 , RECK , S1PR3 , SASH1 , SATB1 , SCARA3 , SIX5 , SLC18A1 , SLC39A13 , SLC7A5 , SMARCD3 , SULT1E1 , TEC , TNFRSF19 , TNS2 , TP53I13 , TPD52L1 , TSPAN4 , ZFYVE21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Skm Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD14B , ADAMTS5 , APBB2 , ARHGEF26 , BCL2 , BEND5 , BEX2 , C1orf115 , C3orf80 , CA8 , CACNA2D3 , CALD1 , CAST , CC2D2A , CEMIP , CHPT1 , CLTCL1 , CPED1 , CRIM1 , CRIP2 , CRYBG1 , CXCL16 , CYP7B1 , DDIT4L , EPHX2 , FAM117B , FBLIM1 , FRMD5 , GABRA5 , GALNT12 , GBX2 , GPM6B , GPR37 , GPRASP2 , GPX7 , GRB10 , GRB14 , HMGA2 , ICAM3 , INAVA , JPH1 , KLRG2 , LAMB3 , LPAR3 , LRATD2 , MCTP2 , MOCOS , MREG , MSRB3 , MTARC1 , MTURN , N4BP2L1 , NHSL2 , NID1 , NPR3 , NR2F2 , NUDT11 , OGDHL , PADI2 , PAWR , PDGFRL , PHACTR3 , PIK3CB , PODXL , PPM1H , PPP1R3C , PROCR , PYROXD2 , RAB38 , RGS16 , RIPOR2 , SBDS , SCD , SERPINB8 , SETMAR , SH3GL3 , SLC6A15 , SLCO4C1 , SNTB1 , SPNS2 , SPRY1 , STAR , STBD1 , STING1 , STK33 , SYNJ2 , TBC1D30 , TENT5C , TEX15 , THBS4 , TMEFF1 , TMEM144 , TNFAIP8 , TONSL , TPD52 , TPD52L1 , VCL , ZDHHC23 , ZNF829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat Bild Et Al Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKRD28 , ARPC2 , ATP10D , EFR3A , GCLM , GRID1 , IER5 , IL1A , IL1RAP , IRAK2 , ISCU , LNPEP , MACROH2A1 , NBPF10 , PLAGL1 , PTHLH , SECISBP2 , SMURF2 , STARD13 , TNFAIP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pten Dn.v2 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3 , ANGPTL4 , ANXA3 , APOL3 , ARHGDIB , ARL4C , ARVCF , ATP2B2 , BIRC3 , CA5B , CASP4 , COL13A1 , CPA4 , CSF1 , CUEDC1 , CXCL8 , DGCR11 , EMP1 , HSPB8 , HTR1B , IL1B , IL32 , IL4R , IL7R , JUN , KRT15 , LAMA3 , LIPG , LOXL2 , MIR22HG , NAV3 , NID2 , NNAT , NOL4 , OSGIN1 , PC , PLAU , PLPP3 , PTGS2 , RHBDF1 , RTN1 , SATB1 , SECTM1 , SLC2A4 , SLC66A3 , SPOCK1 , THBS4 , TIGAR , TMEM127 , TP53I3 , TRIB2 , VAMP5 , ZMAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raf Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABAT , ABCA12 , ACKR3 , ADGRG1 , APBB2 , ARMC9 , ASCL1 , BAG3 , BCL2 , CA12 , CAV1 , CELSR2 , CLIC3 , COL9A3 , CRABP1 , CRYBG1 , DKK1 , DLC1 , DNAJC12 , ELOVL2 , EPB41L2 , EPB41L4B , FOS , GDAP1 , GFRA1 , GHR , GREB1 , H4C8 , HSPB8 , ID1 , IGF1R , IGFBP4 , IGFBP5 , INPP4B , IRS1 , JAK2 , KITLG , KYNU , LRIG1 , MED13L , MGP , MICB , MYB , MYO10 , OSTM1 , PALLD , PCSK6 , PDGFRL , PLK2 , PMP22 , PPM1E , PPP1R3C , PTBP2 , PXDN , RASGRP1 , RND3 , ROBO1 , SH3BGRL , SHROOM2 , SLC39A8 , SMAD7 , SNAP23 , SOX4 , SOX9 , SYTL2 , TBC1D30 , TFPI , TGFB2 , TM4SF1 , TRPS1 , ZHX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat.100 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN1 , CHODL , CRYM , DBNDD1 , DKK1 , DNAJC3 , DUSP4 , EEF1A2 , EFEMP1 , ENO2 , ENPP2 , FLVCR2 , GAD1 , GADD45G , GCNT1 , IRS1 , ITGA9 , RBP1 , RUNX1 , SLC7A8 , TBX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snf5 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABI3BP , APOE , ATP1B1 , AURKB , BUB1 , C1R , C1S , C3AR1 , CD109 , CD68 , CIP2A , CKAP2 , COL26A1 , CORO1C , CXCR4 , DHRS1 , DLK1 , DTL , EGR2 , EVI2A , EVL , FBLN1 , FBXO6 , FGF18 , FNBP1 , FNDC1 , GBP1 , HLA-B , IER5L , IFI44L , IFIT1 , IFIT2 , KIF20A , LAMB2 , LCP1 , LGALS3BP , MCM5 , MEST , MMP14 , MSX1 , NCAN , NCAPG2 , OTULINL , PLCE1 , POFUT2 , PRPS1 , PRRX2 , PSMB8 , PSMB9 , RIPOR2 , SCG2 , SEMA4D , SLC1A5 , SLC2A3 , SOX2 , SP110 , SRPX , TAP2 , TAPBP , TGFB3 , TMEM267 , UBE2C , VAMP5 , ZNFX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Src Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL4 , ADA , ARSJ , ATAD2 , CDCA7 , CENPH , CERKL , COL8A1 , DEPP1 , DGCR11 , DISP2 , DPYD , E2F8 , EMB , EZH2 , FANCL , FRMD4B , GFRA3 , GINS1 , GRID1 , HS3ST3A1 , IFI6 , IFIT1 , IL7R , IRAK2 , IVL , LIG1 , LINC00842 , LYPD3 , MAP3K6 , MCM3 , MCM4 , MCM5 , MEGF6 , MGARP , MIR17HG , MMP1 , MMP10 , MMP3 , MN1 , NBEAL1 , NID2 , NOL12 , NRP1 , PAK3 , PC , PCDH19 , PHLDA2 , PLAT , PLK4 , PTBP2 , RACGAP1 , S1PR3 , SH3TC2 , SLC7A14 , SNX32 , ST8SIA2 , STK17B , SUV39H2 , TMOD1 , UHRF1 , ZNF135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crx Nrl Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGRA2 , ADRB2 , ASPH , C14orf132 , CAMK2B , CAP1 , CHRNA3 , CHRNB4 , CITED1 , CLIC4 , CPLX2 , CTBS , ECE1 , EGR1 , ELOVL2 , ERMAP , FMN1 , FRMD6 , GGACT , GREB1 , GSDME , HEBP1 , HS3ST1 , INPPL1 , INSM2 , KIF5C , LRRC4 , METRN , NECTIN3 , NFKB1 , NR4A1 , NSG1 , NTN4 , PAM , PDIA3 , PLEC , QSOX1 , RASGRF2 , RBP4 , RREB1 , SDC4 , SGCE , TMEM106B , TMEM158 , TNC , TNFRSF12A , TSPAN33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cahoy Oligodendrocutic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHR , AP5Z1 , CCN2 , CLN8 , CRIP2 , CRYM , CSDC2 , DKK3 , DMRTA1 , DOCK10 , EFHD2 , EVI2A , FAM89A , FBP1 , FIGN , FSTL1 , GAB3 , GNG8 , KIAA1958 , LHFPL6 , MAP3K15 , MYRF , NRP1 , P4HA2 , PHLDB1 , PLLP , PRKAG2 , PSTPIP2 , RNASEH2B , RNF122 , SEMA3D , SEMA5A , SERINC5 , SPEG , TENM1 , TSPAN2 , UGT8 , ZNF536</t>
+    <t xml:space="preserve">APOE , AQP3 , CDH10 , COL9A3 , CRLF1 , CUX2 , CYTL1 , DDX60 , DLK1 , DPYD , DYNLT3 , EVI5 , FCGRT , GNPTAB , GPR137B , H2BC21 , IL1R1 , LMO3 , MXRA5 , NEFH , NMNAT2 , OGDHL , PDE4B , PDE5A , PEG3 , PIGN , PRDX2 , PROM1 , S100A4 , SECTM1 , SEMA3E , SLC16A4 , SPINT2 , SSPN , TCEAL2 , TMOD1 , UNC5C , ZNF423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lef1 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2 , AKR1C3 , AP1M2 , ATP1B1 , ATP8A1 , BDKRB2 , BTN3A3 , CCN2 , CRYBG1 , CYP2J2 , ERAP2 , GALNT12 , GDPD3 , GRB14 , ID1 , KCNQ1 , LGR5 , LIMCH1 , MANBA , MANSC1 , MFGE8 , MRNIP , MTARC1 , MVP , NUDT18 , NUDT6 , OAS3 , PAPSS2 , PDGFC , PDGFRL , PIAS3 , PLOD2 , PROS1 , RAB26 , RAB27B , RAC2 , RBM47 , RNF144A , SAMD9 , SH3BGRL , SLC22A18 , SORL1 , TLR3 , TM4SF1 , TPM1 , TRPM4 , USP18 , ZNF711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclin D1 Ke .V1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHR , ATXN1 , BIRC2 , CDK6 , CDKN1A , CDKN2A , CEBPD , CHRNA5 , CHRNB4 , COL18A1 , DAP , DCAF7 , DNASE2 , DUSP4 , DUSP5 , EPHA2 , FAM3C , FHL2 , FOSL2 , GLI1 , GNAI2 , HGFAC , HSF4 , HSPG2 , HTR6 , ID1 , KCNAB2 , KIF22 , KIFC1 , KLF4 , MPHOSPH6 , NRG1 , NTN3 , PLOD1 , POLD1 , PPIB , PRPH , PTPN3 , RAB31 , RRAS , RUNX1 , S100A2 , SLC35D1 , SMTN , TGFBR2 , THY1 , TROAP , ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gli1 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL6 , CD2AP , ESYT1 , RUNX1 , SPECC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapa Early Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXL , CACNB4 , CCDC85B , CIT , CNKSR2 , COBLL1 , COL9A2 , CRIP2 , CRMP1 , DDN , DUSP14 , ENG , EPHB4 , FLOT1 , GALNS , GFRA2 , GPR12 , GRIN1 , GRM2 , GRN , HLA-E , HSPA1A , IGFBP3 , KCNQ1 , LGALS3BP , LMNA , MAP1A , MGST2 , MID1 , MYCN , NAGPA , NCAPH , NFE2L1 , PHYHIP , PINK1 , PLEKHO2 , PLXND1 , PRELP , PSD , PTCH1 , SELPLG , SF3A2 , SMAD9 , SNTB1 , TROAP , TSPAN4 , WFS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2 , DNA2 , EPHX1 , FBP1 , FXYD6 , GAB3 , GCLM , GRM8 , ID1 , MAN1B1 , MANSC1 , MCM6 , MCM7 , MYC , PALMD , PCDH10 , PCNA , PLEKHA6 , PLXNB2 , PMM1 , PRIM1 , SLC35B2 , SNAP25 , SPOCK1 , STMN1 , TIMELESS , TMEM54 , UBE2T , ZFP30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cahoy Neuronal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMER3 , BCL11B , CALB1 , CALN1 , CAMK2B , CAMKV , CBLN4 , CELF4 , CKMT1A , CNTNAP4 , ENO2 , GREM2 , LAMP5 , METRN , MYT1L , NAPB , NEFM , PPFIA2 , SCG2 , STX1A , STXBP1 , SYT1 , SYT13 , SYT4 , SYT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atf2 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABLIM3 , ADM2 , ALX3 , ARSJ , CBX5 , CD8A , CEBPA-DT , CENPU , CLDN1 , CORO2B , DTL , ENDOG , FOXM1 , FSD1 , GDF10 , GNA14 , HOXD11 , INPP4B , KCNAB3 , KCNK3 , LIG1 , LYPD1 , MAP2 , MMP1 , NCAPG , NEDD9 , NEFM , NNAT , NRXN2 , PACS1 , PAFAH1B3 , PCDH1 , PLAU , PLCB4 , PLK4 , PLXNB3 , PODXL , POLD1 , RAD51 , RBP1 , S100A4 , STEAP1B , STRA6 , TRIM9 , TSSK2 , UPP1 , WNT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gcnp Shh Up Late.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN4 , ACVR1 , AGER , AGTRAP , AMOTL2 , ANXA7 , CCDC71L , CDCP1 , CNN1 , CNN2 , DLX5 , EDN1 , EPB41L4B , EPHB6 , FAM111A , FCGRT , FRRS1 , GNPTAB , H2AJ , HSPG2 , IKBKG , IL4R , NACC2 , NBEAL2 , NECAP2 , NMI , NPTN , PSMB8 , PTPRJ , S100A11 , S100A13 , S1PR1 , SAT1 , SLC25A45 , SLC30A3 , STX1A , STX3 , TGFB3 , TMEM214 , UBE3C , VEGFC , WLS , WNK2 , ZDHHC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pgf Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA8 , ADAM9 , AGA , AMPH , ARMCX2 , ATP13A3 , CCPG1 , CD2AP , CRYZ , DCP2 , DNAJC3 , DNASE2 , GPR37 , GRB14 , IL6ST , ITGA2 , KLRG1 , LRRC17 , LTBP1 , MAFK , MMP10 , MTM1 , NAT1 , NEK7 , NRCAM , NUCB2 , PGAP1 , PLA2G4A , RASGRP3 , RIPK2 , RNF6 , SAT1 , SGMS1 , SMC3 , SMC4 , SOCS5 , STAM2 , STXBP3 , SULF1 , SYNE2 , THSD7A , TMED5 , TWF1 , UFL1 , UGP2 , VCAN , ZC3H14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtor Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADORA2B , ALPK2 , ATF3 , BACH2 , BDH1 , BLK , CAPN12 , CDKN2B , GCH1 , GSDME , HMOX1 , IDH3A , IFI35 , IFIT1 , IFIT2 , IL27RA , LGALS3 , LIPG , MCM6 , MGARP , NABP1 , NEIL3 , NIPSNAP3A , NKAIN1 , NQO2 , NTSR1 , PAFAH2 , PCNA , PDK1 , PFKP , PLAT , PTPN14 , PYGL , RCOR2 , RD3 , SP100 , STMN1 , TESC , TMEM97 , TNFRSF12A , UBE2C , USP18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pkca Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM11 , ADGRB1 , BEX1 , CD44 , CENPF , CHST1 , CKAP4 , COL25A1 , CYGB , EAF2 , EXT1 , GASK1B , GBP1 , GLDC , HOXC8 , HS3ST3A1 , KANK2 , MAGT1 , MALAT1 , MAP3K6 , MBOAT1 , MSC , NFKBIZ , NUCB2 , PDGFC , PLAU , PROCR , RFX2 , SEMA6C , SHF , SLC30A1 , SNTB2 , TLR2 , TNFRSF12A , TWF2 , ZBTB7A , ZDHHC1 , ZEB2</t>
   </si>
   <si>
     <t xml:space="preserve">Hinata Nfkb Matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">FN1 , KRT7 , MMP1 , MMP14 , RND3 , SERPINE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc J1 Up Early.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMH , ANGPTL4 , ANXA1 , ANXA3 , ANXA5 , ATF5 , BCL3 , BMP1 , C11orf24 , C16orf74 , CCN1 , CEBPD , CNN1 , CORO2A , CRYL1 , DNAJC30 , DPYSL5 , EDN1 , EGR1 , EPOP , FGF18 , GAP43 , GBP1 , GBP2 , GBX2 , H2BC4 , HASPIN , ID1 , IGFBP3 , KLF4 , LAMC2 , LIMS2 , LPP , MAPT , MYC , NOL12 , NUDT11 , PAFAH2 , PPCS , PPP2R3A , RAB33A , RAMP1 , RELB , REM2 , RNASE4 , RNASEL , RPP25 , SERPINE1 , SLC30A1 , SOCS3 , STAT3 , SYT12 , TAGLN , TCF15 , TNFRSF12A , TRAIP , TRIB3 , TRPS1 , UBA7 , VWA5A , ZFP36 , ZFP36L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc J1 Up Early.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4GALT , ABCG1 , ADCYAP1R1 , ADM , ADTRP , AMPH , AQP3 , BMP7 , C14orf132 , CARD19 , CD68 , CD82 , CDHR1 , COL26A1 , COLQ , COQ8A , CORO2A , CUBN , CXCL12 , DAB2 , DSCAM , ECE2 , ENPP5 , EPHB3 , ETFBKMT , FGF14 , FGFRL1 , FOSL1 , GADD45B , GADD45G , GPRIN1 , GRINA , HES6 , IL15 , LOXL2 , METTL27 , MPP2 , MYB , NAAA , NAGLU , NANOS1 , NEK2 , NSG1 , P4HA1 , P4HA2 , PDGFRB , PHOX2B , PIK3R1 , PLPP3 , PRXL2C , RASL11B , SERPINE2 , SHFL , SIL1 , SLC18A1 , SLC8B1 , STC1 , TLE6 , TMED3 , TMEM38A , TRIB2 , TSPAN1 , TXNDC16 , VSIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myc Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGER , AKR1C3 , ANGPTL4 , BCAR1 , C16orf74 , C1orf54 , CDCA8 , DEPP1 , DUSP18 , GBP3 , GINS1 , GPRC5A , GRHL1 , GRID1 , H2AC6 , HEG1 , IL1R1 , IRAK2 , KLF12 , KRT80 , LINC00173 , LINC00842 , LMNTD2-AS1 , LMTK3 , LYPD3 , MAP3K6 , MCHR1 , MEGF6 , MGARP , MMP1 , MMP3 , MMP9 , MN1 , MTMR11 , NBEAL1 , NID2 , NR6A1 , NRP1 , PAK3 , PBX4 , PC , PDZD2 , PLAT , PLEKHA2 , PODN , PRRT2 , PSMC3IP , RAB4B , REC8 , RNASE4 , SAMD9 , SPOCD1 , SPTB , TEP1 , TGM2 , TLR2 , TP53INP1 , TRIM56 , TRPM4 , WNT5B , WNT9A , ZNF334</t>
+    <t xml:space="preserve">FN1 , MMP1 , SERPINE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapa Early Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADGRE5 , AEBP1 , ANK1 , ANPEP , ASPH , ASTN2 , C2orf72 , CBX5 , CCDC88C , CEBPA , CHD5 , COL6A1 , CTSD , DLX5 , FGFR2 , FKBP1A , GNG12 , GREB1 , GRPR , HIVEP1 , HOXD10 , ITGA5 , L1CAM , NINJ1 , NRL , NUCB1 , OLFML2A , PAQR4 , PDE2A , PDE5A , PLEKHA6 , PRKCG , SHC3 , SLIT1 , SSH1 , ST8SIA3 , STUM , TCTA , TIMP2 , TRIM38 , VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.breast Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , ADAMTS20 , ADAMTS5 , ALOX12B , CRABP1 , DENND2D , ELMO1 , ENTPD5 , FGFR3 , FGGY , FRAS1 , GP1BB , GRIP2 , HCN2 , KCNQ3 , MAML3 , MTHFR , NOS1 , NPR1 , PAQR6 , PGGHG , PPM1E , PTENP1 , RUNDC3B , SLC30A3 , SLC9A7 , SOBP , SPTBN2 , SYNDIG1 , TEX15 , TLR6 , TRIM9 , XYLB , YPEL1 , ZNF37BP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gli1 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGFBP6 , LMO7 , M6PR , NPHP1 , TMOD3 , WEE1</t>
   </si>
   <si>
     <t xml:space="preserve">Bmi1 Dn.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">BLVRB , BST2 , C1orf54 , CHMP2B , CITED1 , COL9A3 , DDX60 , DNAJC12 , DOK5 , DPYD , DYNLT3 , EEF1A2 , EGR1 , EPHA4 , FOS , GAS7 , H2BC21 , H4C8 , IFI44L , IFI6 , IL1R1 , KLF15 , LMO3 , LPAR2 , MSX2 , MVP , NMNAT2 , PADI2 , PDE4B , PDE5A , PEG3 , PID1 , PIK3R3 , PLEKHA4 , PNMA8A , PRDX2 , PRPH , S100A4 , SEMA3E , SH3BGRL , SNAI1 , SOX2 , SSPN , STON1 , SUCLG2 , TCEAL2 , TNNT1 , TRPS1 , TSPAN1 , TSPO , ZNF423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mtor Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ACKR3 , C1QTNF4 , C1R , C2 , COQ8A , CSDC2 , CSGALNACT2 , DDIT3 , DNASE2 , DNMBP , DUSP1 , EFEMP2 , FAH , FANK1 , FBXO32 , H1-10 , HSD17B1 , HTRA1 , ISL1 , ITIH5 , KCNC1 , KCNK3 , KLF2 , KRT15 , LIFR , LTBP1 , MED12L , METTL27 , MYC , MYCN , NCAM1 , NELL2 , NFXL1 , OLFML3 , OSGIN1 , OSMR , PALD1 , PDE4B , PDGFA , PDIA5 , PDLIM3 , PLTP , PPP1R3C , PRSS23 , RBP1 , RRM2B , S1PR3 , SASH1 , SCARA3 , SIX5 , SLC12A4 , SLC2A4 , SLC33A1 , SLC39A13 , SLC44A1 , SMARCD3 , STX1A , SULT1E1 , SYN2 , TH , THBS3 , TNIP2 , TNS2 , TSPAN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cahoy Neuronal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMER3 , BCL11B , CALB1 , CALN1 , CAMK2B , CAMKV , CBLN4 , CELF4 , CELF6 , CKMT1A , CNTNAP4 , CPNE4 , DYNC1I1 , ENO2 , EPHA7 , GABRA5 , GPR22 , GREM2 , JPH4 , KCNIP4 , KIAA0319 , LAMP5 , METRN , MYO5B , MYT1L , NAPB , NEFL , NEFM , NELL1 , NRGN , PPFIA2 , SCG2 , SH2D5 , STX1A , STXBP1 , SYT4 , SYT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Csr Late Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEX1 , BHLHE40 , BIRC5 , CCDC34 , CDC7 , CDCA8 , CDH2 , CDK1 , CHEK2 , CKAP2 , CLSPN , CRISPLD2 , CXCL12 , DCBLD1 , DRAP1 , EZH2 , FAM83D , FANCA , FEN1 , FKBP1A , FOXM1 , GREM2 , HERC4 , HMGB1 , IGFBP3 , IL7R , ITGA6 , KCNC4 , KIF22 , KRT18 , LTBP2 , MAZ , MCM3 , MET , MMP3 , MT1X , MT2A , MYBL2 , NDC1 , NETO2 , NSG1 , NUF2 , PARP11 , PBK , POLD1 , PRIM1 , SERPINB7 , SLC16A3 , TAGLN3 , TIMP1 , TMEM130 , TOMM34 , TPM2 , TRPC4 , UBE2C , UHRF1 , VEGFC , ZNF367 , ZWINT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camp Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK5 , AKAP12 , ANXA1 , ARHGAP5 , ATP2B4 , ATP8A1 , BACH2 , BIRC3 , BSN , CAMK2D , CASP7 , CDCA7L , CHST2 , DAG1 , DCAF6 , DDAH1 , ENO2 , ESYT1 , FOSB , FSTL1 , FUT8 , GEM , GLS , GNG12 , IGFBP5 , IL4R , IL7R , JARID2 , KBTBD11 , KCNN4 , LINC01089 , LRRFIP1 , MAP2 , MBD2 , MYO5B , NAP1L2 , NFATC2 , NFKB1 , NUDT11 , PAK3 , PALLD , PAM , PCLO , PHLDB1 , PINK1 , PLS3 , RAB31 , RNF138 , RRAD , RREB1 , SEL1L3 , SEPTIN11 , SLC2A3 , SLC35E2A , SNRPA , STXBP1 , SVEP1 , SYPL1 , SYT11 , THSD7A , TIMP2 , TMBIM1 , TMEM97 , TMSB4X , TUBB2B , UBE2QL1 , UNC79 , ZFP36 , ZMIZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc J1 Up Late.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMH , ANGPTL4 , BCL3 , BHLHE40 , CALML4 , CAVIN1 , CORO1A , CRMP1 , DDC , DLC1 , DNASE2 , DOC2A , E2F8 , EDN1 , EGR1 , ENDOG , ERCC6L , EVC , FGF18 , FOXN4 , GAP43 , GBX2 , GLI1 , GNG3 , HELB , ICAM1 , INA , KLF4 , MMP11 , MYC , NEFH , NIBAN1 , NNAT , NR0B1 , PASK , PCOLCE2 , PDGFC , PHLDA2 , POLA1 , POLE , PPCS , RASGRP2 , RPP25 , RPP40 , SLC1A5 , SLC27A2 , SMARCD3 , SNTB2 , SOCS3 , SULT4A1 , TAF13 , TBCE , TCF15 , TET1 , TRAIP , TRPS1 , TUBB2B , VEGFC , ZFP62</t>
+    <t xml:space="preserve">BLVRB , CHMP2B , COL9A3 , DDX60 , DNAJC12 , DPYD , DYNLT3 , EEF1A2 , H2BC21 , H4C8 , IFI44L , IL1R1 , KLF15 , LMO3 , LPAR2 , MVP , NDRG2 , NMNAT2 , PADI2 , PDE4B , PDE5A , PEG3 , PID1 , PIK3R3 , PLEKHA4 , PRDX2 , PRPH , S100A4 , SEMA3E , SH3BGRL , SSPN , TCEAL2 , TSPO , ZNF423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nrl Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIB , C14orf132 , CASP7 , CDT1 , CLIC1 , CLIC4 , CLPB , CPLX2 , CTBS , DYSF , ECE1 , ELK3 , ELOVL2 , FKBP9 , GREB1 , GSDME , INPPL1 , KIF5C , METRN , MYOCD , NFKB1 , NSG1 , PLEC , PLEKHH2 , QSOX1 , RASGRF2 , SLC8A3 , SOCS3 , TMED9 , TMEM158 , TOM1L2 , TSPAN33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il21 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ABCC8 , BCL6 , BOK , CPA4 , CT62 , CXCL12 , DLX6 , DPYSL4 , ECM1 , GABRB3 , GIPR , GRIA4 , HEG1 , KCNC3 , LIF , MAFK , MMP25 , MPZ , MUC1 , MYOZ3 , NUDT11 , OLFM1 , P3H3 , PAIP2B , PAQR6 , PCDHA5 , PCSK7 , PLPP2 , PTPRO , PTX3 , SEMA7A , SLC12A8 , SLC29A2 , SLC7A5 , SLCO5A1 , ST8SIA3 , TBC1D19 , TEAD3 , TLR3 , TLR6 , TPBG , TPST2 , VDR , ZNF749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cahoy Astrocytic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADCYAP1R1 , ADORA2B , BMPR1B , CORO1C , CYP7B1 , ELOVL2 , FGFR3 , FRMD5 , IL17RD , IMPA2 , MFGE8 , NCEH1 , NIPAL3 , NRARP , PAK3 , PANK1 , PAPSS2 , SCG3 , SEMA3E , SLC1A2 , SLC30A10 , SLC6A11 , SLC7A10 , SLC7A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wnt Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ABCC3 , ACVR1B , ADAM12 , ADAM19 , APC2 , CD44 , CNTN1 , DDX25 , FAAH , FOXN3 , FZD7 , GFAP , GGNBP1 , GRM8 , HAND1 , HLA-B , IGFBP6 , ISG15 , LGALS3BP , MMP3 , NAGK , NGEF , NGF , OLFM1 , PCDH7 , PCDHA10 , PHOSPHO2 , PIGN , PXMP2 , RAI2 , SDSL , SEPTIN6 , SINHCAF , SLC22A18 , STC1 , SYT11 , TFR2 , TLR6 , USP18 , VIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pdgf Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2P2 , AOX1 , ARSL , ASPH , BCL3 , BHLHE40 , C2 , CBLN1 , CRABP1 , CTNND2 , CYB5R1 , DNMBP , FBN2 , GABPB1-IT1 , GPR39 , IL7R , JUN , KIAA1217 , KLF5 , LIMK1 , LRRTM2 , LTBP1 , MXRA5 , PAFAH2 , PLAT , SEMA3C , SLC22A18 , SLC8A2 , TNS2 , TRAIP , ZBTB7A , ZNF33B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc1 Bmi Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ACE , ANKRD46 , ARL4C , ATP1B2 , CDK6 , CHD7 , COLEC11 , CXCL8 , DCP2 , DELEC1 , DNAJC12 , EDN1 , EOGT , ERAP2 , FCHO1 , GNG3 , GNL3LP1 , GRM2 , H3C12 , HIC2 , HSPB7 , KIF5A , MAFK , MMP25 , MYT1 , OSGIN1 , PAIP2B , PAX5 , PELI2 , PINLYP , RGS16 , RIC3 , RIPK4 , RREB1 , SLC1A2 , SLC6A15 , SLCO4A1 , STUM , TNFAIP3 , TSPAN7 , ZBTB10 , ZNF423 , ZNF91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc2 Suz12 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ACE , ALDH1A3 , ANKRD46 , ARL4C , ATXN1 , BTN3A2 , C1orf21 , CA11 , CALML4 , CHST11 , CNPY4 , CTSS , DCBLD2 , DCP2 , DNAJC12 , ECM2 , EDN1 , ERAP2 , FCHO1 , GAB2 , HBEGF , HR , ITGA2 , KCNN4 , LYPD1 , MYT1 , OSTM1 , PAQR6 , PCBP3 , PINLYP , POU2F1 , PSMB8 , REST , SEMA3E , SETBP1 , SLC6A15 , SLC6A9 , SLCO4A1 , SPTB , TET3 , TOM1L2 , TRIM58 , ZNF208</t>
   </si>
   <si>
     <t xml:space="preserve">Hoxa9 Dn.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ADM , ARRB1 , ATAD2 , ATF5 , BHLHE40 , CBS , CDC45 , CDT1 , COCH , COL9A3 , DLX5 , E2F8 , EGR1 , EPB41L2 , EPS8 , EXOSC5 , FANCG , FANCI , FANCL , FKBP5 , FZD6 , GINS1 , GINS4 , GPM6B , GRB10 , H1-10 , HACD1 , HELLS , INAVA , ITGA4 , ITGB5 , LRRC37A4P , MACROD1 , MCM10 , MCM3AP-AS1 , MICB , NDC1 , NOTCH2 , NPR3 , NPTX2 , NRGN , ORC1 , PDK1 , PFAS , PLAGL1 , PLK4 , PSIP1 , RAB33A , RGS16 , RNASEH2A , RNF144A , SERINC5 , SLC1A5 , SLC29A1 , SLC29A2 , SLC2A3 , SMAGP , SPON2 , SPP1 , SSR3 , TAF4B , TBC1D30 , TEX15 , TOMM34 , TRIB3 , ZNF395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akt Up Mtor Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4GALT , ADGRG1 , ADORA2B , ANGPTL1 , BMP8B , C3orf52 , CALCB , CARD19 , CDKN2B , CRLF1 , CXCL16 , DSCAM , DUSP1 , DUSP8 , EDN1 , FBXL15 , FBXO6 , GCH1 , GIPC1 , GLDC , GPX8 , H4C8 , HBEGF , HCN2 , HIC2 , IFIT1 , IL1R1 , KCNK5 , KLF6 , LAMC2 , LGMN , LYPD1 , MAN2B2 , METRNL , MGARP , MPP2 , MVP , MYCN , MYO5B , NEU1 , NFKB2 , NIBAN1 , NOL12 , PLAGL1 , PLAT , PLK2 , PON2 , PTPRJ , PYGL , RAB3IP , RUNDC3A , SEC14L2 , SLC39A8 , SLC44A1 , SPHK1 , TESC , TGIF1 , TMCC3 , TNFRSF12A , VAMP5 , VANGL2 , VAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erbb2 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM9 , AMIGO2 , ANXA3 , ASCL1 , ATP8B1 , BCL2 , BST2 , CASP6 , CAV1 , CLIC3 , COL9A3 , DBF4 , DDX60 , DEPDC1 , DLC1 , DNAJB14 , DTL , FBXO5 , FHL2 , FLNB , GFRA1 , GREB1 , HERC6 , HSPB8 , IFI44 , IFI44L , IFI6 , IFIH1 , IFIT1 , IGF1R , IRS1 , ITPRID2 , JAK2 , KIF5C , LRIG1 , MAD2L1 , MATN2 , MBNL2 , MGP , MSH2 , MTCL1 , MYB , MYC , NCAPG , NMRK1 , NRCAM , PEG10 , PLK4 , PTBP2 , RAB31 , RAD51AP1 , RASGRP1 , RBBP8 , RMI1 , RNF138 , SMAD7 , SMC3 , STK17A , TFPI2 , TIAM1 , TM4SF1 , TMED5 , TOPBP1 , TTK , TVP23B , UBA6 , ZNF107 , ZNF43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akt Up Mtor Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGPAT5 , ANGPTL4 , BDH1 , BLVRB , BMP7 , C1R , CAP2 , CAV2 , CBS , CD200 , CD248 , COL5A2 , CPLX2 , DPT , DPYD , EFEMP1 , FAS , FBN1 , FEZ2 , FKBP10 , FMC1 , GAS1 , GNG11 , IL13RA1 , IL17RC , IRS1 , ITGA6 , ITPKB , JPH3 , KCNAB3 , KCNK3 , KCNN4 , LIMD1 , LRRC1 , MAZ , MCM6 , MERTK , MGAT4B , MLPH , MOCOS , MSX1 , MYB , NID1 , PDIA5 , PHLDA2 , PLEK2 , PLPP3 , PPP1R3C , RAMP1 , RTN1 , S1PR3 , SASH1 , SATB1 , SLC18A1 , SLC7A5 , SMARCD3 , TBCE , TEC , TM4SF1 , TMEM97 , TNFRSF19 , TP53I13 , TSPAN4 , VCAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.lung.breast Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , ADAMTS6 , ANGPTL4 , BIRC3 , CALB1 , CTNNA2 , CXCL8 , DOCK4 , HAS2 , HBEGF , HOXD11 , HSD17B2 , IGFBP3 , INHBA , ITGA2 , KCNC1 , KCNK15 , KIF5A , KIF5C , LAT2 , LDB3 , LIF , MGLL , MMP1 , MMP10 , MMP9 , NAV3 , NELL2 , NPPB , NRL , OSGIN1 , PDCD1LG2 , PDE2A , PTGS2 , RBP4 , RREB1 , SEMA3B , SLCO4A1 , SLCO5A1 , SNAP25 , SNAP91 , ST3GAL6 , STC1 , TAGLN3 , TBX3 , TERT , TNFAIP3 , TRAF1 , TSPAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notch Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGRG1 , AMPH , ASB9 , ATP1B2 , ATP8A1 , CA5B , CALB1 , CAVIN2 , CCNA1 , CDHR1 , CDKN1A , CHST8 , COL4A1 , CPEB3 , CRYM , CTF1 , DGKI , DPT , EPN3 , FKBP9 , GDNF , GNG11 , GRIN1 , HABP4 , HPCAL4 , IFIT1 , INAVA , KCNH2 , KCNN4 , KLHL21 , KRT18 , LMO3 , MAP3K1 , MN1 , NME5 , NPTX1 , NPTXR , NR6A1 , P2RX3 , P3H3 , PAIP2B , PIAS3 , PNPLA3 , PPP1R13L , PRKG1 , RAB23 , RAG2 , RASGRP1 , RPS6KA4 , RRAD , RUNX2 , SLC30A10 , SLC9A7 , SPTBN2 , SSH3 , STARD8 , STAT2 , SYT12 , TENM1 , TGFB1I1 , TMEM74B , TNS1 , TPPP , YBX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat Bild Et Al Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4 , AXIN2 , B4GALT1 , CALR , CASP4 , CD151 , CTSD , DACH1 , HMGB1 , KLHL15 , PALMD , RPS6KA1 , SIRPA , SLC27A2 , TAGLN , WIPI1 , ZNF703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc2 Eed Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , AKR1C3 , ANGPTL4 , ANKRD46 , ARHGAP24 , ARL4C , ATXN1 , BACH1 , C1orf21 , CACNA2D3 , CDKN1C , CLGN , CLIP1 , CORO2B , CTSO , CUBN , DEPP1 , DNAJC12 , DUSP8 , ELF1 , ENPP2 , ERMAP , EVI5 , FUCA1 , GADD45G , GPC5 , GPR37 , GSG1 , H2AC6 , H2BC21 , H2BC4 , HIC2 , HOXC8 , IFI6 , KCNQ2 , KIF1B , MAP3K7CL , MCTP1 , MTHFD2L , MTSS1 , NIBAN1 , NMT2 , OBSCN , ORAI3 , OSGIN1 , OSTM1 , PDGFA , PLSCR4 , PPM1H , PTBP2 , PTPRT , RBM47 , SATB1 , SCG2 , SEMA6D , SERINC5 , SERPINB7 , SLC12A8 , SLC30A10 , SLC6A15 , TMEM187 , TRPS1 , TUFT1 , VTN , ZNF91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rela Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APBA2 , CCL2 , CD38 , CDK5R2 , CDKN2B , CRB1 , CTF1 , DEPP1 , DGKI , DUSP8 , DYSF , EGR1 , F3 , FGF2 , FOS , FOSB , FOSL1 , GAD1 , GADD45B , GAS7 , HOOK1 , IL1B , JUN , KCNC4 , KCNQ4 , KLF6 , LAMC2 , LGMN , LMO7 , MTMR11 , NOL4 , NOVA1 , PDE5A , PDK1 , PODXL2 , PPP1R15A , PRKG1 , PTGS2 , RIPK1 , RREB1 , SIRPB1 , SNAI1 , TNC , TNFRSF9 , TPMT , TRIM38 , VDR , ZFP36 , ZFP36L1 , ZFP37 , ZNF286A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rb Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADA , CLN6 , CRIP2 , DDIT4L , DNA2 , DNMT1 , EPHX1 , FBP1 , FXYD6 , GAB3 , GCLM , GRM8 , HES1 , ID1 , MAN1B1 , MCM6 , MCM7 , MSH6 , MYC , PALMD , PCDH10 , PCNA , PDXP , PLEKHA6 , PLXNB2 , PMM1 , POLD4 , POLE2 , PPM1M , PRIM1 , RFC3 , SLC24A1 , SNAP25 , SPOCK1 , STMN1 , STUB1 , TIMELESS , TYRP1 , UBE2T , ZFP30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crx Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , ALPK2 , ALPL , ARG2 , ARHGAP10 , B4GALT1 , BCAR3 , BICDL1 , BST1 , BUB1B , C16orf74 , CCDC107 , CKMT1A , CLTRN , CNGB1 , CSGALNACT2 , CUTALP , DPF3 , DUSP14 , FAAH , FAM161A , GAS7 , IER3 , JAG1 , MYRF , NAT1 , PACRG , PAQR4 , PDIA5 , PFKFB2 , PLA2R1 , PLEKHF2 , PLPP2 , RABGEF1 , RAD51 , RNF207 , RTBDN , SLC24A1 , SNTB2 , ST8SIA1 , STK17B , STRA6 , SUV39H2 , TNFAIP3 , UBTD1 , VTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc V6.5 Up Late.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADA , ANGPTL4 , ANXA1 , AVPI1 , BCL3 , BDH1 , BGN , C11orf24 , C16orf74 , CALML4 , CAVIN1 , CBR3 , CD38 , CRMP1 , DYRK3 , E2F8 , EMP1 , EPOP , FBLN2 , GADD45A , GBX2 , GLI1 , HES7 , ICAM1 , INHBA , KIF18A , KLF4 , LGALS3 , LOX , MANBA , MGP , MSC , MYC , NEFH , NEFL , NOL12 , NOTUM , NR0B1 , NUPR1 , PCOLCE2 , PDGFC , PLEKHA4 , POLA1 , RASGRP2 , RPP25 , S100A4 , S100A6 , SEPTIN1 , SERPINE1 , SLC27A2 , SOCS3 , SPP1 , SPTBN4 , SULT4A1 , TCF15 , TEX19 , TIMP1 , TM4SF1 , TRIB3 , TTC39B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc2 Suz12 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ACE , ANKRD46 , ARL4C , ATXN1 , BFSP1 , BMP3 , BTN3A2 , C1orf21 , CA11 , CACNA2D3 , CALML4 , CFB , CNPY4 , COCH , COL13A1 , CTSS , DACH1 , DCBLD2 , DNAJC12 , ECM2 , EDN1 , ERAP2 , ERMAP , FCHO1 , FOLR3 , GAB2 , GPC6 , HBEGF , HR , ITGA2 , KCNN4 , KRT15 , KRT81 , LCAT , LCP1 , LYPD1 , MCTP1 , MYT1 , OSTM1 , PAQR6 , PCBP3 , PINLYP , PLEK2 , POU2F1 , PRKG2 , PSMB8 , REST , RNASEL , SEMA3E , SETBP1 , SLC6A15 , SLC6A9 , SLCO4A1 , SPTB , TET3 , TMEM187 , TOM1L2 , TRIM58 , TRPC6 , XPNPEP2 , ZNF208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tbk1.Dn.48hrs Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1D , BCL2 , BIRC5 , CDK1 , COL4A1 , CRYZ , DUSP22 , DUSP4 , IER3 , IL13RA1 , INPP4B , PAFAH1B3 , PDGFA , PSMB8 , RALB , ST3GAL5 , STX1A , TRIB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD14B , ANXA3 , APBB2 , ARHGEF26 , BCL2 , BEND5 , BEND6 , BEX2 , BTN3A3 , C12orf75 , C16orf74 , C1orf115 , C3orf80 , CA8 , CACNA2D3 , CAST , CHPT1 , CLTCL1 , CRYBG1 , DDAH1 , DSG2 , ENDOD1 , ENHO , FAM117B , FANCE , FBLN7 , FBN2 , FDXR , GALNT12 , GPM6B , GPRASP2 , HES6 , HPDL , JPH1 , KBTBD11 , KLF5 , KLRG2 , LAMP3 , LAMP5 , LPAR3 , LPCAT2 , LRATD2 , MAP3K15 , MATN2 , MGAT4A , MICAL2 , MREG , MTARC1 , MTFR2 , MTURN , NHSL2 , NR2F2 , NUDT11 , OGDHL , PADI2 , PALD1 , PAWR , PCYOX1 , PDGFRL , PIK3CB , PIK3R3 , PLXND1 , PNMA2 , PODXL , POLD1 , PPM1H , PSTPIP2 , RASGRP1 , RET , RGS16 , RIPOR2 , RMI2 , RNF144A , RORB , SCD , SETMAR , SH3GL3 , SIDT2 , SLCO4C1 , STAR , STX11 , TCTA , TENT5C , TEX15 , TMEFF1 , TNFAIP8 , TPD52L1 , TRIM58 , TSPAN2 , VAT1L , VCL , ZDHHC23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc V6.5 Up Late.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOM , ARFGAP3 , ARID3B , BAIAP2L1 , CDH2 , CITED1 , COL4A1 , COL4A2 , CTDSPL , CTSH , CUBN , CYBA , DAB2 , DKK1 , FGF5 , FGFRL1 , FRZB , GAS1 , GRIK5 , GRINA , GSC , GYG1 , H1-0 , HEXA , HLA-B , IER5 , KDELR3 , KIF21A , LCP1 , LGMN , LOXL2 , MACROD1 , MOSPD1 , MSX2 , MYLIP , NAGLU , NUDT11 , P4HA1 , P4HA2 , PDLIM3 , PKDCC , PLAGL1 , PLXNB2 , PODXL , POSTN , PTH1R , RAMP2 , RBP4 , RECK , RIPK4 , SATB1 , SEL1L3 , SGCE , SH3RF1 , SIL1 , SIX5 , SLC39A8 , TCN2 , TNNT2 , TSPAN7 , WLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lef1 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2 , AKR1C3 , ANK3 , AP1M2 , ATP1B1 , ATP8A1 , BDKRB2 , BTN3A3 , C1orf115 , CCN2 , COCH , CRYBG1 , CTSH , CYP2J2 , ERAP2 , FBXL15 , GALNT12 , GRB14 , HERC6 , ID1 , IL17RB , IL20RA , IL33 , LIMCH1 , MANBA , MARCHF2 , MDFIC , MFGE8 , MOCOS , MTARC1 , MVP , MXD3 , MYRIP , NUDT18 , OAS3 , PAPSS2 , PDGFC , PDGFRL , PIAS3 , PLLP , PLSCR4 , PROS1 , RAC2 , RBM47 , RBP4 , RNF144A , SAMD9 , SH3BGRL , SH3GL2 , SLC22A18 , SLC24A1 , TLR3 , TM4SF1 , TMED3 , TMEM144 , TNS3 , TPM1 , TRPM4 , TSPAN1 , TSPAN8 , USP18 , ZNF711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hinata Nfkb Immu Inf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CXCL8 , ICAM1 , IL1B , IRF1 , NFKB1 , PTX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vegf A Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , ADARB1 , ARC , ARL4C , CABP1 , CCL2 , COLQ , CORO2B , DBH , DCX , DDIT3 , DSG2 , DTX4 , DUSP8 , ECM1 , EMILIN1 , ENO2 , ENPP2 , EPHX1 , FEV , FMO5 , GABRA5 , GLI1 , HLA-DMA , HS3ST1 , HSD11B2 , HTR2A , ICAM1 , IL32 , IRF9 , ITGB4 , ITM2A , JCAD , KCNC3 , LCAT , LMOD1 , MATN2 , MERTK , MN1 , MTMR11 , MTSS1 , NEDD9 , NFKB2 , NINJ1 , OPRD1 , OPTN , PART1 , PHLDA1 , PLA2G4C , PLTP , PPL , PSMB8 , PTPRJ , RELB , SDC4 , SEMA5A , TAGLN , THY1 , TNS2 , TRAF1 , TRAF5 , TUB , UBA7 , ZCCHC24</t>
+    <t xml:space="preserve">ALDH1A3 , ARRB1 , ATAD2 , BHLHE40 , CDT1 , COL9A3 , DLX5 , E2F8 , EPS8 , FANCL , FKBP5 , FZD6 , GPM6B , GRB10 , H1-10 , HACD1 , ITGA4 , ITGB5 , LRRC37A4P , MACROD1 , MCM10 , MICB , NOTCH2 , NPR3 , NPTX2 , PDK1 , PER2 , PLK4 , PSIP1 , RAB33A , RGS16 , RNF144A , SLC1A5 , SLC29A1 , SLC29A2 , SLC2A3 , SLITRK5 , SMAGP , SSR3 , STAG3L1 , TAF4B , TBC1D30 , TEX15 , TRIB3 , ZNF395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jnk Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLP1 , APOBEC3F , BCL2L11 , BLM , CABP1 , CDKN3 , DEPP1 , DUSP4 , DUSP8 , DYRK3 , EPHB1 , GPR12 , IDUA , INPPL1 , ITGA10 , JPH3 , KIF22 , KNTC1 , MAFK , MBNL2 , MMP2 , NDRG2 , NELL2 , NOVA1 , NPR1 , P2RX3 , PAQR4 , PCDH9 , PLCD1 , POLD1 , PTP4A3 , QSOX1 , RGS16 , SEMA3B , SGCG , SHB , SMAD9 , THY1 , TNIK , TNS2 , TSPAN2 , UBE2C , VASP , VEGFC , YPEL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.600.Lung.breast Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADAMTS20 , ADD2 , ALOX12B , APC2 , BDKRB1 , BTN3A2 , CCDC102B , CD207 , CD248 , CNTLN , COL5A3 , CRABP1 , CRABP2 , CREB3L1 , DENND2D , DLX6 , ELMO1 , EMID1 , ENTPD5 , ERAP2 , FBXO24 , FGF1 , FGFR3 , FGGY , FRAS1 , GAS1 , GBP1 , GBP2 , GP1BB , GRIA1 , HCN2 , IFI44L , IMPA2 , IVL , MAML3 , MAP2K6 , MAP3K1 , MMP28 , MTHFR , NINJ1 , NLGN4Y , NOS1 , OLFML2A , PAQR6 , PGGHG , PLXND1 , PPFIA2 , PPFIA3 , PROM1 , PTENP1 , PTPRJ , RUNDC3B , SH3GL3 , SLC30A3 , SLC6A9 , SOBP , SOX11 , SPTBN2 , STAG3L1 , SYNDIG1 , TEX15 , THAP9 , THBS3 , TRIM58 , TRIM9 , WHRN , YPEL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pten Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSS3 , ARHGDIG , B3GAT1 , BMP7 , BMPR1B , C2 , CAMTA1 , CCDC102B , CELSR2 , CLTCL1 , COL26A1 , DCC , EDN1 , EEF1A2 , FGF1 , GDF10 , GLT8D2 , GNAO1 , HOXC8 , HS3ST3B1 , JAG1 , KCNQ4 , LYPD1 , MACROH2A2 , MSC , NREP , OSGIN1 , P2RX6 , PCDHA5 , PLPPR4 , PRR16 , PTPRJ , SLC16A7 , SLC30A10 , SORBS2 , SPOCK1 , TCF7L1 , TENT5C , TLE1 , TMEM151B , TONSL , TSPAN2 , TUBB2B , ZBTB10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dca Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ADARB2 , AK5 , ARHGDIG , ATP1B2 , AURKB , BCAS4 , BEST1 , CACNG5 , CD82 , CLPB , COPZ2 , CREB5 , CRIP2 , CXCL8 , DEPP1 , DPP6 , ELAVL4 , EPHB6 , FRMPD1 , GARNL3 , GDPD3 , GIPR , GRIA1 , HTR6 , IFIT2 , KIAA0513 , KREMEN2 , MAPK8IP2 , MCTP2 , MIR600HG , MX1 , MYCT1 , MYOZ3 , NRXN2 , NTN3 , PHLDB1 , PNMT , SIX1 , SLC66A3 , ZNF157 , ZNF185 , ZNF91 , ZSCAN12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P53 Dn.v2 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM11 , ANPEP , BCL2L11 , BEST1 , BMPR1B , C1orf21 , CENPA , CLTCL1 , E2F2 , ELAVL2 , ELL2 , EVC , FAAH , FKBP5 , HNRNPA0 , HOXD13 , HS3ST3B1 , IGFBP4 , IGFBP6 , ITGA4 , KCNJ9 , MTHFR , NDC80 , NUDT6 , PNMA3 , RAB38 , RECK , SIL1 , SLCO2A1 , SNPH , SNTB1 , SSTR2 , TP53TG1 , TP73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wnt Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4GALT , ADGRB1 , AURKB , CHRNA7 , CHRNB2 , CKAP4 , CPS1 , CRMP1 , DCC , DPYSL4 , F2R , FICD , GDF15 , GLI1 , HOXD10 , HOXD3 , HS3ST1 , INSRR , KCNC3 , KCNJ9 , KCNN1 , KIFC1 , MAPK8IP1 , MAZ , NBL1 , NLRX1 , NTSR1 , PKLR , PPP1R3C , PPT1 , PTPRO , RASGRP2 , RBPMS , RNF112 , SDC4 , SEMA5B , ST8SIA3 , SYT3 , TCF7L2 , TGFB1I1 , UBXN11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alk Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP3 , ARID3B , COL9A3 , CTF1 , DLGAP2 , EFNA2 , FXYD6 , FZD8 , GRM2 , IFI44L , IGFBP6 , KCNC3 , KCNJ9 , KCNN4 , LGR5 , LPAR2 , MTHFR , MX1 , NDRG2 , NMNAT2 , OPRD1 , PRPH , PTPRF , RPL23AP7 , SEMA3E , SEMA7A , SPTB , ST8SIA3 , TEDC2 , THSD4 , TIAM1 , UNC93B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb P130 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASB13 , ATP6AP2 , B2M , C9orf72 , CASP6 , CLIP1 , CLU , CTSB , CTSC , CXCL12 , DDX1 , DNAJC1 , EOGT , ERAP1 , EVI5 , GADD45A , GDPD3 , GNS , HTRA1 , LAMP1 , LAMP2 , NRARP , RCN1 , RRAS , SEC23A , SLC35F6 , STAT1 , STAT6 , USP18 , VDR , VOPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dca Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM2 , ALK , ANKRD46 , ASIC4 , ASPM , CDK5R2 , CHEK2 , CNTLN , ENO3 , GABPB1-IT1 , GMPR , GPR137B , GPR19 , GSDMD , IL10RA , LAMA3 , LRP5L , LRRC37A2 , MFGE8 , NUDT11 , PKD1P1 , PLA2G4C , PPP1R12B , PRRX2 , PTPRG , RALGDS , RASSF4 , RNPEPL1 , SETBP1 , SIRPB1 , SLC16A10 , SLC35F6 , SNCB , SP140L , SPC25 , STAG3 , STEAP1B , ZCCHC24 , ZNF248 , ZNF286A , ZNF821 , ZNF84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il15 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM12 , ARL4C , ATP8A1 , BICDL1 , C14orf132 , CD177 , CDKN1C , CLDN11 , CLGN , CNTN1 , CUX2 , DACT1 , DEPTOR , ENTPD5 , EPS8 , FSTL3 , GEM , GPC4 , H3C12 , HOXD13 , JCAD , KCNQ1 , MAP2K6 , MFSD13A , MTARC1 , MYLK , PBXIP1 , PLCL1 , PRDM11 , PRKG1 , PROM1 , RIN2 , S100A3 , SCN3A , SEC14L2 , SEMA6D , SIGLEC15 , SNAI2 , SPATA1 , SYT1 , TBC1D2 , TGFB1I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gcnp Shh Up Early.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTS1 , AURKB , CLIP4 , CSF1 , DHFR , DNAJC3 , E2F8 , ELOVL2 , EPB41L4B , FCGRT , FOSL1 , GTF2H1 , HLA-B , HMGCL , KIF1A , KIF1B , KIF4A , KIFC1 , LBR , LOXL2 , LUC7L3 , MAN1A1 , MBTD1 , MCM10 , MCM6 , MYB , MYT1L , NABP1 , NR0B1 , PRC1 , RPL39L , SDC3 , SGO1 , SPDL1 , STYX , TOP2A , TOP2B , TRAIP , UBE2T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il21 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACHE , AP3B2 , BICDL1 , CD177 , CHGB , CNTN2 , CUX2 , DGCR5 , EPS8 , FRMD4A , GCNT4 , GPC4 , HKDC1 , ITGA2 , ITGA6 , JCAD , KDR , LMOD1 , LRP5L , MAB21L1 , MIR600HG , MYLK , NRXN1 , OSGIN1 , PCDH9 , PLCB4 , PLPPR4 , PNMA3 , PRKG1 , PROX1 , PRR5L , RIN2 , SEC14L2 , SLC17A5 , SLC8B1 , SP4 , SPTBN4 , TESMIN , TFAP2B , TSPAN7 , USP18 , ZNF286A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.prostate Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ABCB1 , ACKR3 , ACSS3 , AK5 , ARL17A , BEND5 , CADM4 , CAMK1D , CFI , CNTFR , DNAJC12 , EDN1 , EPHB6 , GPNMB , GPRASP1 , GRM2 , IDUA , IGFBP3 , KCNQ2 , LUM , NOS1 , PTGIS , REEP1 , RRAD , SERPINB7 , SH2D3C , TAGLN , TFAP2B , TUBB4A , VIL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alk Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTL6B , ADAM12 , ANGPTL4 , BDKRB2 , BEGAIN , BMPR1B , BST1 , CXCR5 , DLX6 , ENPP2 , EPAS1 , FAP , FJX1 , FLVCR2 , GDF15 , GRPR , NNAT , NTRK1 , OLFML3 , P2RX3 , RRAS , SCN1A , SLC12A8 , SLC1A5 , SLC6A9 , SLC7A11 , SLC7A5 , STMN2 , TRIB3 , UNC13A , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2f1 Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AURKB , BCL2 , BOK , CASP7 , CDK5R1 , CNIH2 , CRYZ , DLGAP5 , DNA2 , E2F8 , ERMP1 , EZH2 , FNBP1 , GPR19 , GSDME , HMGB3 , KIFC1 , KLHL21 , LMNB1 , MCM10 , MELTF , MPG , MTSS2 , MXI1 , NASP , NBL1 , NCAPH , PACS1 , PAIP2B , PARP1 , PLK4 , PRC1 , RBM15 , SGO1 , SINHCAF , SIRPA , SMAD1 , TLX2 , TOP2A , TPD52 , TPM2 , UBE2T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atm Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA8 , ADARB1 , APBA2 , ASIC4 , BCL2L11 , BDKRB1 , BEST1 , CD8A , CHGB , CNTFR , COL9A3 , DLX6 , DYSF , ECM2 , ENO3 , FGF5 , FSTL3 , GAB2 , IGFBP4 , LHPP , PARVA , PLTP , PSG5 , RAB3A , RECQL4 , RET , S100A2 , S100A3 , SLC7A5 , SNCB , STAG3 , SYN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pdgf Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM9 , ANXA7 , ARC , ATF3 , CBX2 , CDC25A , CDK5R2 , CDK6 , CDKN1A , DUSP5 , ELOVL2 , FAM3C , FAM98A , FOSL1 , GADD45A , HSPA2 , INHBA , KBTBD11 , KCNK3 , LRPAP1 , NAGLU , NEDD9 , PPP1R12B , RNF14 , SDC3 , SLC30A1 , SLC39A7 , SLC7A5 , STK10 , SUZ12P1 , TET3 , TMEM158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pkca Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACHE , ADORA2B , ADRA1A , ARSG , BSN , CASP6 , CREB3L2 , DBNDD1 , DDX60 , FBP1 , GATA4 , GFAP , GNAO1 , GPR155 , GSTM4 , IL15 , KIRREL1 , KLF15 , NOS1 , OAS3 , PASK , PER2 , RETSAT , SEC14L2 , SECTM1 , SLC16A3 , SLC7A8 , SMPD3 , SPTBN4 , TET1 , TPMT , TREH , TUB , TUBB2B , VWA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ctip Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABLIM2 , ADAM15 , AMPH , BCAM , CAMKV , CARD10 , CDKN1C , CEMIP , CLMN , CTF1 , CYBRD1 , EDEM1 , EDN1 , FAM169A , GPR19 , GSN-AS1 , HIBADH , IGSF9B , INKA2 , KCNC1 , LINC01963 , LRRC32 , NRIP2 , OLFML2A , SLC35D1 , STAG3 , SYNDIG1 , TENT5C , TSPAN7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jnk Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADAM12 , ADAMTS3 , AGTPBP1 , AKR1C3 , ALOX12B , B3GALT5 , BAG2 , BMP7 , C1S , CLCN4 , CRMP1 , CXCL8 , DGCR5 , ECM2 , GCH1 , GNAZ , HR , HTR6 , IGFBP3 , IL10RA , IL13RA2 , KCNJ9 , NID2 , PAPSS2 , PDE4B , PMEL , PRR3 , RGL1 , RIPOR2 , RRAD , RUNX2 , S1PR1 , SHC3 , SNAI2 , STARD13 , SYNE1 , TET3 , TRIM24 , YAP1 , ZFHX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.600.Lung.breast Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM19 , ADAMTS6 , ANGPTL4 , BMP6 , BRSK2 , CALB1 , COL9A3 , CTNNA2 , CXCL8 , DCBLD2 , DOCK4 , FBP1 , FNDC8 , GFAP , HAS2 , HBEGF , HOXD11 , IGFBP3 , IL13RA2 , INHBA , ITGA2 , KCNAB3 , KCNC1 , KCNH2 , KIF5A , KIF5C , LIF , MGLL , MMP1 , MMP10 , NAV3 , NCAM1 , NELL2 , NGF , NRCAM , NRL , NTRK1 , OGDHL , OSGIN1 , PDCD1LG2 , PDE2A , PLAUR , PLXNB3 , PPP1R15A , PTGIS , RREB1 , SEMA3B , SIGLEC15 , SLCO4A1 , SLCO5A1 , SLIT2 , SNAP25 , SNAP91 , SPHK1 , ST3GAL6 , STC1 , STX1A , SYP , TAGLN3 , TERT , TMEM158 , TNFAIP3 , TONSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P53 Dn.v2 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAM12 , ANGPTL4 , CACNG2 , CLCF1 , CXCL12 , CXCL8 , DLX6 , DPF1 , FOSL2 , IER3 , KCNK3 , LRRC32 , MMP3 , MPZ , NFIX , NTRK3 , NTSR1 , OSGIN1 , PCDH1 , PPEF1 , PRDM11 , PTX3 , RELB , RFX2 , RIPK4 , SDC4 , SLC16A4 , SYN1 , TDRKH , TFAP4 , TNFAIP3 , TNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yap1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB4 , FICD , GOLGA2P5 , IL4R , ITGA2 , MYLIP , PDIK1L , SLC9A1 , ZBTB39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pdgf Erk Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APC2 , ARF6 , BCL10 , CEBPB , DUSP1 , DUSP8 , GIPC1 , HIC2 , IDUA , IL7R , ISL1 , JUN , LTBP1 , MAB21L1 , MAFF , MFSD5 , MGAT1 , MYC , MYCN , NEFH , PHOX2B , PKD1P1 , PNMT , RHOB , RTN2 , SLC3A2 , SMAD7 , SMOX , TGIF1 , TMED5 , TRAIP , ZBTB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.50 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , ACKR3 , EPHB6 , IFI44L , NOS1 , OLFML2A , PPFIA3 , RRAD , SOX11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.300 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , ACKR3 , CAMK1D , CHRM2 , CRABP2 , CSDC2 , EPHB6 , FGFR3 , GBP1 , GRM2 , HSPB8 , IFI44L , KCNQ3 , MAML3 , MAP2K6 , MTSS2 , MX1 , NOS1 , OLFML2A , PPFIA3 , RRAD , RUNDC3B , RYR2 , SLC9A7 , SOX11 , SPTBN2 , TAGLN , TEX15 , WHRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.prostate Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM2 , ANGPTL4 , CAMK2B , CHRNA3 , COL26A1 , ENG , FSD1 , GLB1L2 , HKDC1 , IL10RA , IL7R , ITGA2 , KLRG1 , KREMEN2 , LMO1 , MAP3K1 , MMP11 , NBEA , NOL4 , PCDHA2 , SV2C , SYT5 , THSD4 , TLR4 , TSSK2 , TWIST1 , VEGFC , YPEL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb P130 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALK , AURKB , CARD19 , CASP7 , CCNB2 , CDC7 , COQ8A , CRLF1 , CRTAC1 , FGF10 , FST , GREM2 , HMGA2 , ICA1 , IER3 , KIF20A , KIF22 , MYLK , PCSK5 , PIMREG , RGS16 , SEMA5B , SLC29A1 , STMN3 , TWIST2 , UBE2C , ZBTB12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat Gds748 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTS20 , CELSR1 , GAS1 , RPS6KA5 , SKP2 , SNAI2 , TENT5A , ZNF273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singh Kras Dependency Signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD3 , LAMA3 , MAOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bcat.100 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMH , DEPP1 , FZD4 , SNAI2 , TENT5A , ZNF711 , ZNF749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtor Up.n4.V1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5 , ARID5B , BCOR , BRIP1 , CEP68 , CHIC2 , CLN5 , DPY19L2P2 , EOGT , ERAP1 , FBLN5 , GALNT7 , H1-0 , H2AC6 , LRRC37A4P , MME , PBXIP1 , PLCL1 , RAG2 , RNF44 , RYR2 , S1PR1 , SCN3A , SLC35D1 , SMPD3 , ST8SIA4 , STMN3 , SYNE2 , TPM2 , TPP1 , TRIOBP , XYLT1 , YPEL5 , ZNF124 , ZNF34 , ZNF443 , ZNF544 , ZNF711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pten Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADCYAP1R1 , ADGRE5 , ALX3 , ARL17A , B3GALT5 , C1QTNF1 , CAMK1D , CDH10 , CHST7 , CPLX2 , FJX1 , FOSL1 , FST , HPCAL4 , HS3ST1 , INPP4B , LIN7A , LUM , MAMLD1 , MATN3 , OLFM1 , OPRM1 , PNMA3 , PROX1 , PSMB9 , PTENP1 , SEMA4D , SERPINE2 , SH3BGRL , ST8SIA3 , SUGCT , SV2C , TENM1 , TLE6 , TNR , TSPAN7 , TWIST1 , VIM</t>
   </si>
   <si>
     <t xml:space="preserve">Gcnp Shh Up Early.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">AMOTL2 , ANKRD44 , ASPH , BTD , CCL2 , CD38 , CFB , CITED2 , CNN1 , CRABP2 , CRYBG1 , CYBA , CYP27B1 , DLK1 , EGR1 , EMP1 , FRMD5 , GPR19 , GRIN1 , H2BC21 , HAS2 , HES1 , IL1R1 , ITGA4 , JPH3 , KIAA1217 , LAMB3 , LAT2 , LCP1 , LIN9 , LYST , MAF , MERTK , MGP , MIPOL1 , MX2 , MYO5B , MYRF , NLRX1 , NOTCH1 , NPPB , NR6A1 , PHLDB2 , PIGT , PLK2 , POLD4 , RAG2 , RAMP1 , SEZ6 , SIX4 , SLC43A3 , SLC7A3 , TM4SF1 , TMPO , WWC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atf2 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABLIM3 , ADM2 , ARSJ , ASPN , C3AR1 , CARD9 , CBX5 , CD8A , CENPO , CENPU , CLDN1 , CORO2B , DTL , ENDOG , FABP4 , FOXL2 , FOXM1 , FSD1 , GDF10 , GINS2 , GPR63 , HMX1 , HOXD1 , HOXD11 , IL32 , INPP4B , KCNAB3 , KCNK3 , KRT7 , KRT81 , LIG1 , LYPD1 , MAP2 , MMP1 , NCAPG , NEDD9 , NEFL , NEFM , NNAT , NRXN2 , PACS1 , PAFAH1B3 , PCDH1 , PLAU , PLK4 , PODXL , POLD1 , PTGER1 , PTPRT , RAD51 , RBP1 , S100A4 , SCUBE3 , STEAP1B , STRA6 , SULT1B1 , TCIM , TNFSF18 , TRIM9 , UPP1 , WNT5B , ZFR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gcnp Shh Up Late.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AURKB , BOK , CASD1 , CASP4 , CDC25A , CDC25C , CDCA7 , CDK1 , CHEK1 , CKS2 , CLIC4 , DDX39A , DLGAP5 , E2F8 , ELAVL2 , ELOVL2 , FANCC , FRMD6 , GBP2 , IDH2 , INCENP , KIF2C , KIFC1 , LBR , LIG1 , LOXL2 , MBD2 , MCM10 , MCM4 , MCM5 , MCM6 , MIOS , MIS18BP1 , MUC1 , MYB , NECTIN2 , NPAS1 , NPTX1 , NUSAP1 , PCNT , PLEKHA7 , PLK2 , POLA2 , PRC1 , PSMC3IP , RAG2 , RRM1 , SGO1 , SINHCAF , SIX4 , SLC29A1 , SMC4 , SQOR , SYT4 , TEAD3 , TMOD3 , TOP2A , TOP2B , VCAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.lung Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS3 , ADCYAP1R1 , ANGPTL4 , ANO1 , C3AR1 , CFAP69 , CXCL8 , CYP2J2 , DCBLD2 , DOCK2 , DOCK4 , EGFL7 , EVI2A , GRIP2 , HBEGF , HOXD11 , HS3ST3A1 , HTR7 , INHBA , ITGA2 , KIF5C , LDB3 , LRIG1 , MMP1 , NAV3 , NELL2 , NGF , NRP1 , OGDHL , PCDH17 , PDCD1LG2 , PRKG2 , RBP4 , RREB1 , SIGLEC15 , SLC18A1 , SLC6A11 , SLCO4A1 , SLCO5A1 , ST3GAL6 , TBX3 , TMEM158 , TNNT2 , TSPAN1 , ZNF749 , ZNF821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tbk1.Dn.48hrs Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOE , ARL4C , CDKN2A , CHEK2 , DDR1 , DUSP3 , EDN1 , FCHO1 , FKBP14 , FSD1 , IGFBP3 , LBR , LRPAP1 , PSRC1 , SCP2 , SOX2 , ZMIZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yap1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8orf48 , C8orf58 , CDK14 , DLX5 , FAM167A , FLOT1 , GTPBP3 , MAML2 , MOCS2 , MSN , NMRK1 , RHOQ , SEMA3C , SHISA4 , SIAE , SNAP23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il15 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , AHR , APLP1 , CALML4 , CDC25A , CPA4 , CXCL12 , DHRS3 , DUSP4 , ECM1 , EGR1 , EGR2 , FAM3C , FLT3LG , FOS , FOSL1 , GADD45B , HEG1 , HOXC8 , HRH3 , HS3ST1 , HS3ST3B1 , HSD17B14 , IL1A , IRS1 , KCNJ2 , KCNJ9 , KIF1C , LIF , MAF , MAFF , MAFK , NR2F2 , PAK6 , PDE4A , PLEC , PSG4 , PTCH1 , PTH1R , REST , RGS16 , RHOB , RNF144A , RPP25 , SHROOM2 , SLC1A5 , SLC29A2 , SLC7A5 , SLCO4A1 , SOCS1 , SPOCK1 , SPP1 , TET3 , TLR3 , TMEM158 , TNFAIP8 , TNFRSF12A , TNFRSF9 , TPST2 , VDR , ZBTB7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nrl Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGRA2 , ADRB2 , ARHGDIB , BST2 , C14orf132 , CASP7 , CCL2 , CDT1 , CLIC1 , CLIC4 , CPLX2 , CTBS , DYSF , ECE1 , ELK3 , ELOVL2 , ERMAP , FKBP9 , GJD2 , GREB1 , GSDME , INPPL1 , KIF5C , METRN , NFKB1 , NR4A1 , NSG1 , PDE1C , PDIA3 , PIK3AP1 , PLEC , PLEKHH2 , QSOX1 , RASGRF2 , RNASE4 , SLC7A3 , SLC8A3 , SOCS3 , TMED9 , TMEM158 , TOM1L2 , TSPAN33 , TUFT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P53 Dn.v2 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM11 , BCL2L11 , BMP3 , BMPR1B , C1orf21 , C5AR1 , CCNF , CENPA , CLTCL1 , CYP27B1 , E2F2 , ELAVL2 , ELL2 , EPHA7 , EPHX2 , EVC , FAAH , FABP4 , FKBP5 , GPR75 , HMMR , HNRNPA0 , HOXD13 , HS3ST3B1 , IGFBP4 , IGFBP6 , ITGA4 , KCNJ8 , KCNJ9 , NDC80 , NRXN3 , PLEK2 , PNMA3 , POU3F2 , RAB38 , RAB4B , RECK , SCN9A , SELL , SIL1 , SLC24A1 , SLCO2A1 , SNAI1 , SNPH , SNTB1 , TP53TG1 , TP73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pgf Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA8 , ADAM9 , AGA , AMPH , ANGPT2 , ARMCX2 , ATP13A3 , BACH1 , CCPG1 , CD2AP , CFH , COL8A1 , CRYZ , DNAJC3 , DNASE2 , FABP4 , GPR37 , GRB14 , IL6ST , ITGA2 , ITSN2 , KLRG1 , LRRC17 , LTBP1 , MAFK , MMP10 , MTF2 , MTM1 , NAT1 , NEK7 , NRCAM , NUCB2 , PGAP1 , PHEX , PPAT , PTGS2 , RASGRP3 , RIPK2 , RNF6 , SAT1 , SGMS1 , SLC33A1 , SLC38A6 , SMC3 , SMC4 , SOCS5 , STAM2 , STK38L , STON1 , STXBP3 , SULF1 , SYNE2 , TFPI2 , TGFBR3 , THSD7A , TMED5 , TSPAN8 , TWF1 , UFL1 , UGP2 , VCAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akt Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT9 , ADGRG1 , ADORA2B , ANGPTL1 , C3orf52 , CALCB , CARD19 , CDKN2B , CRLF1 , CXCL16 , EDN1 , FBXO6 , GCH1 , GIPC1 , GPX8 , H4C8 , HIC2 , IFIT1 , IFIT2 , IFIT3 , IL1R1 , KCNK5 , KLF6 , LGMN , MAN2B2 , METRNL , MGARP , MYO5B , NEU1 , NIBAN1 , NKAIN1 , P2RX5 , PDGFD , PDK1 , PLAGL1 , PLAT , PLK2 , PON2 , PTPN14 , PTPRJ , PTRH1 , PYGL , RUNDC3A , SEC14L2 , SECTM1 , SPECC1 , SPHK1 , TESC , TMCC3 , TNFRSF12A , UBE2C , UGT8 , VAMP5 , VAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esc V6.5 Up Early.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTSL4 , AGER , ARID3B , CELSR3 , CHD7 , CRAT , DACH1 , DEPTOR , DLC1 , DLL3 , DOC2A , ECE1 , ENG , ENPP2 , ETFBKMT , FBP1 , FGF5 , GADD45G , GPRC5B , GRM8 , HES6 , ITIH3 , KCNC1 , KIF21A , LRIG1 , MAGI3 , MBOAT1 , MDFI , MYB , NRL , OPRD1 , OTUD7A , PARP6 , PCYT2 , PMFBP1 , PSMB9 , PTK7 , RUNX1 , SASH1 , SATB1 , SH3RF1 , SIMC1 , SLC16A3 , SLC29A4 , SOX11 , STIM1 , SUV39H2 , SYT3 , SYTL2 , TERT , TMCO4 , TMEM158 , TMEM42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stk33 Nomo Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD14B , ADGRA2 , ANXA3 , APBB2 , APOBEC3C , BCL2 , BEND5 , BEND6 , BEX2 , BTN3A3 , C16orf74 , C1orf115 , CD24 , CHPT1 , CKMT1A , CRYBG1 , DDAH1 , DLX6-AS1 , DSG2 , ENHO , FAM117B , FANCE , FBLN7 , FBN2 , FDXR , GALNT12 , GCH1 , H1-0 , HEATR5A , HES6 , HOXD13 , HPDL , IL18R1 , JDP2 , JPH1 , KLF5 , KRT81 , LAMP3 , LAMP5 , LPCAT2 , MAP3K15 , MATN2 , MGAT4A , MICAL2 , MTARC1 , MTFR2 , MTHFD2L , MTURN , NEDD4 , NHSL2 , NUDT11 , PADI2 , PALD1 , PAWR , PCYOX1 , PDGFRL , PIK3R3 , PLXND1 , PNMA2 , POLD1 , PSTPIP2 , PTGER2 , RASGRP1 , RET , RMI2 , RNF144A , RORB , SCD , SDK2 , SELL , SEMA3C , SEPTIN1 , SIDT2 , SLAIN1 , SLC16A14 , SLC16A4 , SOBP , STAR , STX11 , TCTA , TET1 , TEX15 , THEM6 , TPD52L1 , TRIM58 , TSPAN2 , VAT1 , VAT1L , ZDHHC23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cahoy Astrocytic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADCYAP1R1 , ADORA2B , BMPR1B , CBS , CORO1C , CYP7B1 , ELOVL2 , FGFR3 , FRMD5 , GRHL1 , IL17RD , IMPA2 , MERTK , MFGE8 , NCEH1 , NIPAL3 , NRARP , PAK3 , PANK1 , PAPSS2 , RORB , SCG3 , SEMA3E , SLC1A2 , SLC25A34 , SLC27A1 , SLC30A10 , SLC6A11 , SLC7A11 , STK38L , TMEM51 , TNFRSF19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eif4e Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM9 , ALPK1 , ANGPTL4 , CLDN23 , CTSC , DENND2D , DOCK1 , EPDR1 , FAS , FNDC3B , FRMD4B , FUCA1 , FZD3 , GALNT5 , IQGAP1 , ITPRIP , KLHL21 , LMO7 , LOXL1 , MMP9 , MYO10 , PLAU , PTGS2 , SEMA4D , SGPP2 , SLC46A3 , SQOR , STRBP , SVIL , TPD52 , TRIM47 , UBA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pdgf Erk Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP5 , ANXA11 , ANXA7 , AQP3 , CALML4 , CCP110 , CDK6 , CETN2 , CFAP70 , CHEK2 , COL1A1 , CORO2B , CPS1 , DDN , FLI1 , FSTL4 , GAP43 , GTF2H5 , INHBA , KBTBD11 , LEPROT , LRPAP1 , LUZP2 , MAML3 , MAOA , MAP2 , MID1 , MYO1E , NAGLU , NRG1 , PDIA3 , PHLDA2 , PMP22 , PPIC , PSMB10 , REST , REXO5 , RRBP1 , SLC39A7 , SPAG5 , TCEAL2 , TNNT2 , TP53I3 , TRAF5 , TSPAN9 , ZNF185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mek Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA12 , AMIGO2 , APBB2 , ARMCX3 , ASCL1 , ATP8B1 , BCL2 , BST2 , CASP8 , CHN1 , COL9A3 , DCAF6 , DDX60 , DLC1 , F12 , GDAP1 , GFRA1 , GREB1 , H2AC6 , H2BC9 , H4C8 , HERC6 , HSPB8 , IFI35 , IFI44 , IFI44L , IFI6 , IFIH1 , IFIT1 , IGF1R , INPP4B , IRF9 , ISG15 , ITPRID2 , JAK2 , KIF5C , LRIG1 , MGP , MOCOS , MOCS2 , MTCL1 , MYB , MYC , NMRK1 , OAS3 , PTBP2 , RAB29 , RASGRP1 , SMAD7 , SP100 , SP110 , STXBP3 , TAP1 , TDRD7 , TFPI , TFPI2 , TM4SF1 , TOP2B , USP18 , ZNF107 , ZNF43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pkca Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , ABI3BP , ADAM11 , ADGRB1 , ADM , BEX1 , CENPF , CFH , CKAP4 , COCH , CYGB , EAF2 , ECE2 , ENPP4 , EXT1 , FABP6 , GASK1B , GBP1 , GLDC , HES7 , HOXC8 , HS3ST3A1 , ITGB6 , KANK2 , MAGT1 , MALAT1 , MAP3K6 , MBOAT1 , MSC , NFKBIZ , NUCB2 , PDGFC , PDGFRB , PLAU , PROCR , RHOJ , SHF , SIK1 , SLC30A1 , SNTB2 , SYT12 , TLR2 , TNFRSF12A , TWF2 , ZBTB7A , ZC3H12A , ZDHHC1 , ZEB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pdgf Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADCY2 , ANXA2P2 , AOX1 , ARSL , ASPH , BCL3 , BHLHE40 , BMP3 , C2 , CBLN1 , COL1A2 , CRABP1 , CRYAB , CTNND2 , CUBN , CYB5R1 , DNMBP , EVI2A , FBN2 , GPR39 , HERC3 , HOXD1 , IL7R , ITGB6 , JUN , KIAA1217 , KLF5 , LIMK1 , LTBP1 , MAP7 , MSX1 , PAFAH2 , PLAT , PPP2R5B , RAD9A , SEMA3C , SLC22A18 , SLC8A2 , TNS2 , TRAIP , ZBTB7A , ZNF33B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.50 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , CGREF1 , EPHB6 , EPHX2 , GADD45G , HTR1B , IFI44L , MX2 , NOS1 , OLFML2A , PPFIA3 , PSORS1C1 , RRAD , SOX11 , THRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2f1 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADA , AURKB , BCL2 , BOK , BUB1 , CASP7 , CDK5R1 , CHAF1B , CHEK1 , CLN6 , CNIH2 , CRYZ , CYBA , DBF4 , DLGAP5 , DNA2 , E2F8 , ERMP1 , EVL , EZH2 , FEN1 , FNBP1 , GPR19 , GSDME , HES1 , HMGB3 , KIFC1 , KLHL21 , LMNB1 , MCM10 , MCM4 , MELTF , MPG , MTSS2 , NASP , NCAPH , PACS1 , PAIP2B , PARP1 , PIGA , PIP4K2A , PLK4 , POLA2 , PPM1M , PRC1 , RBM15 , RHBDL3 , RRM1 , SGO1 , SINHCAF , SIRPA , SMAD1 , TLX2 , TOP2A , TPD52 , TPM2 , TYMS , UBE2T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pgf Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTL6B , ARC , ATP1A3 , ATP2B2 , BCAM , CACNA1H , CAMK2B , COL18A1 , CTF1 , DPF1 , ELAVL3 , ENPP2 , FZD7 , GFRA2 , GRIA1 , GRM2 , HOMER2 , IGFBP5 , IGFBP6 , ITGB4 , KCNAB2 , KCNC3 , KCNN4 , LOXL1 , MAP1A , MAST1 , MSI1 , MTSS2 , NCAM1 , NELL2 , NFKB2 , NOS1AP , NPAS3 , NR6A1 , NUCB1 , OBSCN , PAIP2B , PSG11 , PXN , RELB , RIMS3 , S100A4 , SDC4 , SLC29A2 , SLC30A10 , SLC6A15 , SPRY1 , SPTB , SVEP1 , THY1 , TMEM158 , TMEM97 , TNFAIP3 , TRIO , TROAP , UBE2H , ZFHX2 , ZFR2 , ZNF185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Csr Early Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR3 , ATG101 , BCAR1 , BCAR3 , BDKRB1 , CD274 , CEMIP2 , CRISPLD2 , DCBLD1 , DDIT4L , DOT1L , EHD4 , ELK3 , F3 , FJX1 , FOXD1 , FRMD6 , GAL , GATA2 , HBEGF , HLX , IL11 , INHBA , ITPRIPL2 , MAP2K3 , NSG1 , NT5E , PHLDB1 , PLAUR , PTGS2 , PXN , REST , RGMB , RIPK2 , SCHIP1 , SHB , SLC30A1 , SMAD7 , SMARCA4 , SNAI1 , SOX9 , ST3GAL1 , STC1 , TENT4A , TMEM200A , TNFRSF12A , ZBTB12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il2 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL4C , BICDL1 , BTN3A3 , CBLN1 , CCDC81 , CDKN1C , CEL , CHGB , CHRNB4 , COLQ , CUX2 , DEPTOR , EFNA4 , EVI2A , FUT9 , FZD3 , GUCY1A2 , H2AJ , HKDC1 , HTR2B , ISL1 , JCAD , KCNS1 , MACROH2A2 , MAP2K6 , MTARC1 , MYCT1 , NAP1L2 , NUAK1 , PAK3 , PBXIP1 , PDE1C , PIK3R3 , PLA2G4C , PLCD1 , PLCL1 , PRKG1 , RABEP2 , RASGRP3 , RIN2 , RORB , SCHIP1 , SCN3A , SEC14L2 , SEMA6D , SLC17A5 , SLC24A1 , SNAI2 , SNPH , SULT1B1 , TAGLN3 , TG , TMEM140 , TNS3 , TRIB2 , TSPAN7 , UNC93B1 , ZNF695 , ZSCAN16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.600.Lung.breast Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM19 , ADAMTS6 , ADGRA2 , AKAP12 , ANGPTL4 , ANO1 , ARHGAP24 , BIRC3 , BRSK2 , CALB1 , CFAP69 , CHST2 , COL9A3 , CTNNA2 , CXCL8 , DCBLD2 , DDIT3 , DOCK4 , DYNC1I1 , EVI2A , FBP1 , FOXL2 , GNG11 , HAS2 , HBEGF , HOXD1 , HOXD11 , HSD17B2 , IGFBP3 , IL1B , INHBA , ITGA2 , KCNAB3 , KCNC1 , KCNH2 , KCNK15 , KIF5A , KIF5C , LAT2 , LDB3 , LIF , MGLL , MMP1 , MMP10 , MMP9 , NAV3 , NCAM1 , NELL2 , NGF , NPPB , NRCAM , NRL , NTRK1 , OGDHL , OSGIN1 , PDCD1LG2 , PDE2A , PLAUR , PPP1R15A , PTGS2 , RBP4 , RREB1 , SEMA3B , SIGLEC15 , SLCO4A1 , SLCO5A1 , SLIT2 , SNAP25 , SNAP91 , SPHK1 , ST3GAL6 , ST6GALNAC5 , STC1 , STX1A , SYP , TAGLN3 , TBX3 , TERT , TFPI , TMEM158 , TNFAIP3 , TNNT2 , TONSL , TOX3 , TRAF1 , TSPAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pten Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRA2A , ARHGDIG , ASPN , B3GAT1 , BMP7 , BMPR1B , C2 , CCDC102B , CELSR2 , CLTCL1 , COL26A1 , DCC , DOK5 , EDN1 , EEF1A2 , EPHA4 , EVI2A , FGF1 , GABRA5 , GADD45G , GDF10 , GLT8D2 , GNAO1 , HOXC8 , HOXD1 , HS3ST3B1 , HSPA12A , HTR1B , IL33 , IRF9 , JAG1 , KCNH7 , KCNQ4 , LYPD1 , MACROH2A2 , MSC , MX2 , MYO15A , OSGIN1 , P2RX6 , PCDHB12 , PLCE1 , PLPPR4 , PRR16 , PTPRJ , SLC16A7 , SLC30A10 , SPOCK1 , TCF7L1 , TEC , TENT5C , TGFBR3 , TLE1 , TONSL , TSPAN2 , TUBB2B , VCAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alk Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTL6B , ADAM12 , ANGPT2 , ANGPTL4 , ARHGAP4 , B3GALT4 , BDKRB2 , BEGAIN , BMPR1B , BST1 , CARD9 , CBS , CHST8 , CLSPN , DLX6 , ENPP2 , EPAS1 , FAP , FJX1 , FLVCR2 , GDF15 , GRPR , KRT81 , KYNU , NNAT , NTRK1 , OLFML3 , P2RX3 , PDZD7 , RRAS , SCN1A , SCN9A , SLC12A8 , SLC1A5 , SLC6A9 , SLC7A11 , SLC7A5 , SPP1 , STMN2 , TCIM , TRIB3 , UNC13A , VEGFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jnk Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA4 , APLP1 , ARHGAP4 , BCL2L11 , BLM , CABP1 , CDC42EP2 , CDC45 , CDKN3 , COL13A1 , CRYM , DEPP1 , DUSP4 , DUSP8 , DYRK3 , EPHB1 , FABP6 , GCNT1 , GPR12 , IDUA , INPPL1 , ITGA10 , JPH3 , KCNJ8 , KIF22 , KNTC1 , MAFK , MBNL2 , NELL2 , NOVA1 , NPR1 , NRGN , P2RX3 , PACRG , PAQR4 , PCDH9 , PDGFB , PFAS , PLCD1 , POLD1 , QSOX1 , RGS16 , SEMA3B , SHB , SMAD9 , SMARCD3 , SPRY1 , SRC , STON1 , SVEP1 , THY1 , TNIK , TNS2 , TSPAN2 , UBE2C , VASP , VEGFC , YPEL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.df.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRB2 , AHR , ARID3B , BCAM , BDKRB1 , CAMKV , CLDN1 , CNTFR , COPZ2 , CXADR , EPB41L4B , EPPK1 , FANCE , FBN2 , GAP43 , GLIPR1 , H2BC9 , HOMER2 , HOXC8 , IGFBP3 , KLF11 , KLF15 , KLF4 , LAMP3 , LCAT , LCP1 , LRRC61 , MAP7 , MPP3 , NGF , PAK3 , PAX5 , PCBP3 , PCLO , PDGFA , PTGER1 , PTGS2 , PTPN14 , PXDC1 , RET , RNF122 , SEMA3C , SEZ6L , SF3A2 , SIRPA , SLC30A3 , SMAD7 , STX3 , SYNE1 , SYP , TAGLN , TGFB3 , TNC , TNFRSF9 , TNXB , TUFT1 , VWA5A , WNT6 , ZFHX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc1 Bmi Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ACE , ANKRD46 , ARL4C , ATP1B2 , BIRC3 , CACNA2D3 , CDK6 , CFAP69 , CHD7 , COL13A1 , COLEC11 , CXCL8 , DNAJC12 , EDN1 , EGR2 , EOGT , ERAP2 , ERMAP , FCHO1 , GADD45G , GNG3 , GRM2 , HIC2 , IKZF2 , KIF5A , LPAR3 , MAFK , MCTP1 , MDFI , MYT1 , OSGIN1 , PAIP2B , PAX5 , PCDHB12 , PELI2 , PINLYP , PLEK2 , PSG7 , RGS16 , RIC3 , RIPK4 , RREB1 , SLC1A2 , SLC6A15 , SLCO4A1 , STUM , TLE2 , TMEM187 , TNFAIP3 , TRPC6 , TSPAN7 , XPNPEP2 , YBX2 , ZNF423 , ZNF91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wnt Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4GALT , ADGRB1 , AURKB , CCL2 , CD74 , CHRNA7 , CHRNB2 , CKAP4 , CPS1 , CRMP1 , DCC , DPYSL4 , EYA2 , F2R , FGF18 , FICD , FOS , GDF15 , GJD2 , GLI1 , GRIN2D , HOXD10 , HOXD3 , HS3ST1 , INSM1 , INSRR , KCNC3 , KCNJ9 , KCNN1 , KIFC1 , LCAT , MAPK8IP1 , MAZ , MYO5B , MYRF , NLRX1 , NTSR1 , PLAC9 , POSTN , PPP1R3C , RAD9A , RASGRP2 , RBPMS , RNF112 , SDC4 , SEMA5B , ST8SIA3 , SYT3 , TCF7L2 , TGFB1I1 , THRB , TPK1 , UGT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gcnp Shh Up Late.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4 , ACVR1 , ADRB2 , AGER , AGTRAP , AMOTL2 , ANKRD33B , ANXA7 , CCDC71L , CDCP1 , CNN1 , CNN2 , DLX5 , EDN1 , ENPP1 , EPB41L4B , EPHB6 , FAM111A , FCGRT , FRRS1 , GNPTAB , H2AJ , HSPG2 , IKBKG , IL4R , IRF9 , LAMC2 , MDFI , MEF2A , NACC2 , NBEAL2 , NECAP2 , NMI , NPTN , POLD4 , PPM1M , PSMB8 , PTH1R , PTPRJ , S100A11 , S100A13 , SAT1 , SELL , SLC30A3 , STX1A , STX3 , TGFB3 , TMEM214 , VEGFC , VSNL1 , WLS , WNK2 , ZIK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rb P130 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALK , AURKB , BIRC5 , CACNG4 , CARD19 , CASP7 , CCNB2 , CDC7 , CDK1 , COQ8A , CRLF1 , CYBA , ERG , FAM187A , FGF10 , FST , GREM2 , HMGA2 , ICA1 , IER3 , KIF20A , KIF22 , NPPB , ORC1 , PIMREG , RACGAP1 , RASGRF1 , RENBP , RGS16 , RHOJ , SEMA5B , SLC29A1 , SLC43A3 , STMN3 , SULT1B1 , TWIST2 , UBE2C , WNT2B , ZBTB12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Csr Early Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTSL4 , ADM , ARL4D , C14orf132 , CAVIN2 , CKB , COL1A1 , DHRS3 , ERAP2 , GFRA1 , GRHL1 , HSPG2 , IFIT2 , KBTBD6 , MAB21L1 , MOSPD2 , NMT2 , NPHP3 , OTUD1 , PAPLN , PDE5A , PLCD1 , PRRT2 , SIX1 , SIX5 , SKP2 , SLC16A7 , SLC7A14 , SLC9A7 , SNPH , STAT2 , STOX1 , SULF1 , TENT5C , TRIM56 , ZFYVE1 , ZNF33A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il21 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ABCA6 , ABCC8 , BCL6 , BOK , CPA4 , CXCL12 , DLX6 , DPYSL4 , ECM1 , EGR2 , FOSB , FUZ , GABRB3 , GIPR , GPR176 , GRIA4 , HABP4 , HEG1 , KCNC3 , LAMP3 , LIF , MAFK , MARCHF2 , MUC1 , MYOZ3 , NUDT11 , OLFM1 , P3H3 , PAIP2B , PAQR6 , PLPP2 , PTH1R , PTX3 , ROR2 , RPP25 , SCN9A , SLC12A8 , SLC29A2 , SLC7A5 , SLCO5A1 , SPP1 , ST8SIA3 , TBC1D19 , TEAD3 , TLR3 , TLR6 , TPBG , TPST2 , UGT8 , VDR , VSNL1 , XPNPEP2 , ZC3H12A , ZNF749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.breast Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS20 , ADAMTS5 , APOL3 , CA5B , CALCB , COL5A2 , CRABP1 , DENND2D , DPT , EGFL7 , ELMO1 , ENTPD5 , EPHX2 , FGFR3 , FGGY , FRAS1 , GADD45G , GRIP2 , HCN2 , IL18R1 , KCNA3 , MAML3 , NECTIN1 , NFATC4 , NOS1 , NPR1 , PAQR6 , PGGHG , POU3F2 , PPM1E , RUNDC3B , SLC30A3 , SLC9A7 , SOBP , SPTBN2 , SYNDIG1 , TEX15 , TLR6 , TRIM9 , XYLB , YPEL1 , ZNF37BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc2 Eed Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APLP1 , ARHGAP19 , ARRB2 , ASF1B , BUB1B , CDC45 , CDCA8 , CHAF1B , CHST3 , CLSPN , CORO1A , CSDC2 , CSPG4 , CXCL12 , DBF4B , DLK2 , ENO2 , FKBP5 , FOSL2 , GLI1 , GNAI2 , GPR176 , H1-10 , HELLS , IDH2 , INCENP , ITPKB , KCNS1 , KIF4A , LMOD1 , MAP3K6 , MCM10 , MCM2 , MCM5 , MICALL2 , MYBL2 , ORC1 , PACS1 , PC , PCDHGC3 , PDCD1LG2 , PDE4D , PEAK1 , PLAAT3 , PNPLA3 , POLA2 , POLD1 , PTGER2 , RECQL4 , RIPK1 , SCD , SEMA3B , SLC12A4 , SYN1 , TACC3 , TEDC2 , TRPM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pten Dn.v2 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABLIM2 , ARHGAP33 , ATF5 , ATP11B , BAHCC1 , BCOR , CCDC88C , COPZ2 , COQ8A , CORO2B , CRIP2 , ENTPD7 , EVA1B , FABP6 , FANCA , FGFR3 , KRT7 , LOXL1 , MAFK , MID1 , MRC2 , MXD3 , NECTIN3 , NIPAL3 , NUDT18 , OGDHL , RECQL4 , RIC3 , RIT2 , SCGN , SERPINH1 , SMAD7 , SPDL1 , SPHK1 , STMN1 , TACC2 , TBX3 , TERT , TGFBI , THEM6 , TRPM4 , ZNF124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclin D1 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRA2A , BLM , BMP1 , CEBPD , CGREF1 , CHGA , CHRNA5 , COL4A2 , CTF1 , DCAF7 , DNASE2 , EGR1 , EPHA2 , FDXR , FHL2 , GADD45A , GALNS , HNRNPA0 , HSPG2 , HTR6 , ID1 , KCNAB2 , KIF22 , KLF4 , MALL , MKI67 , MSN , MYL6 , MYT1 , NCSTN , NSG1 , OPRD1 , PDE2A , PLOD1 , PPIB , PTPN3 , RAB31 , RASGRF1 , REEP5 , RPS6KA1 , RRAS , SELPLG , SHC3 , SLC12A4 , SLC6A9 , SMOX , SYN1 , TAGLN , TAP1 , TFPI2 , TGFB1 , THY1 , TK2 , TRAF1 , ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.prostate Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM2 , ANGPTL4 , ARHGAP24 , CAMK2B , CEL , CFH , CHRNA3 , COL26A1 , DNM1 , ENG , FSD1 , GLB1L2 , HKDC1 , IL7R , INSM1 , ITGA2 , KLRG1 , KREMEN2 , LMO1 , LRRC15 , MAP3K1 , MMP11 , MYO7B , MYRIP , NOL4 , PADI3 , PCDHA2 , PLCH2 , PLLP , POPDC2 , SV2C , SYT5 , TEC , TG , THSD4 , TLR4 , TPK1 , TWIST1 , VEGFC , YPEL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mtor Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADORA2B , ALPK2 , BACH2 , BDH1 , BST2 , CDK1 , CDKN2B , DBF4 , GCH1 , GGACT , GSDME , H6PD , HELLS , IFI30 , IFI35 , IFIT1 , IFIT2 , IL27RA , LGALS3 , LIPG , MCM5 , MCM6 , MGARP , MSX2 , MYO7B , NABP1 , NEIL3 , NIPSNAP3A , NKAIN1 , NQO2 , NTSR1 , PAFAH2 , PCNA , PCYT2 , PDK1 , PLAT , PTPN14 , PYGL , RCOR2 , RD3 , SP100 , STMN1 , TESC , TG , TMEM97 , TNFRSF12A , UBE2C , UHRF1 , USP18 , VIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wnt Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ABCC3 , ACKR1 , ACVR1B , ADAM12 , ADAM19 , APC2 , CNTN1 , COL9A1 , CYBA , DDX25 , DPF3 , FAAH , FZD7 , GRM8 , HAND1 , HLA-B , HSD3B7 , IFIH1 , IGFBP6 , IRF9 , ISG15 , KCNA3 , KITLG , LGALS3BP , MET , MMP3 , NAGK , NFATC2 , NGEF , NGF , NMT2 , NT5DC2 , OLFM1 , PCDH7 , PHOSPHO2 , PIGN , PTGS2 , RAI2 , SDSL , SEPTIN6 , SINHCAF , SLC22A18 , STC1 , SYT11 , TFR2 , TGFBR3 , TLR6 , USP18 , VIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.300 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ACTG2 , BST2 , CA5B , CGREF1 , CHRM2 , CRABP2 , CSDC2 , DPT , EPHB6 , EPHX2 , FGFR3 , GADD45G , GBP1 , GRM2 , HSPB8 , HTR1B , HTR1D , IFI44L , MAML3 , MAP2K6 , MTSS2 , MX1 , MX2 , MXD3 , NOS1 , OLFML2A , PDE11A , PPFIA3 , PSORS1C1 , RRAD , RUNDC3B , RYR2 , SLC9A7 , SOX11 , SPTBN2 , TAGLN , TEX15 , THRB , WHRN , YBX2</t>
+    <t xml:space="preserve">AMOTL2 , ANKRD44 , ASPH , CITED2 , CNN1 , CRABP2 , CRYBG1 , DLK1 , FRMD5 , GNA14 , GPR19 , GRIN1 , H2BC21 , HAS2 , IL1R1 , ITGA4 , JPH3 , KIAA1217 , LYST , MAF , MGP , NLRX1 , NOTCH1 , NR6A1 , PHLDB2 , PIGT , PLA2G4A , RAG2 , SETDB1 , SEZ6 , SIX4 , TM4SF1 , TMPO , WWC2</t>
   </si>
   <si>
     <t xml:space="preserve">Kras.breast Up.v1 Up</t>
   </si>
   <si>
-    <t xml:space="preserve">AKAP12 , BIRC3 , CALB1 , COL9A1 , COL9A3 , CTNNA2 , GSG1 , HAS2 , HSD17B2 , IGFBP3 , IL17RB , IL1B , IL1RAPL1 , KCNAB3 , KCNK15 , KCNK3 , KIF5A , LIF , MAPK4 , MGLL , MMP10 , MMP9 , MYCN , NPAS1 , NPPB , NRL , OSGIN1 , PDE2A , PDE3B , PPP1R15A , SNAP25 , SPON2 , STC1 , STX1A , SYP , TAGLN3 , TERT , TFPI , TNFAIP3 , TRAF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pten Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA6 , ADCYAP1R1 , ADGRE5 , B3GALT5 , B4GALNT1 , C1QTNF1 , CCDC68 , CDH10 , CDH11 , CHST7 , CPLX2 , EMP3 , FJX1 , FOLR3 , FOSL1 , FST , GNG11 , HLA-DMA , HLA-DPB1 , HPCAL4 , HS3ST1 , INPP4B , ITIH3 , KRT81 , LCP1 , LUM , MAMLD1 , MSX2 , MTUS2 , NPPB , OLFM1 , OPRM1 , PNMA3 , PROX1 , PSMB9 , RFPL1S , RLN2 , SELL , SEMA4D , SERPINE2 , SGCE , SH3BGRL , ST8SIA3 , SUGCT , SV2C , TBX3 , TENM1 , TLE6 , TNR , TSPAN7 , TWIST1 , UGT8 , VIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclin D1 Ke .V1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRA2A , AHR , ATXN1 , CDK6 , CDKN1A , CDKN2A , CEBPD , CGREF1 , CHRNA5 , CHRNB4 , COL18A1 , COL5A2 , DAP , DCAF7 , DNASE2 , DUSP4 , DUSP5 , EPHA2 , FAM3C , FHL2 , FOSL2 , GLI1 , GNAI2 , HSF4 , HSPG2 , HTR6 , ID1 , KCNAB2 , KIF22 , KIFC1 , KLF4 , MALL , NRG1 , NTN3 , PDE4C , PLOD1 , POLD1 , PPIB , PRPH , PTPN3 , RAB31 , REEP5 , RRAS , RUNX1 , S100A2 , SLC35D1 , SLC38A3 , TGFBR2 , THY1 , TNNT2 , TRAF1 , TRIO , TROAP , ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.600.Lung.breast Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADAMTS20 , ADD2 , APC2 , APOL3 , BDKRB1 , BTN3A2 , CA5B , CACNA2D3 , CALCB , CCDC102B , CD248 , CD36 , CLCA2 , COL5A2 , COL5A3 , CRABP1 , CRABP2 , CREB3L1 , CRYAB , DENND2D , DLX6 , DPT , ELMO1 , ENTPD5 , EPHX2 , ERAP2 , FGF1 , FGFR3 , FGGY , FRAS1 , FSCN2 , GADD45G , GAS1 , GBP1 , GBP2 , GDNF , GPRC5B , GRIA1 , HCN2 , HTR1B , HTR1D , HTR1E , IFI44L , IL18R1 , IMPA2 , IVL , MAML3 , MAP2K6 , MAP3K1 , MMP28 , MXD3 , NECTIN1 , NEUROD1 , NINJ1 , NOS1 , OLFML2A , PAQR6 , PARP3 , PGGHG , PLAAT4 , PLXND1 , PPFIA2 , PPFIA3 , PSORS1C1 , PTPRJ , RUNDC3B , SH3GL3 , SLC30A3 , SLC6A9 , SOBP , SOX11 , SPTBN2 , SYNDIG1 , TEX15 , THAP9 , THBS3 , TRIM58 , TRIM9 , TYRP1 , WHRN , YBX2 , YPEL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singh Kras Dependency Signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD3 , C6orf141 , LAMA3 , LAMC2 , MAOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gli1 Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGFBP6 , LMO7 , M6PR , NPHP1 , PTH1R , TMOD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapa Early Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP4 , AXL , CIT , CNKSR2 , COBLL1 , COL9A1 , COL9A2 , CRIP2 , CRMP1 , DDN , DUSP14 , ENG , EPHB4 , FLOT1 , FLT3LG , GALNS , GFRA2 , GLUL , GPR12 , GRIN1 , GRM2 , GRN , HLA-E , HLCS , IGFBP3 , LGALS3BP , LMNA , MAP1A , MET , MGST2 , MID1 , MYCN , NAGPA , NCAPH , NFE2L1 , PHYHIP , PINK1 , PLEKHO2 , PLPP3 , PLXND1 , PSD , PTCH1 , PTGS1 , ROR2 , SELPLG , SF3A2 , SMAD9 , SNTB1 , TH , TRIM22 , TROAP , TSPAN4 , WFS1</t>
+    <t xml:space="preserve">BMP6 , CALB1 , COL9A3 , CTNNA2 , HAS2 , IGFBP3 , IL13RA2 , KCNAB3 , KCNK3 , KIF5A , LIF , MAPK4 , MGLL , MMP10 , MYCN , NPAS1 , NRL , OSGIN1 , PDE2A , PDE3B , PPP1R15A , SNAP25 , STC1 , STX1A , SYP , TAGLN3 , TERT , TNFAIP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nfe2l2.V2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCC2 , ABHD4 , ACKR3 , ADRA1A , AIFM2 , AKR1C1 , AKR1C3 , AXIN2 , BCL2L11 , BRIP1 , C1S , C1orf21 , CBR3 , CCDC138 , CCND3 , CDKN2B , CFI , CKAP4 , CPLX1 , CPLX2 , CXCL12 , DDC , DHFR , ECM2 , EFCAB14 , EPHX1 , F2RL2 , FAM86DP , FGF7 , FTH1 , FTL , FZD7 , G6PD , GCLM , GPC1 , GPNMB , GRPR , HMOX1 , HPDL , IGFBP3 , ITGB8 , JDP2 , KCNE4 , KCNQ2 , KIF5C , KPNA5 , L1CAM , L3HYPDH , LINC01963 , MAP2 , MCF2L-AS1 , MCM10 , MCM3 , MELTF , MGST1 , MPP3 , MPPED2 , MRAP2 , NDUFC2 , NEDD4 , NEIL3 , NQO1 , NQO2 , NR0B1 , NRCAM , NSD2 , NUPR1 , OSGIN1 , OSTF1 , PALLD , PCSK6 , PEG3 , PHLDB1 , PLXND1 , PPFIA2 , PRR36 , PTGR1 , RDM1 , REEP1 , RET , RIMKLA , RPL22L1 , SCARA3 , SCUBE1 , SLC2A4 , SLC7A11 , SMAD9 , SPTB , SQSTM1 , ST8SIA2 , STXBP5L , SULT1E1 , SUV39H2 , TERT , TET1 , TLR4 , TP73 , TSPAN7 , VIL1 , VTN , XYLB , ZNF135 , ZNF714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.lung.breast Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADAMTS20 , ADD2 , ALOX12B , BDKRB1 , CD248 , CRABP2 , ERAP2 , FGFR3 , FRAS1 , HCN2 , IFI44L , IVL , MAP2K6 , MMP28 , MTHFR , NOS1 , OLFML2A , PAQR6 , PGGHG , RUNDC3B , SLC6A9 , SOBP , SOX11 , SPTBN2 , SYNDIG1 , TRIM9 , YPEL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tbk1.Df Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANGPTL4 , ATP6AP2 , BCL2L1 , BDH1 , CASP6 , CAVIN2 , CBX5 , CD2AP , CDK6 , CHMP2B , CLN5 , COL4A1 , CXADR , DCP2 , DDX60 , DKK1 , DNAJB14 , DNAJC3 , ELL2 , ERAP1 , GALNT7 , GAS1 , GJA1 , GOLT1B , H1-2 , HIPK3 , HMBOX1 , HNRNPA0 , HOOK1 , IFIT1 , ITGA2 , KLF5 , KLF7 , LIMS1 , LMNB1 , LUC7L3 , MAOA , MSH2 , NEK7 , OSBPL3 , PAFAH1B3 , PCYOX1 , PDGFA , PLEKHA2 , PPCS , PSMB8 , PSMB9 , RAI14 , SEMA3C , SERPINE2 , SLC37A4 , SMURF2 , SNTB2 , SPDL1 , SRPRA , THBS1 , TLN1 , TMOD3 , UFL1 , ZNF395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brca1 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDH13 , CHD5 , DDX25 , EXTL1 , HMGA2 , LDB2 , LRRTM2 , MAP2 , N4BP2L2-IT2 , NLGN4Y , P3H3 , PHOX2B , RAG2 , RNF122 , SHANK1 , SIX1 , SLC16A4 , SP4 , STAR , TENT5C , THBS2 , TNC , TRPA1 , TSSK2 , TTLL7 , ZNF423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirna Eif4gi Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2B4 , ATP6V0E1 , C1QTNF1 , CYTL1 , DUSP4 , EIF5A2 , FAM111A , FSTL1 , LOXL2 , NEDD4 , NEK7 , PAPSS2 , RIPK2 , S1PR1 , SCML2 , SMURF2 , SP140L , SSR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notch Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCA1 , ACKR3 , AMOTL2 , CD82 , CHST1 , CRMP1 , CYP7B1 , DLK1 , DNAJC3 , DRAM1 , E2F2 , FCGRT , FSTL3 , ID1 , IL11 , IL7R , ITGA9 , KCNN1 , KLF15 , KLF2 , MMP25 , MRM1 , MYCN , MYO1D , MYO1E , NID1 , NOTCH3 , PLAT , RAMP2 , RPL39L , SERPINE1 , TUBB2B , VN1R1 , ZFP37 , ZNF221 , ZNF74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ctip Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHODL , COPZ2 , CXCL8 , FSTL4 , GDF10 , GNG7 , GRPR , INA , INSR , KCNK2 , LMO1 , NPPA , OLFML2B , ONECUT2 , PCDHA5 , PDGFRL , PMEL , PNMT , PPEF1 , SALL2 , SLC16A4 , TERT , TESMIN , TSSK2 , ZNF253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclin D1 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ACVR1 , CBLN1 , CHRM1 , CXCR4 , DNAJB4 , EZH2 , GAL , GATA4 , GNAZ , GNS , IL1A , IL7R , INHBA , ITGA3 , KIF1A , LAMB1 , MAPK8IP2 , MOK , MYO1C , N4BP2L2-IT2 , NEDD4 , NOS1 , NR6A1 , PAFAH1B3 , PBXIP1 , PIK3R1 , RAB9A , RBMS2 , RGS16 , S100A4 , SMPD1 , SYPL1 , SYT1 , TPD52 , TPM2 , VASP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak2 Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMTSL4 , ATP8B1 , CEP152 , COL26A1 , DBH , DLL3 , DOCK5 , DPY19L2P2 , ECM2 , FLCN , GOLGA2P10 , HIBADH , KIF13A , KIRREL1 , LRRC37A2 , MBTD1 , MTMR11 , NAALAD2 , PEX3 , PGAP1 , RFX3 , SIGLEC15 , SOCS7 , STAG3L1 , SUZ12P1 , TRIM36 , ZNF221 , ZNF551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc2 Suz12 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGER , ALOXE3 , ANK1 , AP1M2 , ARRB2 , CACNA2D2 , CACNG2 , CIB1 , DCC , DCX , DLGAP1 , FRMD8 , HOXD11 , IL10RA , KAT8 , KBTBD11 , KLF15 , KLHL23 , LDB2 , LMOD1 , LRP5L , MAPT , NLGN1 , NPY2R , ONECUT2 , PGAP1 , PHOX2B , PNPLA3 , PTPRO , RECQL4 , RFX2 , RUNDC3A , SCHIP1 , SLC16A10 , SLC35D1 , SYN3 , ZNF695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.600 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCB1 , ACKR3 , ADAMTS9 , BCL11B , C1QL1 , CADM4 , CAMK1D , CCDC102B , CCDC33 , CD207 , CD248 , CHRM2 , CLIC3 , CNTFR , CRABP2 , CSDC2 , CSPG4 , DLK2 , DLX6 , EDN1 , EPHB3 , EPHB6 , FGFR3 , FGGY , FRAS1 , GBP1 , GPR173 , GRM2 , HOXC8 , HRH3 , HSPB8 , IFI44L , IMPA2 , IVL , KCNQ3 , MAML3 , MAP2K6 , MCHR1 , MTSS2 , MX1 , NINJ1 , NOS1 , OLFML2A , PNMT , PPFIA3 , RRAD , RUNDC3B , RYR2 , SCGN , SLC9A7 , SOX11 , SPTBN2 , TAGLN , TEX15 , TGFB2 , WHRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.amp.lung Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATK , ACE , ADAMTS5 , APC2 , CORO2B , CPLX2 , CTF1 , DCC , EPB41 , GDF10 , GNAZ , GPRC5C , H2AJ , HOXC8 , KCNN1 , KREMEN2 , PAIP2B , PGPEP1 , PPFIA3 , PROM1 , RBFOX1 , RELB , SHANK1 , SNCB , TLR4 , USP53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prc1 Bmi Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKS1B , APOBEC3F , CACNA2D2 , CD207 , CHRNA3 , CLIC3 , DCC , DDX25 , FGFR3 , FKBP5 , GAS1 , GFAP , HOXD11 , IFIT1 , INKA2 , KBTBD11 , KCNC1 , LINC02249 , LMOD1 , LRRC37A4P , ONECUT2 , P2RX3 , PCDHA10 , PEAK1 , PLXNB3 , PNPLA3 , PTPRO , SDK2 , SHANK1 , SLC16A10 , SLC66A3 , SPTBN2 , STMN3 , SYN1 , SYN3 , TRPM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirna Eif4gi Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASAH1 , ATF3 , CEBPD , CORO1B , CTSC , ESYT1 , HLA-B , HSPB1 , IGF2R , LRPAP1 , NQO1 , NSG1 , PSAP , PYGL , SETDB1 , SUGCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camp Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL4 , APOBEC3C , ATXN7L3B , CHAF1A , CKMT1A , COL6A3 , CRABP1 , CXCL8 , ECSIT , ELMO1 , FLOT1 , HMGB2 , HSPA5 , IFIT2 , IFITM3 , LIMS1 , MAD2L1 , MYC , NDEL1 , NDRG2 , NLRP1 , NQO2 , NUAK2 , P4HB , PPIB , PPP1R15A , PRIM1 , PXK , SEC61A1 , SESN2 , SIL1 , SSR3 , TGFBI , TMED9 , TNIK , TRIM38 , UPP1 , WIPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclin D1 Ke .V1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACKR3 , ADARB1 , ADD3 , ALK , ATP2B3 , CHRNB2 , COL3A1 , CRMP1 , CXCL12 , DNAJB4 , DPF1 , F3 , GJA1 , GNAZ , GPSM3 , GRIA1 , IFIT3 , IL1R1 , IL7R , KIF1A , LIMS1 , MAPK4 , MX1 , MXI1 , NEDD4 , NKX3-1 , NOS1 , NPAS1 , NR6A1 , NTSR1 , PAFAH1B3 , PIK3R1 , POU2F2 , SALL2 , TMSB15A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2f3 Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM2 , ANKRD46 , ARHGAP18 , BDKRB2 , C16orf74 , DCC , GIPR , GPRC5A , GRID1 , IRAK2 , KCNQ1OT1 , KRT80 , LIF , LINC00842 , MMP1 , MMP3 , NACC2 , NR6A1 , NRL , OLFM1 , PC , PLAT , PODN , RAB43 , SPTB , STX1A , STXBP5L , TGM2 , TLR2 , ZNF135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myc Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5orf46 , CALML4 , CDCA7L , COQ8A , DENND2D , DGAT2 , DLL3 , DPYSL5 , HLF , HS3ST3A1 , HS6ST2 , ITPR1 , JPH1 , KLRG2 , MMP25 , NEFH , OAF , P2RX5 , PCDHB18P , PCOLCE2 , PLA2G4A , PLD6 , PRR3 , S100A10 , SIX3 , SLC25A25-AS1 , SLC29A4 , SLC6A15 , TAF4B , TAF5 , TMEM132B , TMEM97 , ZNF420</t>
   </si>
   <si>
     <t xml:space="preserve">Brca1 Dn.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">BMPR1B , BRCA1 , C14orf93 , CARD10 , CDC42EP2 , COLQ , CYSLTR2 , CYTH3 , DLK2 , E2F2 , EXOC6B , GABRB3 , GM2A , GPR19 , GREB1L , GRIP1 , HAND1 , HSD11B2 , IFI35 , INSR , ITIH3 , KCNQ2 , LRRC17 , MSH5 , MX2 , NRGN , OLFML2B , PDLIM3 , PNMA3 , PPM1E , PROX1 , RBP4 , SNAI1 , SUSD5 , TCF7L1 , VAMP3 , ZMYND10 , ZNF124 , ZNF253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dca Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP5 , ADAM19 , AK5 , ARHGDIG , ATP1B2 , AURKB , BCAS4 , BFSP1 , CACNG5 , CD82 , CDC45 , CFAP70 , CLN6 , COLQ , COPZ2 , CRIP2 , CUBN , CXCL8 , DEPP1 , EFS , ELAVL4 , EPHB6 , EYA2 , FRMPD1 , GARNL3 , GIPR , GRIA1 , GRIN2D , HTR6 , IFIT2 , KIAA0513 , KREMEN2 , LIMD1 , LPAR3 , MAPK8IP2 , MCTP2 , MIR600HG , MX1 , MYCT1 , MYOZ3 , NRXN2 , NTN3 , PHLDB1 , PTPRT , RNASEL , RNF125 , SIX1 , SLC66A3 , TNNT2 , ZNF157 , ZNF185 , ZNF91 , ZSCAN12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rb P130 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP24 , ASB13 , ATP6AP2 , B2M , C9orf72 , CASP6 , CLIP1 , CLU , CTSB , CTSC , CXCL12 , DDX1 , DNAJC1 , EOGT , ERAP1 , EVI5 , GADD45A , GNS , HTRA1 , KIF16B , LAMP1 , LAMP2 , LIFR , NEAT1 , NRARP , PARP9 , PCDHB17P , RCN1 , RNASET2 , RRAS , SEC23A , STAT1 , STAT6 , TMEM140 , TOMM34 , USP18 , VDR , VOPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yap1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FICD , GOLGA2P5 , IL4R , ITGA2 , ITGBL1 , LCA5L , LIMD1 , MYLIP , PDIK1L , SLC9A1 , VSNL1 , ZBTB39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gli1 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD2AP , ESYT1 , RUNX1 , SPECC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rb P107 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADVL , ACP5 , ANXA1 , ANXA4 , ARL1 , ARPC1B , BDH1 , CAP1 , CRABP2 , CTSL , CXCL12 , EDN1 , ELOVL1 , GBE1 , GNG12 , H2BC4 , LACTB2 , LPAR3 , MBNL3 , MYO1D , NFE2L1 , NFE2L2 , NMI , NRBP1 , NUCB2 , PAFAH1B3 , PANK1 , PEX3 , PLEKHA7 , S100A16 , SCD , STAT6 , TDRD7 , TLR2 , TPRG1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P53 Dn.v2 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM12 , ANGPTL4 , APOL3 , CACNG2 , CD68 , CHST8 , CLCF1 , CXCL12 , CXCL8 , DLX6 , DPF1 , EVI2A , FOSL2 , FOXL2 , H6PD , HTR1E , IER3 , IL1RAPL1 , ITM2A , KCNK3 , LRRC32 , MMP3 , NFIX , NTRK3 , NTSR1 , OSGIN1 , PCDH1 , PPEF1 , PRRG3 , PTX3 , RELB , RIPK4 , SDC4 , SLC16A4 , SLC38A3 , SYN1 , TDRKH , TFAP4 , TNFAIP3 , TNFRSF9 , TNR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pdgf Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM9 , ANXA7 , ARC , CBX2 , CDC25A , CDK5R2 , CDK6 , CDKN1A , CITED1 , DUSP5 , EGR1 , ELOVL2 , FAM3C , FAM98A , FOS , FOSL1 , GADD45A , GNG11 , HSPA2 , HTR1E , INHBA , KBTBD11 , KCNK3 , LRPAP1 , NAGLU , NEDD9 , RNF14 , SDC3 , SIK1 , SLC30A1 , SLC39A7 , SLC7A5 , SNRNP35 , STK10 , SUZ12P1 , TET3 , TFPI2 , TJP2 , TMEM158 , TRAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat.100 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMH , DEPP1 , DOCK3 , FZD4 , IGFBP5 , KLHL4 , SNAI2 , TENT5A , ZNF711 , ZNF749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapa Early Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGRE5 , ANK1 , ASPH , ASTN2 , C2orf72 , CBX5 , CCDC88C , CDC42EP2 , COL5A2 , COL6A1 , CTSD , DLX5 , FGFR2 , FKBP1A , GNG12 , GREB1 , GRPR , HERC3 , HIVEP1 , HOXD10 , ITGA5 , KCNC4 , L1CAM , MYRF , NINJ1 , NRL , NUCB1 , OLFML2A , PAQR4 , PART1 , PDE2A , PDE4A , PDE5A , PLEKHA6 , PRKCG , RAD9A , SHC3 , SLIT1 , SSH1 , ST8SIA3 , STUM , TCTA , TIMP2 , TLE3 , TRIM38 , VTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ctip Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABI3BP , ABLIM2 , AMPH , ANO1 , BCAM , CAMKV , CARD10 , CCNA1 , CDKN1C , CEMIP , CITED1 , CTF1 , CYBRD1 , DGCR11 , ECE2 , EDEM1 , EDN1 , FMO5 , GPR19 , HIBADH , IGSF9B , KCNC1 , KCNH7 , LINC01963 , LRRC32 , OLFML2A , PTGS1 , RAC3 , RASGRF1 , RNF125 , SLC35D1 , STAG3 , SYNDIG1 , TENT5C , TRPC6 , TSPAN7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jnk Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCD1 , ACKR3 , ADAM12 , ADAMTS3 , AGTPBP1 , AKR1C3 , B3GALT5 , BAG2 , BIRC3 , BMP7 , C1S , CACNA1H , CLCN4 , CRMP1 , CXCL8 , DDIT3 , ECM2 , EPHA4 , EYA2 , FAM161A , GCH1 , GNAZ , GPX7 , HR , HSPA12A , HTR6 , IGFBP3 , KCNJ9 , KCNS1 , MAP7 , NID2 , PAPSS2 , PDE4B , PIP4K2A , PMEL , PRR3 , RGL1 , RIPOR2 , RRAD , RUNX2 , SHC3 , SLCO2B1 , SNAI2 , STARD13 , SYNE1 , TET3 , TNFSF4 , TNNT2 , TRIM24 , YAP1 , ZFHX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alk Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADCY2 , AQP3 , ARID3B , CCDC81 , COL9A3 , CRYAB , CTF1 , DOC2A , EFNA2 , FOS , FXYD6 , GRM2 , GSG1 , IFI44L , IFI6 , IGFBP6 , IRF9 , KCNC3 , KCNJ9 , KCNN4 , KIAA0408 , LPAR2 , MX1 , NMNAT2 , OPRD1 , PRODH , PRPH , PSORS1C1 , RPL23AP7 , SEMA3E , SPTB , ST8SIA3 , STUB1 , TEDC2 , THSD4 , TIAM1 , UNC93B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gcnp Shh Up Early.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AURKB , CHEK1 , CKS2 , CSF1 , DHFR , DNAJC3 , E2F8 , ELOVL2 , EPB41L4B , FCGRT , FEN1 , FOSL1 , GTF2H1 , HLA-B , HMGCL , KIF1A , KIF1B , KIF4A , KIFC1 , LBR , LOXL2 , MAN1A1 , MBTD1 , MCM10 , MCM5 , MCM6 , MSH6 , MYB , MYT1L , NABP1 , NR0B1 , PLCG2 , POLA2 , PRC1 , RPL39L , RRM1 , SDC3 , SGO1 , SLC27A1 , SPDL1 , STYX , TOP2A , TOP2B , TRAIP , TYMS , UBE2T , WFDC21P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il21 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADTRP , AP3B2 , BICDL1 , CACNA2D3 , CD177 , CEL , CHGB , CNTN2 , CORO2A , CUX2 , DNAH7 , DOC2A , EPS8 , FRMD4A , GCNT4 , GDNF , HKDC1 , ITGA2 , ITGA6 , JCAD , KCNC4 , KCNS1 , LMOD1 , LRP5L , MAB21L1 , MIR600HG , NEFL , NRXN1 , OSGIN1 , PACRG , PCDH9 , PDE1C , PLPPR4 , PNMA3 , PRKG1 , PRKG2 , PROX1 , PRR5L , RIN2 , SEC14L2 , SLC17A5 , SLC8B1 , SP4 , SPTBN4 , TESMIN , TFAP2B , TG , TSPAN7 , USP18 , WNT4 , ZNF286A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.600 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ACTG2 , ADAMTS9 , APOL3 , BCL11B , BST2 , C1QL1 , CA5B , CADM4 , CALCB , CCDC102B , CCDC33 , CD248 , CD36 , CGREF1 , CHRM2 , CLCA2 , CLIC3 , CNGB1 , CNTFR , CRABP2 , CSDC2 , CSPG4 , DBF4B , DLK2 , DLX6 , DPT , EDN1 , ENPP1 , EPHB3 , EPHB6 , EPHX2 , FGFR3 , FGGY , FRAS1 , GADD45G , GBP1 , GPR173 , GRM2 , HOXC8 , HRH3 , HSPB8 , HTR1B , HTR1D , IFI44L , IMPA2 , IVL , LYPD3 , MAML3 , MAP2K6 , MATN2 , MCHR1 , MTSS2 , MX1 , MX2 , MXD3 , NINJ1 , NOS1 , NRXN3 , OLFML2A , PDE11A , PPFIA3 , PRODH , PSORS1C1 , RRAD , RUNDC3B , RYR2 , SCGN , SLC9A7 , SOX11 , SPTBN2 , TAGLN , TEX15 , TGFB2 , THRB , VGLL3 , WHRN , YBX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.lung.breast Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADAMTS20 , ADD2 , BDKRB1 , CALCB , CD248 , CD36 , CLCA2 , COL5A2 , CRABP2 , DPT , EPHX2 , ERAP2 , FGFR3 , FRAS1 , GADD45G , GDNF , HCN2 , HTR1B , HTR1E , IFI44L , IVL , MAP2K6 , MMP28 , MXD3 , NOS1 , OLFML2A , PAQR6 , PARP3 , PGGHG , RUNDC3B , SLC6A9 , SOBP , SOX11 , SPTBN2 , SYNDIG1 , TRIM9 , YPEL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pdgf Erk Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM , APC2 , BCL10 , CCNF , CEBPB , CKS2 , CNTRL , DUSP1 , DUSP8 , EGR1 , GIPC1 , HIC2 , IDUA , IL7R , ISL1 , ITGB6 , JUN , KLHL25 , LTBP1 , MAB21L1 , MAFF , MFSD5 , MYC , MYCN , NCAPH2 , NEFH , PDE4A , PHOX2B , PPP2R5B , RHOB , RTN2 , SLC3A2 , SMAD7 , SMOX , SULT1A1 , TGIF1 , TMED5 , TRAIP , ZBTB5 , ZFP36L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notch Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA1 , ACKR3 , ADTRP , AMOTL2 , C3AR1 , CA8 , CCDC81 , CD82 , CEL , CRMP1 , CYP7B1 , DLK1 , DNAJC3 , DOC2A , DRAM1 , E2F2 , FCGRT , FSTL3 , HES1 , HS1BP3 , ID1 , IFI30 , IL11 , IL7R , INSM1 , ITGA9 , KCNN1 , KLF15 , KLF2 , MYCN , MYO1D , MYO1E , MYO7B , NID1 , NOTCH3 , PLAT , RAMP2 , RPL39L , SERPINE1 , SLC28A3 , TBX3 , TFPI2 , TMEM92 , TUBB2B , VN1R1 , ZC3H12A , ZFP37 , ZNF221 , ZNF74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atm Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCA8 , ADARB1 , APBA2 , ASIC4 , BCHE , BCL2L11 , BDKRB1 , CD36 , CD8A , CHGB , CNTFR , COL9A3 , DLX6 , DYSF , ECM2 , FGF5 , FSTL3 , GAB2 , H6PD , IGFBP4 , ITIH3 , LHPP , PARP3 , PARVA , PLTP , PPL , PSG5 , RAB3A , RECQL4 , RET , S100A2 , S100A3 , SLC7A5 , SNCB , SPAG4 , STAG3 , SYN1 , TRAF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.amp.lung Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ABCD1 , ACE , ADAMTS5 , APC2 , CGREF1 , CORO2B , CPLX2 , CTF1 , DBF4B , DCC , DNM1 , ENPP1 , EPB41 , GDF10 , GNAZ , GRIK5 , H2AJ , HOXC8 , HTR1D , KCNN1 , KREMEN2 , MXD3 , PAIP2B , PDE11A , PGPEP1 , PLCH2 , PPFIA3 , PPM1H , PRODH , RBFOX1 , RELB , SHANK1 , SNCB , STARD8 , TLR4 , USP53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bcat Gds748 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS20 , CELSR1 , GAS1 , HLX , PMFBP1 , RPS6KA5 , SKP2 , SNAI2 , TENT5A , ZNF273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il15 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM12 , ARL4C , ATP8A1 , BICDL1 , C14orf132 , CD177 , CDKN1C , CLDN11 , CLGN , CNTN1 , CUX2 , DACT1 , DEPTOR , DOCK3 , ENTPD5 , EPS8 , EVI2A , FSTL3 , GDNF , GEM , HOXD13 , HTR2B , JCAD , KCNC4 , KCNS1 , KIZ , MAP2K6 , MFSD13A , MMP19 , MTARC1 , PARP11 , PBXIP1 , PIK3IP1 , PLCL1 , PRKG1 , RIN2 , RLN2 , S100A3 , SCN3A , SEC14L2 , SEMA6D , SIGLEC15 , SNAI2 , SPAG4 , TBC1D2 , TG , TGFB1I1 , TNS3 , WNT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ctip Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCAN , CHODL , COCH , COL1A2 , COPZ2 , CXCL8 , DDIT3 , EFS , EGFL7 , FSTL4 , GDF10 , GRPR , IFI6 , INA , INSR , KCNC4 , KCNK2 , KCNS1 , LMO1 , NPPA , OLFML2B , ONECUT2 , PDGFRL , PMEL , PPEF1 , PSG7 , PTH1R , SLC16A4 , SLC35G2 , SNAI1 , TERT , TESMIN , TRAF1 , ZNF253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nfe2l2.V2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCC2 , ABHD4 , ACKR3 , ADAMTS12 , AIFM2 , AKR1C1 , AKR1C3 , AXIN2 , B4GALNT1 , BCAN , BCL2L11 , BRIP1 , C1S , C1orf21 , CBR3 , CBS , CCDC138 , CD101 , CDC45 , CDKN2B , CFI , CHRDL2 , CKAP4 , CNTNAP5 , CPLX1 , CPLX2 , CRTAP , CXCL12 , DBF4 , DBF4B , DDC , DHFR , ECM2 , EFCAB14 , EPHX1 , ESCO2 , F2RL2 , FGF7 , FTH1 , FTH1P20 , FTL , FZD7 , G6PD , GAS7 , GCLM , GPC1 , GPNMB , GRPR , HPDL , HSPB3 , IGFBP3 , IL18R1 , ITGB8 , JAKMIP3 , JDP2 , KCNE4 , KCNQ2 , KIAA0319 , KIF5C , L1CAM , L3HYPDH , LANCL3 , LINC01963 , MAP2 , MCF2L-AS1 , MCM10 , MCM3 , MDFIC , MELTF , MPP3 , MPPED2 , MRAP2 , MTBP , NEDD4 , NEIL3 , NFE2L2 , NMRAL2P , NQO1 , NQO2 , NR0B1 , NRCAM , NSD2 , NUPR1 , ORC1 , OSGIN1 , OSTF1 , PALLD , PATJ , PCSK6 , PEG3 , PHLDB1 , PLXND1 , PPAT , PPFIA2 , PRR36 , PRR5 , PTGR1 , RDM1 , REEP1 , RET , RHBDL3 , RIMKLA , RPL22L1 , SCARA3 , SCUBE1 , SIAE , SLC2A4 , SLC7A11 , SLCO2B1 , SLCO4C1 , SMAD9 , SPP1 , SPTB , SQSTM1 , ST8SIA2 , STXBP5L , SULT1E1 , SUV39H2 , TERT , TET1 , TEX19 , TLR4 , TP73 , TPD52L1 , TSPAN7 , TXNRD1 , VTN , XYLB , ZNF135 , ZNF367 , ZNF714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mtor Up.n4.V1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAM9 , ADARB1 , ADM , ANXA3 , APOL6 , ARG2 , BCHE , BHLHE40 , CALML4 , CAMKV , CEBPB , CLIC4 , CYTL1 , DDIT3 , DDN , DNMT3B , EAF2 , FAH , FAS , FGF1 , GAS2L1 , GBE1 , GCH1 , GRM2 , HERPUD1 , IFI30 , IL21R , IL7R , ITPR1 , LGMN , LIMA1 , MAP1A , MGAT4A , NIBAN1 , NQO2 , OPCML , PHACTR2 , PTPRK , RIMS3 , RIT1 , SLC1A5 , SLC3A2 , SLC6A9 , SLC7A11 , SLC7A5 , SLCO4A1 , SPRED2 , SQOR , STX4 , TRIB3 , UGCG</t>
+    <t xml:space="preserve">BMPR1B , CARD10 , CYTH3 , DLK2 , E2F2 , GABRB3 , GM2A , GPR19 , GSDMD , HAND1 , IFI35 , INSR , KCNQ2 , LRRC17 , OLFML2B , PDLIM3 , PNMA3 , PPM1E , PROX1 , TCF7L1 , VAMP3 , ZNF124 , ZNF253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.lung Up.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACHE , ADD2 , CD248 , CDKN1C , CRABP2 , EMID1 , EPHB3 , GAS1 , GPNMB , IL10RA , IVL , LMO1 , MAP2K6 , MAP3K1 , OLFML2A , PROM1 , SCRG1 , SGCD , SH3GL3 , SLC6A9 , SPTBN2 , STAG3L1 , THAP9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rela Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMPR1B , C1orf21 , CALY , DLK1 , DNMT3A , HOXD3 , IDUA , IL7R , KCNK5 , KNL1 , L1CAM , MBNL2 , NEURL1 , NNAT , PC , PKLR , PSD , RASA3 , RBP1 , RFX2 , SEZ6L , STAG3 , TAF13 , VEGFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Src Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABTB1 , AMER1 , ANGPTL6 , APC2 , ATP6V1E1 , BCL2 , COL26A1 , CPLX2 , CRTAC1 , DLL3 , DNAJC22 , FBLN2 , FNDC8 , GAS6-DT , GVQW3 , MAPK8IP2 , NAT8L , NEU1 , PRR3 , RAB3A , SCARF2 , SOCS1 , SUGCT , SULT4A1 , SYN1 , TECTA , TFR2 , TMEM255B , TMEM88 , TONSL , WTIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atm Dn.v1 Dn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALX3 , CLCN4 , CYP2J2 , ENTPD7 , FBXO24 , GRM8 , HS3ST3B1 , ITGB4 , KCNQ4 , NNAT , PLCD1 , PMEL , PRDM11 , RAPGEF4 , STK17B , SULT1E1 , TAGLN , ZFP36L1 , ZNF208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eif4e Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHLHE40 , CAMK2N2 , CNTN4 , FBXL13 , MAP2K3 , MAPK8IP1 , MRPL17 , PPCS , RIPOR3 , SLC25A30 , SNTB1 , TAX1BP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak2 Dn.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTA2 , ADCYAP1R1 , ADGRB1 , CACNB4 , CNKSR2 , COL6A3 , CPED1 , CSPG4 , DLGAP1 , ESRRG , FOXD1 , FRMPD1 , HRH3 , INA , LRIG1 , METRN , NELL2 , PHF14 , PTPRO , PXDC1 , SEMA5A , SNCB , SUV39H2 , ZNF821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kras.amp.lung Up.v1 Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLX5 , EFCAB6 , EFNA2 , FGF7 , HGFAC , KCNC1 , LRRC37A4P , NELL2 , NGF , NOVA1 , NPAS3 , NPHP1 , PNMA3 , REST , SEMA3E , SLC2A4 , ST3GAL6 , ST8SIA2 , VTN , ZNF257 , ZNF835</t>
   </si>
   <si>
     <t xml:space="preserve">Kras.kidney Up.v1 Dn</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCA3 , ACE , ADAMTSL2 , ASPN , B3GALT5 , CARD9 , CHRM2 , CNN1 , EGFL7 , EPHA5 , FCHO1 , GRM2 , GRM8 , HSD17B2 , IFI30 , IFI44L , ITIH5 , KCNN1 , MAGEA10 , MDFI , MSC , MX1 , MX2 , NGF , NPPB , PHLDA3 , PTGER2 , RASGRF1 , RYR2 , SEMA5A , SRC , STX11 , THRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mtor Up.n4.V1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5 , ARID5B , ATP6V1G2 , BCOR , BRIP1 , CEP68 , CHIC2 , CLN5 , DACH1 , DPY19L2P2 , EOGT , ERAP1 , EVI2A , FBLN5 , GALNT7 , H1-0 , H2AC6 , H2BC12 , HES1 , IKZF2 , LRRC37A4P , MIS18BP1 , MME , NEAT1 , PBXIP1 , PLCL1 , RAG2 , RCOR3 , RNF44 , RYR2 , SCN3A , SLC35D1 , SMPD3 , SPRY1 , ST8SIA4 , STMN3 , SYNE2 , TFPI , TPM2 , TPP1 , TRIOBP , XYLT1 , YPEL5 , ZNF124 , ZNF443 , ZNF544 , ZNF711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pkca Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADA , ADORA2B , BSN , CASP6 , CD36 , CREB3L2 , DBNDD1 , DDX60 , DHRS1 , FBLN1 , FBP1 , GNAO1 , GPR155 , GSTM4 , IL15 , IL33 , KIRREL1 , KLF15 , LPAR3 , NECAB2 , NMT2 , NOS1 , OAS3 , PASK , PSMC3IP , RETSAT , RTBDN , SEC14L2 , SECTM1 , SGK3 , SLC16A3 , SLC27A2 , SLC7A8 , SMPD3 , SPNS2 , SPTBN4 , TET1 , TPMT , TUB , TUBB2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sirna Eif4gi Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2B4 , ATP6V0E1 , C1QTNF1 , CCL2 , CDH11 , CYTL1 , DUSP4 , EIF5A2 , FAM111A , FSTL1 , LOXL2 , MFAP5 , NEDD4 , NEK7 , PAPSS2 , PMP22 , PSMC3IP , RIPK2 , SCML2 , SLC43A3 , SMURF2 , SP140L , SSR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.prostate Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATK , ACKR3 , AK5 , BEND5 , CA5B , CADM4 , CFI , CGREF1 , CNTFR , DNAJC12 , EDN1 , ENPP1 , EPHB6 , EPHX2 , GPNMB , GRM2 , IDUA , IGFBP3 , KCNQ2 , LUM , NOS1 , OPCML , POU3F2 , PTH1R , RASGRP1 , REEP1 , RRAD , SERPINB7 , SH2D3C , TAGLN , TFAP2B , TUBB4A , VGLL3 , YBX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclin D1 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ACVR1 , ANK3 , AP3B1 , CAPG , CAV1 , CBLN1 , CFB , CHRM1 , CXCR4 , DNAJB4 , ERG , EZH2 , GAL , GNAZ , GNS , GUCY1A2 , HRH1 , IL1A , IL7R , ILF3 , INHBA , ITGA3 , ITGB6 , KIF1A , MAPK8IP2 , MATK , MOK , MYL5 , MYO1C , NEDD4 , NELL1 , NOS1 , NR6A1 , PAFAH1B3 , PBXIP1 , PIK3R1 , RAB9A , RBMS2 , RGS16 , RNASE4 , S100A4 , SMPD1 , SYPL1 , TPD52 , TPM2 , VASP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dca Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM2 , ALK , ANKRD46 , ASIC4 , ASPM , ATP10D , CDK5R2 , CHEK2 , CHST2 , CPLANE2 , GMPR , GPR137B , GPR19 , IRAK4 , LAMA3 , LRP5L , MARCHF2 , MCTP1 , MFGE8 , MSH5 , NR4A1 , NUDT11 , PLA2G4C , PRRX2 , PTPRG , RALGDS , RASSF4 , RNPEPL1 , SETBP1 , SIRPB1 , SLC16A10 , SLC22A17 , SLC38A3 , SNCB , SNX24 , SP140L , SPC25 , STAG3 , STEAP1B , TDRD7 , TG , TNFSF18 , ZCCHC24 , ZNF286A , ZNF821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc2 Suz12 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP5 , ADCY2 , AGER , ALOXE3 , ANK1 , AP1M2 , ARRB2 , CACNA2D2 , CACNG2 , CFAP70 , CHEK1 , CIB1 , CORO1A , DCC , DCX , EPHX2 , EPPK1 , FRMD8 , HAUS5 , HOXD11 , KBTBD11 , KLF15 , KLHL23 , LDB2 , LMOD1 , LRP5L , LRRC61 , MAPT , NPY2R , ONECUT2 , OPCML , ORC1 , PGAP1 , PHOX2B , PNPLA3 , POLA2 , RAVER2 , RECQL4 , RPS6KA2 , RUNDC3A , SCHIP1 , SLC16A10 , SLC35D1 , ST3GAL1 , SYN3 , TNNT2 , ZNF695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rela Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRA1D , BMPR1B , C1orf21 , CALY , CUBN , DLK1 , DNMT3A , FMO5 , GCNT1 , HOXD3 , HSD17B1 , IDUA , IL17RB , IL7R , KCNK5 , KNL1 , L1CAM , MBNL2 , NECTIN1 , NEURL1 , NNAT , NRXN3 , PC , PSD , RAMP1 , RBP1 , SEZ6L , SRPX2 , STAG3 , TAF13 , TRAF1 , VEGFC , XPNPEP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tbk1.Df Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANGPTL4 , ATP6AP2 , BACH1 , BCL2L1 , BDH1 , CASP6 , CAVIN2 , CBX5 , CD2AP , CDK6 , CHMP2B , CLN5 , COL4A1 , COL5A2 , CXADR , DDX60 , DKK1 , DNAJB14 , DNAJC3 , DSN1 , ELL2 , ERAP1 , FOS , GALNT7 , GAS1 , GJA1 , GOLT1B , HIPK3 , HMBOX1 , HNRNPA0 , HOOK1 , IFIT1 , ITGA2 , ITGB6 , KIF14 , KLF5 , KLF7 , LIMS1 , LMNB1 , LMO4 , MAOA , MBP , MED13L , MIS18BP1 , MSH2 , NCOA3 , NEK7 , OSBPL3 , P3H2 , PAFAH1B3 , PCYOX1 , PDGFA , PLEKHA2 , PPCS , PSMB8 , PSMB9 , RAI14 , SEMA3C , SERPINE2 , SLC39A8 , SMURF2 , SNTB2 , SPDL1 , SRPRA , STOM , SUSD6 , TBK1 , THBS1 , TLN1 , TMOD3 , UFL1 , VRK1 , ZNF395 , ZWINT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclin D1 Ke .V1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACKR3 , ADARB1 , ALK , ALPL , ATP2B3 , CAPG , CAV1 , CFB , CHRNB2 , CNGB1 , CRMP1 , CXCL12 , DNAJB4 , DPF1 , ERBB2 , F3 , GJA1 , GNAZ , GRIA1 , IFIT3 , IL1R1 , IL7R , ILF3 , KCNJ8 , KIF1A , LIMS1 , MAPK4 , MATK , MX1 , MYL5 , NEDD4 , NELL1 , NOS1 , NPAS1 , NR6A1 , NTSR1 , PAFAH1B3 , PIK3R1 , PIP4K2A , PLCG2 , POU2F2 , PRKG2 , PTH1R , RIT2 , TMSB15A , VCAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2f3 Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM2 , ANKRD46 , ARHGAP18 , BDKRB2 , C16orf74 , DCC , GIPR , GPRC5A , GRID1 , HAPLN4 , IRAK2 , KCNQ1OT1 , KRT80 , LIF , LINC00173 , LINC00842 , LRRC8E , LYPD3 , MEGF6 , MMP1 , MMP3 , NACC2 , NR6A1 , NRL , OLFM1 , PC , PLAT , PODN , RAB43 , SLCO2B1 , SPTB , STK40 , STX1A , STXBP5L , TGM2 , TLR2 , ZNF135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sirna Eif4gi Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASAH1 , CEBPD , CORO1B , CTSC , CTSH , DAG1 , DTX4 , ESYT1 , HLA-B , HSPB1 , IGF2R , LRPAP1 , NQO1 , NSG1 , PERP , PSAP , PYGL , SUGCT , TNNT1 , ZFP36L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Src Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABTB1 , AMER1 , APC2 , ATOX1 , BCL2 , COL26A1 , CPLX2 , DLGAP1-AS2 , DLL3 , DNAJC22 , ETV7 , FBLN2 , FBXO44 , FOS , GINS2 , GVQW3 , HMX1 , LAMP3 , MAPK8IP2 , MATK , MTMR9LP , NAT8L , NEU1 , NUDT4B , PDZD7 , PLAAT4 , POU3F2 , PRR3 , RAB3A , SCARF2 , SOCS1 , SRC , SUGCT , SULT4A1 , SYN1 , TECTA , TFR2 , TMEM255B , TONSL , TOX3 , TTC21A , WTIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atm Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCD1 , CFH , CLCN4 , CYP2J2 , ENTPD7 , FMO5 , GDNF , GPR22 , GRIN2D , GRM8 , HS3ST3B1 , IL1RAPL1 , ITGB4 , KCNC4 , KCNG1 , KCNQ4 , LPAR3 , MDFI , NEUROD1 , NNAT , OPCML , PLCD1 , PMEL , RAPGEF4 , ST3GAL1 , STK17B , SULT1E1 , TAGLN , ZFP36L1 , ZNF208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brca1 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3GALT2 , CDH13 , CFAP69 , DDX25 , EXTL1 , HMGA2 , IQCA1 , KCNH7 , LDB2 , MAP2 , P3H3 , PHOX2B , RAG2 , RNF122 , RPP25 , SHANK1 , SIX1 , SLC16A4 , SP4 , STAR , TENT5C , THBS2 , TNC , TTLL7 , ZNF423 , ZNF780B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camp Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL4 , APOBEC3C , ATXN7L3B , CD74 , CHAF1A , CKMT1A , COL6A3 , CRABP1 , CXCL8 , CYBA , ECSIT , ELMO1 , FLOT1 , FOS , HMGB2 , HSPA5 , IFIT2 , LIMS1 , MAD2L1 , MT2A , MYC , NDEL1 , NLRP1 , NQO2 , NUAK2 , P4HB , PDIA3 , PPIB , PPP1R15A , PRIM1 , SEC61A1 , SESN2 , SIL1 , SLC22A17 , SSR3 , TFPI2 , TGFBI , TMED9 , TNIK , TRIM38 , UPP1 , WIPI1 , ZDHHC23 , ZNF367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eif4e Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BHLHE40 , BMP3 , CAMK2N2 , FBXL13 , GTF2H5 , MAP2K3 , MAPK8IP1 , MIRLET7BHG , MRPL17 , PPCS , SLC25A30 , SNTB1 , TAX1BP3 , TST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak2 Dn.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTSL4 , ATP8B1 , CEP152 , COL26A1 , DBF4B , DBH , DLL3 , DOCK5 , DPY19L2P2 , DSCAM , ECM2 , FLCN , HIBADH , IKZF2 , ITGBL1 , KIF13A , KIRREL1 , MBTD1 , MTMR11 , NEAT1 , NOL12 , PEX3 , PGAP1 , RFX3 , SGCE , SIGLEC15 , SOCS7 , SUZ12P1 , TRIM36 , ZNF221 , ZNF551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak2 Dn.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTA2 , ADCYAP1R1 , ADGRB1 , ALPL , CDH11 , CNKSR2 , COL6A3 , CPED1 , CSPG4 , DOT1L , DUOX1 , EPPK1 , ESRRG , FLT3LG , FOXD1 , FRMPD1 , HOXD1 , HRH3 , HSPA12A , INA , KCNIP4 , KITLG , LRIG1 , METRN , NEK11 , NELL2 , PCDHB12 , PHF14 , PSG2 , PXDC1 , RBP4 , SEMA5A , SLC22A17 , SNCB , SUV39H2 , ZFHX4 , ZNF821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.amp.lung Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMPER , C3AR1 , DLX5 , DOCK3 , DUSP9 , DYNC1I1 , EFCAB6 , EFNA2 , FGF7 , KCNC1 , LRRC37A4P , MAGEA12 , NELL2 , NGF , NOVA1 , NPAS3 , NPHP1 , PNMA3 , PRKG2 , REST , SEMA3E , SLC2A4 , SPP1 , ST3GAL6 , ST8SIA2 , TNNT2 , VTN , XPNPEP2 , ZNF257 , ZNF835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kras.lung Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADD2 , CD248 , CDKN1C , CRABP2 , CRYAB , EPHB3 , ERG , GAS1 , GDNF , GPNMB , HTR1B , HTR1D , IVL , KRT15 , LMO1 , LYPD3 , MAP2K6 , MAP3K1 , OLFML2A , PLCH2 , POSTN , PRODH , PSG7 , PSORS1C1 , SCRG1 , SGCD , SH3GL3 , SLC6A9 , SPTBN2 , THAP9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myc Up.v1 Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5orf46 , CALML4 , CDCA7L , CFAP70 , CGREF1 , COQ8A , DENND2D , DGAT2 , DLL3 , DPYSL5 , ECE2 , EXOSC5 , FOS , HLF , HS3ST3A1 , HS6ST2 , ITPR1 , JPH1 , KLRG2 , LRRC61 , LYPD6 , MTFP1 , NEFH , OAF , P2RX5 , PCOLCE2 , PLD6 , PRR3 , RPP40 , S100A10 , SIX3 , SLC25A25-AS1 , SLC27A2 , SLC29A4 , SLC6A15 , TAF4B , TAF5 , TMEM132B , TMEM97 , VPS9D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prc1 Bmi Up.v1 Dn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKS1B , CACNA2D2 , CHRNA3 , CLIC3 , CLSPN , CORO1A , DCC , DDX25 , EPHX2 , FGFR3 , FKBP5 , GAS1 , HLA-DPB1 , HOXD11 , IFIT1 , KBTBD11 , KCNC1 , LINC02249 , LMOD1 , LRRC37A4P , ONECUT2 , OPCML , P2RX3 , PADI1 , PDGFB , PEAK1 , PNPLA3 , SDK2 , SHANK1 , SLC16A10 , SLC66A3 , SPTBN2 , STMN3 , SYN1 , SYN3 , TNNT2 , TRPM4</t>
+    <t xml:space="preserve">ABCA3 , ACE , ADAMTSL2 , B3GALT5 , CHRM2 , CNN1 , FCHO1 , GATA4 , GRM2 , GRM8 , IFI44L , KCNN1 , MSC , MX1 , NGF , PHLDA3 , PTGER2 , RYR2 , SEMA5A , STX11</t>
   </si>
   <si>
     <t xml:space="preserve">hypeR</t>
@@ -1182,13 +1182,13 @@
     <t xml:space="preserve">Signature Head</t>
   </si>
   <si>
-    <t xml:space="preserve">ICA1,GLCCI1,UNC79,GABRB3,ADAM9,ASPH</t>
+    <t xml:space="preserve">RIMS4,UNC79,EML5,BRSK2,MANEAL,ICA1</t>
   </si>
   <si>
     <t xml:space="preserve">Signature Size</t>
   </si>
   <si>
-    <t xml:space="preserve">5078</t>
+    <t xml:space="preserve">4400</t>
   </si>
   <si>
     <t xml:space="preserve">Signature Type</t>
@@ -1206,7 +1206,7 @@
     <t xml:space="preserve">Background</t>
   </si>
   <si>
-    <t xml:space="preserve">16335</t>
+    <t xml:space="preserve">17895</t>
   </si>
   <si>
     <t xml:space="preserve">P-Value</t>
@@ -1590,22 +1590,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00000000000000039</v>
+        <v>0.000000000003</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000000000000074</v>
+        <v>0.00000000057</v>
       </c>
       <c r="D2" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E2" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1616,22 +1616,22 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000000000000038</v>
+        <v>0.000000000017</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000000000025</v>
+        <v>0.0000000016</v>
       </c>
       <c r="D3" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E3" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1642,22 +1642,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>0.000000000000043</v>
+        <v>0.000000000037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0000000000025</v>
+        <v>0.0000000019</v>
       </c>
       <c r="D4" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="F4" t="n">
         <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
@@ -1668,22 +1668,22 @@
         <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>0.000000000000053</v>
+        <v>0.00000000004</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0000000000025</v>
+        <v>0.0000000019</v>
       </c>
       <c r="D5" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E5" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -1694,22 +1694,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0000000092</v>
+        <v>0.0000000017</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00000035</v>
+        <v>0.000000066</v>
       </c>
       <c r="D6" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G6" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -1720,22 +1720,22 @@
         <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>0.000000016</v>
+        <v>0.00000015</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00000046</v>
+        <v>0.0000046</v>
       </c>
       <c r="D7" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E7" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F7" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1746,22 +1746,22 @@
         <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000000017</v>
+        <v>0.00000034</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00000046</v>
+        <v>0.0000091</v>
       </c>
       <c r="D8" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E8" t="n">
-        <v>287</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H8" t="s">
         <v>21</v>
@@ -1772,22 +1772,22 @@
         <v>22</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00000002</v>
+        <v>0.00000038</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00000047</v>
+        <v>0.0000091</v>
       </c>
       <c r="D9" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G9" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H9" t="s">
         <v>23</v>
@@ -1798,22 +1798,22 @@
         <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00000015</v>
+        <v>0.00000081</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0000029</v>
+        <v>0.000017</v>
       </c>
       <c r="D10" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
@@ -1824,22 +1824,22 @@
         <v>26</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00000015</v>
+        <v>0.00000094</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0000029</v>
+        <v>0.000017</v>
       </c>
       <c r="D11" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>290</v>
       </c>
       <c r="F11" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G11" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H11" t="s">
         <v>27</v>
@@ -1850,22 +1850,22 @@
         <v>28</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0000002</v>
+        <v>0.00000099</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0000035</v>
+        <v>0.000017</v>
       </c>
       <c r="D12" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E12" t="n">
-        <v>193</v>
+        <v>287</v>
       </c>
       <c r="F12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G12" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
@@ -1876,22 +1876,22 @@
         <v>30</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00000078</v>
+        <v>0.0000036</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000011</v>
+        <v>0.000056</v>
       </c>
       <c r="D13" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E13" t="n">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H13" t="s">
         <v>31</v>
@@ -1902,22 +1902,22 @@
         <v>32</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00000081</v>
+        <v>0.0000039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000011</v>
+        <v>0.000056</v>
       </c>
       <c r="D14" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E14" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -1928,22 +1928,22 @@
         <v>34</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00000081</v>
+        <v>0.0000046</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000011</v>
+        <v>0.000063</v>
       </c>
       <c r="D15" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E15" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H15" t="s">
         <v>35</v>
@@ -1954,22 +1954,22 @@
         <v>36</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0000025</v>
+        <v>0.0000065</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000031</v>
+        <v>0.000082</v>
       </c>
       <c r="D16" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E16" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H16" t="s">
         <v>37</v>
@@ -1980,22 +1980,22 @@
         <v>38</v>
       </c>
       <c r="B17" t="n">
-        <v>0.000025</v>
+        <v>0.000011</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00029</v>
+        <v>0.00013</v>
       </c>
       <c r="D17" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -2006,22 +2006,22 @@
         <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00006</v>
+        <v>0.000049</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00067</v>
+        <v>0.00054</v>
       </c>
       <c r="D18" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E18" t="n">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H18" t="s">
         <v>41</v>
@@ -2032,22 +2032,22 @@
         <v>42</v>
       </c>
       <c r="B19" t="n">
-        <v>0.000065</v>
+        <v>0.000093</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00068</v>
+        <v>0.00097</v>
       </c>
       <c r="D19" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E19" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F19" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H19" t="s">
         <v>43</v>
@@ -2058,22 +2058,22 @@
         <v>44</v>
       </c>
       <c r="B20" t="n">
-        <v>0.000072</v>
+        <v>0.00012</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00072</v>
+        <v>0.0012</v>
       </c>
       <c r="D20" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E20" t="n">
-        <v>290</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2084,22 +2084,22 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>0.000081</v>
+        <v>0.00012</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00075</v>
+        <v>0.0012</v>
       </c>
       <c r="D21" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E21" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F21" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H21" t="s">
         <v>47</v>
@@ -2110,22 +2110,22 @@
         <v>48</v>
       </c>
       <c r="B22" t="n">
-        <v>0.000084</v>
+        <v>0.00022</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00075</v>
+        <v>0.0019</v>
       </c>
       <c r="D22" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="G22" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H22" t="s">
         <v>49</v>
@@ -2136,22 +2136,22 @@
         <v>50</v>
       </c>
       <c r="B23" t="n">
-        <v>0.00019</v>
+        <v>0.00022</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0017</v>
+        <v>0.0019</v>
       </c>
       <c r="D23" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E23" t="n">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="F23" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="G23" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H23" t="s">
         <v>51</v>
@@ -2162,22 +2162,22 @@
         <v>52</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00024</v>
+        <v>0.00023</v>
       </c>
       <c r="C24" t="n">
         <v>0.0019</v>
       </c>
       <c r="D24" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E24" t="n">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H24" t="s">
         <v>53</v>
@@ -2188,22 +2188,22 @@
         <v>54</v>
       </c>
       <c r="B25" t="n">
-        <v>0.00025</v>
+        <v>0.0003</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0019</v>
+        <v>0.0024</v>
       </c>
       <c r="D25" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E25" t="n">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="F25" t="n">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H25" t="s">
         <v>55</v>
@@ -2214,22 +2214,22 @@
         <v>56</v>
       </c>
       <c r="B26" t="n">
-        <v>0.00036</v>
+        <v>0.00035</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="D26" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E26" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H26" t="s">
         <v>57</v>
@@ -2240,22 +2240,22 @@
         <v>58</v>
       </c>
       <c r="B27" t="n">
-        <v>0.00058</v>
+        <v>0.00039</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0042</v>
+        <v>0.0028</v>
       </c>
       <c r="D27" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E27" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G27" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H27" t="s">
         <v>59</v>
@@ -2266,22 +2266,22 @@
         <v>60</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00089</v>
+        <v>0.00058</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0062</v>
+        <v>0.0041</v>
       </c>
       <c r="D28" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H28" t="s">
         <v>61</v>
@@ -2292,22 +2292,22 @@
         <v>62</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00097</v>
+        <v>0.0009</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0066</v>
+        <v>0.006</v>
       </c>
       <c r="D29" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E29" t="n">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="F29" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G29" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H29" t="s">
         <v>63</v>
@@ -2318,22 +2318,22 @@
         <v>64</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0073</v>
+        <v>0.008</v>
       </c>
       <c r="D30" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E30" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F30" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G30" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H30" t="s">
         <v>65</v>
@@ -2344,22 +2344,22 @@
         <v>66</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0013</v>
+        <v>0.0015</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0079</v>
+        <v>0.0093</v>
       </c>
       <c r="D31" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E31" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G31" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H31" t="s">
         <v>67</v>
@@ -2370,22 +2370,22 @@
         <v>68</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0014</v>
+        <v>0.002</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0083</v>
+        <v>0.012</v>
       </c>
       <c r="D32" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E32" t="n">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="F32" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G32" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H32" t="s">
         <v>69</v>
@@ -2396,22 +2396,22 @@
         <v>70</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0029</v>
+        <v>0.0021</v>
       </c>
       <c r="C33" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="D33" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E33" t="n">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="F33" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H33" t="s">
         <v>71</v>
@@ -2422,22 +2422,22 @@
         <v>72</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0034</v>
+        <v>0.0024</v>
       </c>
       <c r="C34" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="D34" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="F34" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G34" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H34" t="s">
         <v>73</v>
@@ -2448,22 +2448,22 @@
         <v>74</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0045</v>
+        <v>0.0028</v>
       </c>
       <c r="C35" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="D35" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E35" t="n">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="F35" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="G35" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H35" t="s">
         <v>75</v>
@@ -2474,22 +2474,22 @@
         <v>76</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0048</v>
+        <v>0.0029</v>
       </c>
       <c r="C36" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="D36" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E36" t="n">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G36" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H36" t="s">
         <v>77</v>
@@ -2500,22 +2500,22 @@
         <v>78</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0053</v>
+        <v>0.0031</v>
       </c>
       <c r="C37" t="n">
-        <v>0.028</v>
+        <v>0.016</v>
       </c>
       <c r="D37" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E37" t="n">
         <v>187</v>
       </c>
       <c r="F37" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G37" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H37" t="s">
         <v>79</v>
@@ -2526,22 +2526,22 @@
         <v>80</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0061</v>
+        <v>0.0036</v>
       </c>
       <c r="C38" t="n">
-        <v>0.031</v>
+        <v>0.018</v>
       </c>
       <c r="D38" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E38" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="F38" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="G38" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H38" t="s">
         <v>81</v>
@@ -2552,22 +2552,22 @@
         <v>82</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0073</v>
+        <v>0.0038</v>
       </c>
       <c r="C39" t="n">
-        <v>0.036</v>
+        <v>0.019</v>
       </c>
       <c r="D39" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E39" t="n">
         <v>192</v>
       </c>
       <c r="F39" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G39" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H39" t="s">
         <v>83</v>
@@ -2578,22 +2578,22 @@
         <v>84</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0098</v>
+        <v>0.0089</v>
       </c>
       <c r="C40" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="D40" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E40" t="n">
-        <v>278</v>
+        <v>188</v>
       </c>
       <c r="F40" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="G40" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H40" t="s">
         <v>85</v>
@@ -2604,22 +2604,22 @@
         <v>86</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="C41" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="D41" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E41" t="n">
-        <v>132</v>
+        <v>282</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G41" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H41" t="s">
         <v>87</v>
@@ -2630,22 +2630,22 @@
         <v>88</v>
       </c>
       <c r="B42" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="C42" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="D42" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E42" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F42" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H42" t="s">
         <v>89</v>
@@ -2656,22 +2656,22 @@
         <v>90</v>
       </c>
       <c r="B43" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="C43" t="n">
-        <v>0.064</v>
+        <v>0.052</v>
       </c>
       <c r="D43" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E43" t="n">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="F43" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G43" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H43" t="s">
         <v>91</v>
@@ -2682,22 +2682,22 @@
         <v>92</v>
       </c>
       <c r="B44" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="C44" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
       <c r="D44" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E44" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="F44" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H44" t="s">
         <v>93</v>
@@ -2708,22 +2708,22 @@
         <v>94</v>
       </c>
       <c r="B45" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="C45" t="n">
-        <v>0.096</v>
+        <v>0.081</v>
       </c>
       <c r="D45" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E45" t="n">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H45" t="s">
         <v>95</v>
@@ -2734,22 +2734,22 @@
         <v>96</v>
       </c>
       <c r="B46" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="C46" t="n">
-        <v>0.098</v>
+        <v>0.087</v>
       </c>
       <c r="D46" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E46" t="n">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="F46" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G46" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H46" t="s">
         <v>97</v>
@@ -2760,22 +2760,22 @@
         <v>98</v>
       </c>
       <c r="B47" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="C47" t="n">
-        <v>0.11</v>
+        <v>0.089</v>
       </c>
       <c r="D47" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E47" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F47" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G47" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H47" t="s">
         <v>99</v>
@@ -2786,22 +2786,22 @@
         <v>100</v>
       </c>
       <c r="B48" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="C48" t="n">
         <v>0.11</v>
       </c>
       <c r="D48" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E48" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F48" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G48" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H48" t="s">
         <v>101</v>
@@ -2812,22 +2812,22 @@
         <v>102</v>
       </c>
       <c r="B49" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="C49" t="n">
         <v>0.11</v>
       </c>
       <c r="D49" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E49" t="n">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="F49" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G49" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H49" t="s">
         <v>103</v>
@@ -2838,22 +2838,22 @@
         <v>104</v>
       </c>
       <c r="B50" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
       <c r="C50" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="D50" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E50" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="F50" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G50" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H50" t="s">
         <v>105</v>
@@ -2864,22 +2864,22 @@
         <v>106</v>
       </c>
       <c r="B51" t="n">
-        <v>0.028</v>
+        <v>0.036</v>
       </c>
       <c r="C51" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="D51" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E51" t="n">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="F51" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G51" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H51" t="s">
         <v>107</v>
@@ -2890,22 +2890,22 @@
         <v>108</v>
       </c>
       <c r="B52" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="C52" t="n">
         <v>0.14</v>
       </c>
       <c r="D52" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E52" t="n">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H52" t="s">
         <v>109</v>
@@ -2916,22 +2916,22 @@
         <v>110</v>
       </c>
       <c r="B53" t="n">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
       <c r="C53" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D53" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E53" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F53" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="G53" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H53" t="s">
         <v>111</v>
@@ -2942,22 +2942,22 @@
         <v>112</v>
       </c>
       <c r="B54" t="n">
-        <v>0.051</v>
+        <v>0.042</v>
       </c>
       <c r="C54" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D54" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E54" t="n">
         <v>46</v>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G54" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H54" t="s">
         <v>113</v>
@@ -2968,22 +2968,22 @@
         <v>114</v>
       </c>
       <c r="B55" t="n">
-        <v>0.051</v>
+        <v>0.044</v>
       </c>
       <c r="C55" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D55" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E55" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F55" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G55" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H55" t="s">
         <v>115</v>
@@ -2994,22 +2994,22 @@
         <v>116</v>
       </c>
       <c r="B56" t="n">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="C56" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D56" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E56" t="n">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F56" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G56" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H56" t="s">
         <v>117</v>
@@ -3020,22 +3020,22 @@
         <v>118</v>
       </c>
       <c r="B57" t="n">
-        <v>0.054</v>
+        <v>0.048</v>
       </c>
       <c r="C57" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D57" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E57" t="n">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="F57" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G57" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H57" t="s">
         <v>119</v>
@@ -3046,22 +3046,22 @@
         <v>120</v>
       </c>
       <c r="B58" t="n">
-        <v>0.055</v>
+        <v>0.048</v>
       </c>
       <c r="C58" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D58" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E58" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F58" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G58" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H58" t="s">
         <v>121</v>
@@ -3072,22 +3072,22 @@
         <v>122</v>
       </c>
       <c r="B59" t="n">
-        <v>0.076</v>
+        <v>0.058</v>
       </c>
       <c r="C59" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="D59" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E59" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="F59" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="G59" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H59" t="s">
         <v>123</v>
@@ -3098,22 +3098,22 @@
         <v>124</v>
       </c>
       <c r="B60" t="n">
-        <v>0.079</v>
+        <v>0.062</v>
       </c>
       <c r="C60" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D60" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E60" t="n">
         <v>126</v>
       </c>
       <c r="F60" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G60" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H60" t="s">
         <v>125</v>
@@ -3124,22 +3124,22 @@
         <v>126</v>
       </c>
       <c r="B61" t="n">
-        <v>0.084</v>
+        <v>0.067</v>
       </c>
       <c r="C61" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="D61" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="F61" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G61" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H61" t="s">
         <v>127</v>
@@ -3150,22 +3150,22 @@
         <v>128</v>
       </c>
       <c r="B62" t="n">
-        <v>0.091</v>
+        <v>0.079</v>
       </c>
       <c r="C62" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="D62" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H62" t="s">
         <v>129</v>
@@ -3176,22 +3176,22 @@
         <v>130</v>
       </c>
       <c r="B63" t="n">
-        <v>0.092</v>
+        <v>0.081</v>
       </c>
       <c r="C63" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="D63" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E63" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="F63" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G63" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H63" t="s">
         <v>131</v>
@@ -3202,22 +3202,22 @@
         <v>132</v>
       </c>
       <c r="B64" t="n">
-        <v>0.092</v>
+        <v>0.086</v>
       </c>
       <c r="C64" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="D64" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E64" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H64" t="s">
         <v>133</v>
@@ -3228,22 +3228,22 @@
         <v>134</v>
       </c>
       <c r="B65" t="n">
-        <v>0.092</v>
+        <v>0.087</v>
       </c>
       <c r="C65" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="D65" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E65" t="n">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G65" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H65" t="s">
         <v>135</v>
@@ -3254,22 +3254,22 @@
         <v>136</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1</v>
+        <v>0.088</v>
       </c>
       <c r="C66" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="D66" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E66" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="F66" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G66" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H66" t="s">
         <v>137</v>
@@ -3280,22 +3280,22 @@
         <v>138</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1</v>
+        <v>0.089</v>
       </c>
       <c r="C67" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="D67" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E67" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="F67" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G67" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H67" t="s">
         <v>139</v>
@@ -3306,22 +3306,22 @@
         <v>140</v>
       </c>
       <c r="B68" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="C68" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="D68" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E68" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="F68" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G68" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H68" t="s">
         <v>141</v>
@@ -3332,22 +3332,22 @@
         <v>142</v>
       </c>
       <c r="B69" t="n">
-        <v>0.12</v>
+        <v>0.099</v>
       </c>
       <c r="C69" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="D69" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E69" t="n">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F69" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H69" t="s">
         <v>143</v>
@@ -3358,22 +3358,22 @@
         <v>144</v>
       </c>
       <c r="B70" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="D70" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E70" t="n">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="F70" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H70" t="s">
         <v>145</v>
@@ -3384,22 +3384,22 @@
         <v>146</v>
       </c>
       <c r="B71" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="D71" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E71" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="F71" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G71" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H71" t="s">
         <v>147</v>
@@ -3410,22 +3410,22 @@
         <v>148</v>
       </c>
       <c r="B72" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="C72" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="D72" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E72" t="n">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="F72" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G72" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H72" t="s">
         <v>149</v>
@@ -3436,22 +3436,22 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C73" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="D73" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E73" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F73" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G73" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H73" t="s">
         <v>151</v>
@@ -3462,22 +3462,22 @@
         <v>152</v>
       </c>
       <c r="B74" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="C74" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="D74" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E74" t="n">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="F74" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G74" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H74" t="s">
         <v>153</v>
@@ -3488,22 +3488,22 @@
         <v>154</v>
       </c>
       <c r="B75" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="C75" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="D75" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E75" t="n">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="F75" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G75" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H75" t="s">
         <v>155</v>
@@ -3514,22 +3514,22 @@
         <v>156</v>
       </c>
       <c r="B76" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="C76" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="D76" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E76" t="n">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="F76" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G76" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H76" t="s">
         <v>157</v>
@@ -3540,22 +3540,22 @@
         <v>158</v>
       </c>
       <c r="B77" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="C77" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="D77" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E77" t="n">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G77" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H77" t="s">
         <v>159</v>
@@ -3566,22 +3566,22 @@
         <v>160</v>
       </c>
       <c r="B78" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="D78" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E78" t="n">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="F78" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G78" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H78" t="s">
         <v>161</v>
@@ -3592,22 +3592,22 @@
         <v>162</v>
       </c>
       <c r="B79" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="D79" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E79" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G79" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H79" t="s">
         <v>163</v>
@@ -3618,22 +3618,22 @@
         <v>164</v>
       </c>
       <c r="B80" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="C80" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="D80" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E80" t="n">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="F80" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G80" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H80" t="s">
         <v>165</v>
@@ -3644,22 +3644,22 @@
         <v>166</v>
       </c>
       <c r="B81" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="C81" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="D81" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E81" t="n">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="F81" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G81" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H81" t="s">
         <v>167</v>
@@ -3670,22 +3670,22 @@
         <v>168</v>
       </c>
       <c r="B82" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="C82" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="D82" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E82" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="F82" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G82" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H82" t="s">
         <v>169</v>
@@ -3696,22 +3696,22 @@
         <v>170</v>
       </c>
       <c r="B83" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D83" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E83" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F83" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G83" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H83" t="s">
         <v>171</v>
@@ -3722,22 +3722,22 @@
         <v>172</v>
       </c>
       <c r="B84" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="D84" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="F84" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="G84" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H84" t="s">
         <v>173</v>
@@ -3751,19 +3751,19 @@
         <v>0.27</v>
       </c>
       <c r="C85" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="D85" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E85" t="n">
+        <v>187</v>
+      </c>
+      <c r="F85" t="n">
         <v>50</v>
       </c>
-      <c r="F85" t="n">
-        <v>18</v>
-      </c>
       <c r="G85" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H85" t="s">
         <v>175</v>
@@ -3774,22 +3774,22 @@
         <v>176</v>
       </c>
       <c r="B86" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="C86" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="D86" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E86" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="F86" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="G86" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H86" t="s">
         <v>177</v>
@@ -3803,19 +3803,19 @@
         <v>0.29</v>
       </c>
       <c r="C87" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D87" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E87" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F87" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G87" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H87" t="s">
         <v>179</v>
@@ -3829,19 +3829,19 @@
         <v>0.29</v>
       </c>
       <c r="C88" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D88" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E88" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F88" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G88" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H88" t="s">
         <v>181</v>
@@ -3852,22 +3852,22 @@
         <v>182</v>
       </c>
       <c r="B89" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="C89" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="D89" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E89" t="n">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G89" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H89" t="s">
         <v>183</v>
@@ -3878,22 +3878,22 @@
         <v>184</v>
       </c>
       <c r="B90" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="C90" t="n">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="D90" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E90" t="n">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="F90" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="G90" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H90" t="s">
         <v>185</v>
@@ -3904,22 +3904,22 @@
         <v>186</v>
       </c>
       <c r="B91" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="C91" t="n">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="D91" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E91" t="n">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="F91" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G91" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H91" t="s">
         <v>187</v>
@@ -3930,22 +3930,22 @@
         <v>188</v>
       </c>
       <c r="B92" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="C92" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="D92" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E92" t="n">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H92" t="s">
         <v>189</v>
@@ -3956,22 +3956,22 @@
         <v>190</v>
       </c>
       <c r="B93" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="C93" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="D93" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E93" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F93" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G93" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H93" t="s">
         <v>191</v>
@@ -3982,22 +3982,22 @@
         <v>192</v>
       </c>
       <c r="B94" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="C94" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="D94" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E94" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="F94" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G94" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H94" t="s">
         <v>193</v>
@@ -4008,22 +4008,22 @@
         <v>194</v>
       </c>
       <c r="B95" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="C95" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="D95" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E95" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F95" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G95" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H95" t="s">
         <v>195</v>
@@ -4034,22 +4034,22 @@
         <v>196</v>
       </c>
       <c r="B96" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="C96" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="D96" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E96" t="n">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="F96" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G96" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H96" t="s">
         <v>197</v>
@@ -4060,22 +4060,22 @@
         <v>198</v>
       </c>
       <c r="B97" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="C97" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="D97" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E97" t="n">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="F97" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G97" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H97" t="s">
         <v>199</v>
@@ -4086,22 +4086,22 @@
         <v>200</v>
       </c>
       <c r="B98" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="C98" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="D98" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E98" t="n">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="F98" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G98" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H98" t="s">
         <v>201</v>
@@ -4112,22 +4112,22 @@
         <v>202</v>
       </c>
       <c r="B99" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="C99" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="D99" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E99" t="n">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="F99" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G99" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H99" t="s">
         <v>203</v>
@@ -4138,22 +4138,22 @@
         <v>204</v>
       </c>
       <c r="B100" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="C100" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="D100" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E100" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F100" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G100" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H100" t="s">
         <v>205</v>
@@ -4164,22 +4164,22 @@
         <v>206</v>
       </c>
       <c r="B101" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="C101" t="n">
-        <v>0.81</v>
+        <v>0.68</v>
       </c>
       <c r="D101" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E101" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="F101" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G101" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H101" t="s">
         <v>207</v>
@@ -4190,22 +4190,22 @@
         <v>208</v>
       </c>
       <c r="B102" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="C102" t="n">
-        <v>0.81</v>
+        <v>0.7</v>
       </c>
       <c r="D102" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E102" t="n">
         <v>166</v>
       </c>
       <c r="F102" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G102" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H102" t="s">
         <v>209</v>
@@ -4216,22 +4216,22 @@
         <v>210</v>
       </c>
       <c r="B103" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="C103" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="D103" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E103" t="n">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="F103" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="G103" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H103" t="s">
         <v>211</v>
@@ -4242,22 +4242,22 @@
         <v>212</v>
       </c>
       <c r="B104" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C104" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="D104" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="F104" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G104" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H104" t="s">
         <v>213</v>
@@ -4268,22 +4268,22 @@
         <v>214</v>
       </c>
       <c r="B105" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C105" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="D105" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E105" t="n">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="F105" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G105" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H105" t="s">
         <v>215</v>
@@ -4294,22 +4294,22 @@
         <v>216</v>
       </c>
       <c r="B106" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="C106" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="D106" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E106" t="n">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="F106" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G106" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H106" t="s">
         <v>217</v>
@@ -4320,22 +4320,22 @@
         <v>218</v>
       </c>
       <c r="B107" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="C107" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="D107" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E107" t="n">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="F107" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H107" t="s">
         <v>219</v>
@@ -4346,22 +4346,22 @@
         <v>220</v>
       </c>
       <c r="B108" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="C108" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="D108" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E108" t="n">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F108" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G108" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H108" t="s">
         <v>221</v>
@@ -4372,22 +4372,22 @@
         <v>222</v>
       </c>
       <c r="B109" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="C109" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="D109" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E109" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="F109" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G109" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H109" t="s">
         <v>223</v>
@@ -4398,22 +4398,22 @@
         <v>224</v>
       </c>
       <c r="B110" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="C110" t="n">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="D110" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E110" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="F110" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G110" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H110" t="s">
         <v>225</v>
@@ -4424,22 +4424,22 @@
         <v>226</v>
       </c>
       <c r="B111" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="C111" t="n">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="D111" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E111" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F111" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G111" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H111" t="s">
         <v>227</v>
@@ -4450,22 +4450,22 @@
         <v>228</v>
       </c>
       <c r="B112" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="C112" t="n">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="D112" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E112" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F112" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G112" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H112" t="s">
         <v>229</v>
@@ -4476,22 +4476,22 @@
         <v>230</v>
       </c>
       <c r="B113" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="C113" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="D113" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E113" t="n">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="F113" t="n">
         <v>47</v>
       </c>
       <c r="G113" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H113" t="s">
         <v>231</v>
@@ -4502,22 +4502,22 @@
         <v>232</v>
       </c>
       <c r="B114" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="C114" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="D114" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E114" t="n">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="F114" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G114" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H114" t="s">
         <v>233</v>
@@ -4528,22 +4528,22 @@
         <v>234</v>
       </c>
       <c r="B115" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="C115" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="D115" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E115" t="n">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="F115" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="G115" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H115" t="s">
         <v>235</v>
@@ -4554,22 +4554,22 @@
         <v>236</v>
       </c>
       <c r="B116" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="C116" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="D116" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E116" t="n">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G116" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H116" t="s">
         <v>237</v>
@@ -4580,22 +4580,22 @@
         <v>238</v>
       </c>
       <c r="B117" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="C117" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="D117" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E117" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F117" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G117" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H117" t="s">
         <v>239</v>
@@ -4606,22 +4606,22 @@
         <v>240</v>
       </c>
       <c r="B118" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="C118" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="D118" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E118" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="F118" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G118" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H118" t="s">
         <v>241</v>
@@ -4632,22 +4632,22 @@
         <v>242</v>
       </c>
       <c r="B119" t="n">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="C119" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D119" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E119" t="n">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="F119" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H119" t="s">
         <v>243</v>
@@ -4658,22 +4658,22 @@
         <v>244</v>
       </c>
       <c r="B120" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="C120" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="D120" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="F120" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G120" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H120" t="s">
         <v>245</v>
@@ -4684,22 +4684,22 @@
         <v>246</v>
       </c>
       <c r="B121" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="C121" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="D121" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E121" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="F121" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G121" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H121" t="s">
         <v>247</v>
@@ -4710,22 +4710,22 @@
         <v>248</v>
       </c>
       <c r="B122" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D122" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E122" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F122" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G122" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H122" t="s">
         <v>249</v>
@@ -4736,22 +4736,22 @@
         <v>250</v>
       </c>
       <c r="B123" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="D123" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E123" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G123" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H123" t="s">
         <v>251</v>
@@ -4762,22 +4762,22 @@
         <v>252</v>
       </c>
       <c r="B124" t="n">
-        <v>0.69</v>
+        <v>0.6</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D124" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E124" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="F124" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G124" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H124" t="s">
         <v>253</v>
@@ -4788,22 +4788,22 @@
         <v>254</v>
       </c>
       <c r="B125" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D125" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E125" t="n">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="F125" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="G125" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H125" t="s">
         <v>255</v>
@@ -4814,22 +4814,22 @@
         <v>256</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D126" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E126" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="F126" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G126" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H126" t="s">
         <v>257</v>
@@ -4840,22 +4840,22 @@
         <v>258</v>
       </c>
       <c r="B127" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D127" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E127" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F127" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G127" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H127" t="s">
         <v>259</v>
@@ -4866,22 +4866,22 @@
         <v>260</v>
       </c>
       <c r="B128" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D128" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E128" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="F128" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G128" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H128" t="s">
         <v>261</v>
@@ -4892,22 +4892,22 @@
         <v>262</v>
       </c>
       <c r="B129" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D129" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E129" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F129" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G129" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H129" t="s">
         <v>263</v>
@@ -4918,22 +4918,22 @@
         <v>264</v>
       </c>
       <c r="B130" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D130" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E130" t="n">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="F130" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="G130" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H130" t="s">
         <v>265</v>
@@ -4944,22 +4944,22 @@
         <v>266</v>
       </c>
       <c r="B131" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D131" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E131" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="F131" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G131" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H131" t="s">
         <v>267</v>
@@ -4970,22 +4970,22 @@
         <v>268</v>
       </c>
       <c r="B132" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D132" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E132" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="F132" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G132" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H132" t="s">
         <v>269</v>
@@ -4996,22 +4996,22 @@
         <v>270</v>
       </c>
       <c r="B133" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="D133" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E133" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F133" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G133" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H133" t="s">
         <v>271</v>
@@ -5022,22 +5022,22 @@
         <v>272</v>
       </c>
       <c r="B134" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D134" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E134" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="F134" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G134" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H134" t="s">
         <v>273</v>
@@ -5048,22 +5048,22 @@
         <v>274</v>
       </c>
       <c r="B135" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="D135" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E135" t="n">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="F135" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G135" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H135" t="s">
         <v>275</v>
@@ -5074,22 +5074,22 @@
         <v>276</v>
       </c>
       <c r="B136" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E136" t="n">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="F136" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G136" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H136" t="s">
         <v>277</v>
@@ -5100,22 +5100,22 @@
         <v>278</v>
       </c>
       <c r="B137" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E137" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="F137" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="G137" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H137" t="s">
         <v>279</v>
@@ -5126,22 +5126,22 @@
         <v>280</v>
       </c>
       <c r="B138" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E138" t="n">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G138" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H138" t="s">
         <v>281</v>
@@ -5152,22 +5152,22 @@
         <v>282</v>
       </c>
       <c r="B139" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E139" t="n">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G139" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H139" t="s">
         <v>283</v>
@@ -5178,22 +5178,22 @@
         <v>284</v>
       </c>
       <c r="B140" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E140" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F140" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G140" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H140" t="s">
         <v>285</v>
@@ -5204,22 +5204,22 @@
         <v>286</v>
       </c>
       <c r="B141" t="n">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E141" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F141" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G141" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H141" t="s">
         <v>287</v>
@@ -5230,22 +5230,22 @@
         <v>288</v>
       </c>
       <c r="B142" t="n">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E142" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="F142" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G142" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H142" t="s">
         <v>289</v>
@@ -5256,22 +5256,22 @@
         <v>290</v>
       </c>
       <c r="B143" t="n">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E143" t="n">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="F143" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G143" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H143" t="s">
         <v>291</v>
@@ -5282,22 +5282,22 @@
         <v>292</v>
       </c>
       <c r="B144" t="n">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E144" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="F144" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G144" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H144" t="s">
         <v>293</v>
@@ -5308,22 +5308,22 @@
         <v>294</v>
       </c>
       <c r="B145" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E145" t="n">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G145" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H145" t="s">
         <v>295</v>
@@ -5334,22 +5334,22 @@
         <v>296</v>
       </c>
       <c r="B146" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E146" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="F146" t="n">
         <v>35</v>
       </c>
       <c r="G146" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H146" t="s">
         <v>297</v>
@@ -5360,22 +5360,22 @@
         <v>298</v>
       </c>
       <c r="B147" t="n">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E147" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F147" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G147" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H147" t="s">
         <v>299</v>
@@ -5386,22 +5386,22 @@
         <v>300</v>
       </c>
       <c r="B148" t="n">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E148" t="n">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="F148" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G148" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H148" t="s">
         <v>301</v>
@@ -5412,22 +5412,22 @@
         <v>302</v>
       </c>
       <c r="B149" t="n">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E149" t="n">
-        <v>41</v>
+        <v>280</v>
       </c>
       <c r="F149" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="G149" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H149" t="s">
         <v>303</v>
@@ -5438,22 +5438,22 @@
         <v>304</v>
       </c>
       <c r="B150" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E150" t="n">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F150" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G150" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H150" t="s">
         <v>305</v>
@@ -5464,22 +5464,22 @@
         <v>306</v>
       </c>
       <c r="B151" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E151" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G151" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H151" t="s">
         <v>307</v>
@@ -5490,22 +5490,22 @@
         <v>308</v>
       </c>
       <c r="B152" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E152" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="F152" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H152" t="s">
         <v>309</v>
@@ -5516,22 +5516,22 @@
         <v>310</v>
       </c>
       <c r="B153" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E153" t="n">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="F153" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G153" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H153" t="s">
         <v>311</v>
@@ -5548,16 +5548,16 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E154" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="F154" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="G154" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H154" t="s">
         <v>313</v>
@@ -5574,16 +5574,16 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E155" t="n">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="F155" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G155" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H155" t="s">
         <v>315</v>
@@ -5600,16 +5600,16 @@
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E156" t="n">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="F156" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="G156" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H156" t="s">
         <v>317</v>
@@ -5620,22 +5620,22 @@
         <v>318</v>
       </c>
       <c r="B157" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E157" t="n">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="F157" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H157" t="s">
         <v>319</v>
@@ -5646,22 +5646,22 @@
         <v>320</v>
       </c>
       <c r="B158" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E158" t="n">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="F158" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="G158" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H158" t="s">
         <v>321</v>
@@ -5678,16 +5678,16 @@
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E159" t="n">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="F159" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H159" t="s">
         <v>323</v>
@@ -5698,22 +5698,22 @@
         <v>324</v>
       </c>
       <c r="B160" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E160" t="n">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="F160" t="n">
         <v>38</v>
       </c>
       <c r="G160" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H160" t="s">
         <v>325</v>
@@ -5724,22 +5724,22 @@
         <v>326</v>
       </c>
       <c r="B161" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E161" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="F161" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G161" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H161" t="s">
         <v>327</v>
@@ -5750,22 +5750,22 @@
         <v>328</v>
       </c>
       <c r="B162" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E162" t="n">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="F162" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G162" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H162" t="s">
         <v>329</v>
@@ -5776,22 +5776,22 @@
         <v>330</v>
       </c>
       <c r="B163" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E163" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="F163" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G163" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H163" t="s">
         <v>331</v>
@@ -5802,22 +5802,22 @@
         <v>332</v>
       </c>
       <c r="B164" t="n">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E164" t="n">
-        <v>135</v>
+        <v>469</v>
       </c>
       <c r="F164" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="G164" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H164" t="s">
         <v>333</v>
@@ -5828,22 +5828,22 @@
         <v>334</v>
       </c>
       <c r="B165" t="n">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E165" t="n">
-        <v>469</v>
+        <v>142</v>
       </c>
       <c r="F165" t="n">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="G165" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H165" t="s">
         <v>335</v>
@@ -5854,22 +5854,22 @@
         <v>336</v>
       </c>
       <c r="B166" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E166" t="n">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="F166" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G166" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H166" t="s">
         <v>337</v>
@@ -5880,22 +5880,22 @@
         <v>338</v>
       </c>
       <c r="B167" t="n">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E167" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F167" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G167" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H167" t="s">
         <v>339</v>
@@ -5906,22 +5906,22 @@
         <v>340</v>
       </c>
       <c r="B168" t="n">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E168" t="n">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="F168" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G168" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H168" t="s">
         <v>341</v>
@@ -5932,22 +5932,22 @@
         <v>342</v>
       </c>
       <c r="B169" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E169" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="F169" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G169" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H169" t="s">
         <v>343</v>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E170" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="F170" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G170" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H170" t="s">
         <v>345</v>
@@ -5984,22 +5984,22 @@
         <v>346</v>
       </c>
       <c r="B171" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E171" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="F171" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G171" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H171" t="s">
         <v>347</v>
@@ -6010,22 +6010,22 @@
         <v>348</v>
       </c>
       <c r="B172" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E172" t="n">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="F172" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G172" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H172" t="s">
         <v>349</v>
@@ -6036,22 +6036,22 @@
         <v>350</v>
       </c>
       <c r="B173" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F173" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G173" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H173" t="s">
         <v>351</v>
@@ -6062,22 +6062,22 @@
         <v>352</v>
       </c>
       <c r="B174" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E174" t="n">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="F174" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G174" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H174" t="s">
         <v>353</v>
@@ -6088,22 +6088,22 @@
         <v>354</v>
       </c>
       <c r="B175" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E175" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F175" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G175" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H175" t="s">
         <v>355</v>
@@ -6114,22 +6114,22 @@
         <v>356</v>
       </c>
       <c r="B176" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E176" t="n">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="F176" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="G176" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H176" t="s">
         <v>357</v>
@@ -6140,22 +6140,22 @@
         <v>358</v>
       </c>
       <c r="B177" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E177" t="n">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="F177" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="G177" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H177" t="s">
         <v>359</v>
@@ -6166,22 +6166,22 @@
         <v>360</v>
       </c>
       <c r="B178" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E178" t="n">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="F178" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G178" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H178" t="s">
         <v>361</v>
@@ -6192,22 +6192,22 @@
         <v>362</v>
       </c>
       <c r="B179" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E179" t="n">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="F179" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G179" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H179" t="s">
         <v>363</v>
@@ -6218,22 +6218,22 @@
         <v>364</v>
       </c>
       <c r="B180" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E180" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F180" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G180" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H180" t="s">
         <v>365</v>
@@ -6244,22 +6244,22 @@
         <v>366</v>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E181" t="n">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="F181" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G181" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H181" t="s">
         <v>367</v>
@@ -6270,22 +6270,22 @@
         <v>368</v>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E182" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F182" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G182" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H182" t="s">
         <v>369</v>
@@ -6296,22 +6296,22 @@
         <v>370</v>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E183" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="F183" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G183" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H183" t="s">
         <v>371</v>
@@ -6322,22 +6322,22 @@
         <v>372</v>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E184" t="n">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="F184" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G184" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H184" t="s">
         <v>373</v>
@@ -6348,22 +6348,22 @@
         <v>374</v>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E185" t="n">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="F185" t="n">
         <v>31</v>
       </c>
       <c r="G185" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H185" t="s">
         <v>375</v>
@@ -6380,16 +6380,16 @@
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E186" t="n">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="F186" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G186" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H186" t="s">
         <v>377</v>
@@ -6406,16 +6406,16 @@
         <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E187" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F187" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G187" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H187" t="s">
         <v>379</v>
@@ -6432,16 +6432,16 @@
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E188" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="F188" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G188" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H188" t="s">
         <v>381</v>
@@ -6458,16 +6458,16 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E189" t="n">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="F189" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G189" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H189" t="s">
         <v>383</v>
@@ -6484,16 +6484,16 @@
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>5076</v>
+        <v>4400</v>
       </c>
       <c r="E190" t="n">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="F190" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G190" t="n">
-        <v>16335</v>
+        <v>17895</v>
       </c>
       <c r="H190" t="s">
         <v>385</v>
